--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4757" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4762" uniqueCount="659">
   <si>
     <t xml:space="preserve">50001583 - xemortiz stock </t>
   </si>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46238.48778556713</v>
+        <v>46240.823163877314</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>140</v>
@@ -9490,9 +9490,11 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="10"/>
+        <v>123</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>124</v>
+      </c>
       <c r="I127" s="9">
         <v>46281</v>
       </c>
@@ -9532,7 +9534,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46231.65337424769</v>
+        <v>46240.82316032407</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>140</v>
@@ -9541,9 +9543,11 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="I128" s="5">
         <v>46281</v>
       </c>
@@ -9583,7 +9587,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46231.65337373843</v>
+        <v>46240.8231571412</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>140</v>
@@ -9592,9 +9596,11 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H129" s="10"/>
+        <v>123</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>124</v>
+      </c>
       <c r="I129" s="9">
         <v>46281</v>
       </c>
@@ -9634,7 +9640,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46238.4877890625</v>
+        <v>46240.823153680554</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>140</v>
@@ -9643,9 +9649,11 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H130" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="I130" s="5">
         <v>46281</v>
       </c>
@@ -9685,7 +9693,7 @@
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46238.487794375</v>
+        <v>46240.82315002315</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>140</v>
@@ -9694,9 +9702,11 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="10"/>
+        <v>123</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>124</v>
+      </c>
       <c r="I131" s="9">
         <v>46281</v>
       </c>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -4699,7 +4699,7 @@
         <v>46238.48761943287</v>
       </c>
       <c r="D39" s="9">
-        <v>46238.48763195601</v>
+        <v>46241.206588078705</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>142</v>
@@ -4743,8 +4743,8 @@
       <c r="R39" s="9">
         <v>46244</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>32</v>
+      <c r="S39" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -453,37 +453,37 @@
     <t>Ingenieria y diseño:,Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
+    <t>1216916670896948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216916670896949</t>
+  </si>
+  <si>
+    <t>ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216950828707864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>Plano Preliminar  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216916670896948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216916670896949</t>
-  </si>
-  <si>
-    <t>ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216950828707864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>Plano Preliminar  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1216916670896950</t>
@@ -4524,7 +4524,7 @@
         <v>46232.578841863426</v>
       </c>
       <c r="D36" s="5">
-        <v>46234.19120591435</v>
+        <v>46242.18180460648</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>129</v>
@@ -4568,8 +4568,8 @@
       <c r="R36" s="5">
         <v>46237</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>134</v>
+      <c r="S36" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46231.5654175463</v>
@@ -4592,16 +4592,16 @@
         <v>46232.578818078706</v>
       </c>
       <c r="E37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="H37" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46231.56561290509</v>
@@ -4647,16 +4647,16 @@
         <v>46232.5788287037</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I38" s="5">
         <v>46237</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B39" s="9">
         <v>46231.5603328588</v>
@@ -4702,7 +4702,7 @@
         <v>46241.206588078705</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -4732,10 +4732,10 @@
         <v>126</v>
       </c>
       <c r="O39" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="P39" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="Q39" s="9">
         <v>46248</v>
@@ -4744,7 +4744,7 @@
         <v>46244</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4767,16 +4767,16 @@
         <v>46238.487596446765</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I40" s="5">
         <v>46244</v>
@@ -4794,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>129</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4822,16 +4822,16 @@
         <v>46238.48760439815</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I41" s="9">
         <v>46244</v>
@@ -4849,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>129</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4883,10 +4883,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46251</v>
@@ -4942,16 +4942,16 @@
         <v>46238.48774091435</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I43" s="9">
         <v>46251</v>
@@ -4972,7 +4972,7 @@
         <v>67</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>67</v>
@@ -4997,16 +4997,16 @@
         <v>46238.4877480787</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I44" s="5">
         <v>46251</v>
@@ -5027,7 +5027,7 @@
         <v>67</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>67</v>
@@ -5113,7 +5113,7 @@
         <v>46231.66593079861</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -5143,7 +5143,7 @@
         <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>153</v>
@@ -5166,7 +5166,7 @@
         <v>46231.665927685186</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -5196,7 +5196,7 @@
         <v>153</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>160</v>
@@ -5219,7 +5219,7 @@
         <v>46231.66592474537</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -5249,7 +5249,7 @@
         <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>153</v>
@@ -5272,7 +5272,7 @@
         <v>46231.66592186343</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -5302,7 +5302,7 @@
         <v>153</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>153</v>
@@ -5325,7 +5325,7 @@
         <v>46231.66591891204</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -5355,7 +5355,7 @@
         <v>153</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>153</v>
@@ -5378,7 +5378,7 @@
         <v>46231.66591577546</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -5408,7 +5408,7 @@
         <v>153</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>153</v>
@@ -5431,7 +5431,7 @@
         <v>46231.665912372686</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -5461,7 +5461,7 @@
         <v>153</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>153</v>
@@ -5484,7 +5484,7 @@
         <v>46231.66590944445</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -5514,7 +5514,7 @@
         <v>153</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>153</v>
@@ -5537,7 +5537,7 @@
         <v>46231.66590684028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -5567,7 +5567,7 @@
         <v>153</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>153</v>
@@ -5590,7 +5590,7 @@
         <v>46231.66590353009</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -5620,7 +5620,7 @@
         <v>153</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>153</v>
@@ -5643,7 +5643,7 @@
         <v>46231.66590057871</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5673,7 +5673,7 @@
         <v>153</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>153</v>
@@ -5696,7 +5696,7 @@
         <v>46231.66589771991</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5726,7 +5726,7 @@
         <v>153</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>153</v>
@@ -5749,7 +5749,7 @@
         <v>46231.66589495371</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5779,7 +5779,7 @@
         <v>153</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>153</v>
@@ -5802,7 +5802,7 @@
         <v>46231.66589175926</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5832,7 +5832,7 @@
         <v>153</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>153</v>
@@ -5855,7 +5855,7 @@
         <v>46231.6658891088</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5885,7 +5885,7 @@
         <v>153</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>153</v>
@@ -5908,7 +5908,7 @@
         <v>46231.66588648148</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5938,7 +5938,7 @@
         <v>153</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>153</v>
@@ -5961,7 +5961,7 @@
         <v>46231.66588371528</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5991,7 +5991,7 @@
         <v>153</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>153</v>
@@ -6014,7 +6014,7 @@
         <v>46231.665880636574</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -6044,7 +6044,7 @@
         <v>153</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>153</v>
@@ -6067,7 +6067,7 @@
         <v>46231.66587766204</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -6097,7 +6097,7 @@
         <v>153</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>153</v>
@@ -6120,7 +6120,7 @@
         <v>46231.66587439815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -6150,7 +6150,7 @@
         <v>153</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>153</v>
@@ -6173,7 +6173,7 @@
         <v>46231.66587150463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -6203,7 +6203,7 @@
         <v>153</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>153</v>
@@ -6226,7 +6226,7 @@
         <v>46231.665866979165</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -6256,7 +6256,7 @@
         <v>153</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>153</v>
@@ -6279,7 +6279,7 @@
         <v>46231.66585614583</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -6309,7 +6309,7 @@
         <v>153</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>153</v>
@@ -6332,7 +6332,7 @@
         <v>46231.66585559028</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -6362,7 +6362,7 @@
         <v>153</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>153</v>
@@ -6385,7 +6385,7 @@
         <v>46231.665857326385</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -6415,7 +6415,7 @@
         <v>153</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>153</v>
@@ -7036,7 +7036,7 @@
         <v>46238.48778015046</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -7089,7 +7089,7 @@
         <v>46238.48777791667</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -7142,7 +7142,7 @@
         <v>46238.48776831018</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -7195,7 +7195,7 @@
         <v>46238.48778649306</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -7248,7 +7248,7 @@
         <v>46238.48778996528</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -7301,7 +7301,7 @@
         <v>46238.48778768518</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -7354,7 +7354,7 @@
         <v>46238.48778834491</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -7407,7 +7407,7 @@
         <v>46238.48778460648</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7460,7 +7460,7 @@
         <v>46238.48779039352</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -7513,7 +7513,7 @@
         <v>46238.4877950463</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7566,7 +7566,7 @@
         <v>46238.48779283564</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7619,7 +7619,7 @@
         <v>46238.487791493055</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7672,7 +7672,7 @@
         <v>46238.48778605324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7725,7 +7725,7 @@
         <v>46238.48778420139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7778,7 +7778,7 @@
         <v>46238.48779195602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7831,7 +7831,7 @@
         <v>46238.487793657405</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7884,7 +7884,7 @@
         <v>46238.48779326389</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7937,7 +7937,7 @@
         <v>46238.48778962963</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7990,7 +7990,7 @@
         <v>46238.48778335648</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -8043,7 +8043,7 @@
         <v>46238.48778688657</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -8096,7 +8096,7 @@
         <v>46238.487783749995</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -8149,7 +8149,7 @@
         <v>46238.48779547453</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -8202,7 +8202,7 @@
         <v>46238.48778292824</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -8255,7 +8255,7 @@
         <v>46238.487793900465</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8308,7 +8308,7 @@
         <v>46238.48778729167</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -8424,7 +8424,7 @@
         <v>46238.48777921296</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -8477,7 +8477,7 @@
         <v>46238.487780752315</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8530,7 +8530,7 @@
         <v>46238.4877812037</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8583,7 +8583,7 @@
         <v>46231.66672795139</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8613,7 +8613,7 @@
         <v>251</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>259</v>
@@ -8636,7 +8636,7 @@
         <v>46238.487785000005</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8689,7 +8689,7 @@
         <v>46231.66672108797</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8742,7 +8742,7 @@
         <v>46238.48779480324</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8795,7 +8795,7 @@
         <v>46231.66671467593</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8825,7 +8825,7 @@
         <v>251</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>259</v>
@@ -8848,7 +8848,7 @@
         <v>46231.66671130787</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8901,7 +8901,7 @@
         <v>46238.487792395834</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8954,7 +8954,7 @@
         <v>46238.487790949075</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -9007,7 +9007,7 @@
         <v>46231.66670135417</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -9037,7 +9037,7 @@
         <v>251</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>259</v>
@@ -9060,7 +9060,7 @@
         <v>46238.48779597222</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -9113,7 +9113,7 @@
         <v>46231.66669519676</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -9143,7 +9143,7 @@
         <v>251</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>259</v>
@@ -9166,7 +9166,7 @@
         <v>46231.66669142361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -9196,7 +9196,7 @@
         <v>251</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>259</v>
@@ -9219,7 +9219,7 @@
         <v>46231.66668751158</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9249,7 +9249,7 @@
         <v>251</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>273</v>
@@ -9272,7 +9272,7 @@
         <v>46231.66668429398</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -9302,7 +9302,7 @@
         <v>251</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>273</v>
@@ -9325,7 +9325,7 @@
         <v>46231.66667890047</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9355,7 +9355,7 @@
         <v>251</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>273</v>
@@ -9378,7 +9378,7 @@
         <v>46231.66666850694</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9408,7 +9408,7 @@
         <v>251</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>273</v>
@@ -9431,7 +9431,7 @@
         <v>46231.66667090278</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9461,7 +9461,7 @@
         <v>251</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>273</v>
@@ -9484,7 +9484,7 @@
         <v>46240.823163877314</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9537,7 +9537,7 @@
         <v>46240.82316032407</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9567,7 +9567,7 @@
         <v>251</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>273</v>
@@ -9590,7 +9590,7 @@
         <v>46240.8231571412</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9620,7 +9620,7 @@
         <v>251</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>273</v>
@@ -9643,7 +9643,7 @@
         <v>46240.823153680554</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9696,7 +9696,7 @@
         <v>46240.82315002315</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -10095,7 +10095,7 @@
         <v>46231.66768597222</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10125,7 +10125,7 @@
         <v>301</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>304</v>
@@ -10148,7 +10148,7 @@
         <v>46231.66769336806</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -10178,7 +10178,7 @@
         <v>301</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>306</v>
@@ -10201,7 +10201,7 @@
         <v>46231.667685312495</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10231,7 +10231,7 @@
         <v>301</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>308</v>
@@ -10254,7 +10254,7 @@
         <v>46231.66768938657</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10284,7 +10284,7 @@
         <v>301</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>310</v>
@@ -10307,7 +10307,7 @@
         <v>46231.667695219905</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10337,7 +10337,7 @@
         <v>301</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>301</v>
@@ -10360,7 +10360,7 @@
         <v>46231.6676892824</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10390,7 +10390,7 @@
         <v>301</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>301</v>
@@ -10413,7 +10413,7 @@
         <v>46231.667685821754</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10443,7 +10443,7 @@
         <v>301</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>301</v>
@@ -10466,7 +10466,7 @@
         <v>46231.66768554398</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10496,7 +10496,7 @@
         <v>301</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P145" s="10" t="s">
         <v>301</v>
@@ -10519,7 +10519,7 @@
         <v>46231.6676859838</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10549,7 +10549,7 @@
         <v>301</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>301</v>
@@ -10572,7 +10572,7 @@
         <v>46231.66768939815</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10602,7 +10602,7 @@
         <v>301</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P147" s="10" t="s">
         <v>301</v>
@@ -10625,7 +10625,7 @@
         <v>46231.667693055555</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10655,7 +10655,7 @@
         <v>301</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>301</v>
@@ -10678,7 +10678,7 @@
         <v>46231.66769350694</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10708,7 +10708,7 @@
         <v>301</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>301</v>
@@ -10731,7 +10731,7 @@
         <v>46231.66769018519</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10761,7 +10761,7 @@
         <v>301</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>301</v>
@@ -10784,7 +10784,7 @@
         <v>46231.66768600694</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10814,7 +10814,7 @@
         <v>301</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>301</v>
@@ -10837,7 +10837,7 @@
         <v>46231.66768511574</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10867,7 +10867,7 @@
         <v>301</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>301</v>
@@ -10890,7 +10890,7 @@
         <v>46231.66771173611</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10920,7 +10920,7 @@
         <v>301</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P153" s="10" t="s">
         <v>301</v>
@@ -10943,7 +10943,7 @@
         <v>46231.66768918981</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10973,7 +10973,7 @@
         <v>301</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>301</v>
@@ -10996,7 +10996,7 @@
         <v>46231.66768920139</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -11026,7 +11026,7 @@
         <v>301</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>301</v>
@@ -11049,7 +11049,7 @@
         <v>46231.66768591435</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -11079,7 +11079,7 @@
         <v>301</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>301</v>
@@ -11102,7 +11102,7 @@
         <v>46231.66768583334</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -11132,7 +11132,7 @@
         <v>301</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>301</v>
@@ -11155,7 +11155,7 @@
         <v>46231.66768583334</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11185,7 +11185,7 @@
         <v>301</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>301</v>
@@ -11208,7 +11208,7 @@
         <v>46231.66768945602</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -11238,7 +11238,7 @@
         <v>301</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>301</v>
@@ -11261,7 +11261,7 @@
         <v>46231.66768604166</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11291,7 +11291,7 @@
         <v>301</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>301</v>
@@ -11314,7 +11314,7 @@
         <v>46231.66768939815</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11344,7 +11344,7 @@
         <v>301</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>301</v>
@@ -11367,7 +11367,7 @@
         <v>46231.66769310185</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11397,7 +11397,7 @@
         <v>301</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>301</v>
@@ -11483,7 +11483,7 @@
         <v>46238.48777972222</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11536,7 +11536,7 @@
         <v>46238.487781620366</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11589,7 +11589,7 @@
         <v>46238.487778553244</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11642,7 +11642,7 @@
         <v>46231.667831597224</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11695,7 +11695,7 @@
         <v>46231.667839699076</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11748,7 +11748,7 @@
         <v>46231.667835925924</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11801,7 +11801,7 @@
         <v>46231.667833680556</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11854,7 +11854,7 @@
         <v>46231.667830844905</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11907,7 +11907,7 @@
         <v>46231.66784657407</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11960,7 +11960,7 @@
         <v>46231.66782869213</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -12013,7 +12013,7 @@
         <v>46231.667833217594</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -12066,7 +12066,7 @@
         <v>46231.66783061343</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -12119,7 +12119,7 @@
         <v>46231.66784224537</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -12172,7 +12172,7 @@
         <v>46231.66783100694</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -12225,7 +12225,7 @@
         <v>46231.667828958336</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -12278,7 +12278,7 @@
         <v>46231.66783663194</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -12331,7 +12331,7 @@
         <v>46231.66783365741</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12384,7 +12384,7 @@
         <v>46231.66783075231</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12437,7 +12437,7 @@
         <v>46231.66782876157</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12490,7 +12490,7 @@
         <v>46231.66783196759</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12543,7 +12543,7 @@
         <v>46231.66783085648</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12596,7 +12596,7 @@
         <v>46231.6678306713</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12649,7 +12649,7 @@
         <v>46231.66784248843</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12702,7 +12702,7 @@
         <v>46231.667834085645</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12755,7 +12755,7 @@
         <v>46231.6678331713</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12871,7 +12871,7 @@
         <v>46231.66826131944</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12924,7 +12924,7 @@
         <v>46231.667989050926</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12977,7 +12977,7 @@
         <v>46231.6679641088</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -13030,7 +13030,7 @@
         <v>46231.66796936342</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -13083,7 +13083,7 @@
         <v>46231.66796449074</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -13136,7 +13136,7 @@
         <v>46231.66796210648</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -13189,7 +13189,7 @@
         <v>46231.66797386574</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -13242,7 +13242,7 @@
         <v>46231.66796228009</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -13295,7 +13295,7 @@
         <v>46231.66796244213</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -13348,7 +13348,7 @@
         <v>46231.66801194444</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -13401,7 +13401,7 @@
         <v>46231.668014675924</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13454,7 +13454,7 @@
         <v>46231.66801396991</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13507,7 +13507,7 @@
         <v>46231.66801421296</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13560,7 +13560,7 @@
         <v>46231.668014097224</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13613,7 +13613,7 @@
         <v>46231.66801686343</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13666,7 +13666,7 @@
         <v>46231.66801703704</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13719,7 +13719,7 @@
         <v>46231.668013946764</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13772,7 +13772,7 @@
         <v>46231.66801465278</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13825,7 +13825,7 @@
         <v>46231.66801458334</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13878,7 +13878,7 @@
         <v>46231.66796421296</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13931,7 +13931,7 @@
         <v>46231.6679640625</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13984,7 +13984,7 @@
         <v>46231.66796466435</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -14037,7 +14037,7 @@
         <v>46231.66796478009</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -14090,7 +14090,7 @@
         <v>46231.66796820602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -14143,7 +14143,7 @@
         <v>46231.667986134256</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -14259,7 +14259,7 @@
         <v>46231.66839868056</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -14312,7 +14312,7 @@
         <v>46238.48778229167</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -14365,7 +14365,7 @@
         <v>46231.668395995366</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -14418,7 +14418,7 @@
         <v>46231.66839239583</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14471,7 +14471,7 @@
         <v>46231.668395671295</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14524,7 +14524,7 @@
         <v>46231.66839586805</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14577,7 +14577,7 @@
         <v>46231.66839528935</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14630,7 +14630,7 @@
         <v>46231.66839170139</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
@@ -14683,7 +14683,7 @@
         <v>46231.66839528935</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
@@ -14736,7 +14736,7 @@
         <v>46231.66839199074</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
@@ -14789,7 +14789,7 @@
         <v>46231.668389108796</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
@@ -14842,7 +14842,7 @@
         <v>46231.668388935184</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
@@ -14895,7 +14895,7 @@
         <v>46231.66839212963</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
@@ -14948,7 +14948,7 @@
         <v>46231.66839202546</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
@@ -15001,7 +15001,7 @@
         <v>46231.66839535879</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
@@ -15054,7 +15054,7 @@
         <v>46231.66839859953</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
@@ -15107,7 +15107,7 @@
         <v>46231.668392141204</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -15160,7 +15160,7 @@
         <v>46231.66838898148</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
@@ -15213,7 +15213,7 @@
         <v>46231.66839825231</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
@@ -15266,7 +15266,7 @@
         <v>46231.668391851854</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
@@ -15319,7 +15319,7 @@
         <v>46231.668389583334</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
@@ -15372,7 +15372,7 @@
         <v>46231.668389074075</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15425,7 +15425,7 @@
         <v>46231.66838769676</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
@@ -15478,7 +15478,7 @@
         <v>46231.6683890162</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15531,7 +15531,7 @@
         <v>46231.66838675926</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15641,7 +15641,7 @@
         <v>46231.66850771991</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
@@ -15694,7 +15694,7 @@
         <v>46231.66851130787</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
@@ -15747,7 +15747,7 @@
         <v>46231.66851420139</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
@@ -15800,7 +15800,7 @@
         <v>46231.66851157407</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
@@ -15853,7 +15853,7 @@
         <v>46231.66850605324</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
@@ -15906,7 +15906,7 @@
         <v>46231.66851423611</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>26</v>
@@ -15959,7 +15959,7 @@
         <v>46231.66850797454</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>26</v>
@@ -16012,7 +16012,7 @@
         <v>46231.66850921296</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
@@ -16065,7 +16065,7 @@
         <v>46231.668514537036</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F250" s="6" t="s">
         <v>26</v>
@@ -16118,7 +16118,7 @@
         <v>46231.66850494213</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F251" s="10" t="s">
         <v>26</v>
@@ -16171,7 +16171,7 @@
         <v>46231.6685083912</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F252" s="6" t="s">
         <v>26</v>
@@ -16224,7 +16224,7 @@
         <v>46231.66850829861</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F253" s="10" t="s">
         <v>26</v>
@@ -16277,7 +16277,7 @@
         <v>46231.668502939814</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F254" s="6" t="s">
         <v>26</v>
@@ -16330,7 +16330,7 @@
         <v>46231.66851447917</v>
       </c>
       <c r="E255" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F255" s="10" t="s">
         <v>26</v>
@@ -16383,7 +16383,7 @@
         <v>46231.668505520836</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>26</v>
@@ -16436,7 +16436,7 @@
         <v>46231.66850818287</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>26</v>
@@ -16489,7 +16489,7 @@
         <v>46231.66851451389</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>26</v>
@@ -16542,7 +16542,7 @@
         <v>46231.6685082176</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F259" s="10" t="s">
         <v>26</v>
@@ -16595,7 +16595,7 @@
         <v>46231.66850509259</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>26</v>
@@ -16648,7 +16648,7 @@
         <v>46231.66851416667</v>
       </c>
       <c r="E261" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F261" s="10" t="s">
         <v>26</v>
@@ -16701,7 +16701,7 @@
         <v>46231.66851125</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F262" s="6" t="s">
         <v>26</v>
@@ -16754,7 +16754,7 @@
         <v>46231.66851166666</v>
       </c>
       <c r="E263" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F263" s="10" t="s">
         <v>26</v>
@@ -16807,7 +16807,7 @@
         <v>46231.668511192125</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F264" s="6" t="s">
         <v>26</v>
@@ -16860,7 +16860,7 @@
         <v>46231.66850479167</v>
       </c>
       <c r="E265" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F265" s="10" t="s">
         <v>26</v>
@@ -16913,7 +16913,7 @@
         <v>46231.66851174769</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>26</v>
@@ -17023,7 +17023,7 @@
         <v>46231.6686428588</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>26</v>
@@ -17076,7 +17076,7 @@
         <v>46231.668646087965</v>
       </c>
       <c r="E269" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F269" s="10" t="s">
         <v>26</v>
@@ -17129,7 +17129,7 @@
         <v>46231.66864605324</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>26</v>
@@ -17182,7 +17182,7 @@
         <v>46231.66864655093</v>
       </c>
       <c r="E271" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F271" s="10" t="s">
         <v>26</v>
@@ -17235,7 +17235,7 @@
         <v>46231.668646261576</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>26</v>
@@ -17288,7 +17288,7 @@
         <v>46231.668647604165</v>
       </c>
       <c r="E273" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F273" s="10" t="s">
         <v>26</v>
@@ -17341,7 +17341,7 @@
         <v>46231.66865532407</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>26</v>
@@ -17394,7 +17394,7 @@
         <v>46231.66864230324</v>
       </c>
       <c r="E275" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F275" s="10" t="s">
         <v>26</v>
@@ -17447,7 +17447,7 @@
         <v>46231.66865127315</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F276" s="6" t="s">
         <v>26</v>
@@ -17500,7 +17500,7 @@
         <v>46231.66864081018</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F277" s="10" t="s">
         <v>26</v>
@@ -17553,7 +17553,7 @@
         <v>46231.668640868054</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F278" s="6" t="s">
         <v>26</v>
@@ -17606,7 +17606,7 @@
         <v>46231.66864261574</v>
       </c>
       <c r="E279" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F279" s="10" t="s">
         <v>26</v>
@@ -17659,7 +17659,7 @@
         <v>46231.668640648146</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F280" s="6" t="s">
         <v>26</v>
@@ -17712,7 +17712,7 @@
         <v>46231.668646122685</v>
       </c>
       <c r="E281" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F281" s="10" t="s">
         <v>26</v>
@@ -17765,7 +17765,7 @@
         <v>46231.66864037037</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F282" s="6" t="s">
         <v>26</v>
@@ -17818,7 +17818,7 @@
         <v>46231.66863724537</v>
       </c>
       <c r="E283" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F283" s="10" t="s">
         <v>26</v>
@@ -17871,7 +17871,7 @@
         <v>46231.66864261574</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
@@ -17924,7 +17924,7 @@
         <v>46231.66864297454</v>
       </c>
       <c r="E285" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F285" s="10" t="s">
         <v>26</v>
@@ -17977,7 +17977,7 @@
         <v>46231.66863702546</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F286" s="6" t="s">
         <v>26</v>
@@ -18030,7 +18030,7 @@
         <v>46231.66864275463</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F287" s="10" t="s">
         <v>26</v>
@@ -18083,7 +18083,7 @@
         <v>46231.66864267361</v>
       </c>
       <c r="E288" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F288" s="6" t="s">
         <v>26</v>
@@ -18136,7 +18136,7 @@
         <v>46231.66863684027</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F289" s="10" t="s">
         <v>26</v>
@@ -18189,7 +18189,7 @@
         <v>46231.66864052083</v>
       </c>
       <c r="E290" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F290" s="6" t="s">
         <v>26</v>
@@ -18242,7 +18242,7 @@
         <v>46231.66864081018</v>
       </c>
       <c r="E291" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F291" s="10" t="s">
         <v>26</v>
@@ -18295,7 +18295,7 @@
         <v>46231.668645937505</v>
       </c>
       <c r="E292" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F292" s="6" t="s">
         <v>26</v>
@@ -18405,7 +18405,7 @@
         <v>46231.66880484954</v>
       </c>
       <c r="E294" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F294" s="6" t="s">
         <v>26</v>
@@ -18458,7 +18458,7 @@
         <v>46231.66880197916</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>26</v>
@@ -18511,7 +18511,7 @@
         <v>46231.66881472222</v>
       </c>
       <c r="E296" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F296" s="6" t="s">
         <v>26</v>
@@ -18564,7 +18564,7 @@
         <v>46231.66881128472</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F297" s="10" t="s">
         <v>26</v>
@@ -18617,7 +18617,7 @@
         <v>46231.66880478009</v>
       </c>
       <c r="E298" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F298" s="6" t="s">
         <v>26</v>
@@ -18670,7 +18670,7 @@
         <v>46231.668812268515</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F299" s="10" t="s">
         <v>26</v>
@@ -18723,7 +18723,7 @@
         <v>46231.66880841435</v>
       </c>
       <c r="E300" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F300" s="6" t="s">
         <v>26</v>
@@ -18776,7 +18776,7 @@
         <v>46231.66880237269</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F301" s="10" t="s">
         <v>26</v>
@@ -18829,7 +18829,7 @@
         <v>46231.66881479167</v>
       </c>
       <c r="E302" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F302" s="6" t="s">
         <v>26</v>
@@ -18882,7 +18882,7 @@
         <v>46231.66880479167</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F303" s="10" t="s">
         <v>26</v>
@@ -18935,7 +18935,7 @@
         <v>46231.66880506944</v>
       </c>
       <c r="E304" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F304" s="6" t="s">
         <v>26</v>
@@ -18988,7 +18988,7 @@
         <v>46231.668814432865</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F305" s="10" t="s">
         <v>26</v>
@@ -19041,7 +19041,7 @@
         <v>46231.66880857639</v>
       </c>
       <c r="E306" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F306" s="6" t="s">
         <v>26</v>
@@ -19094,7 +19094,7 @@
         <v>46231.66880244213</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>26</v>
@@ -19147,7 +19147,7 @@
         <v>46231.6688147338</v>
       </c>
       <c r="E308" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F308" s="6" t="s">
         <v>26</v>
@@ -19200,7 +19200,7 @@
         <v>46231.66880950231</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F309" s="10" t="s">
         <v>26</v>
@@ -19253,7 +19253,7 @@
         <v>46231.668803611115</v>
       </c>
       <c r="E310" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F310" s="6" t="s">
         <v>26</v>
@@ -19306,7 +19306,7 @@
         <v>46231.66881472222</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F311" s="10" t="s">
         <v>26</v>
@@ -19359,7 +19359,7 @@
         <v>46231.66880457176</v>
       </c>
       <c r="E312" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F312" s="6" t="s">
         <v>26</v>
@@ -19412,7 +19412,7 @@
         <v>46231.66881471065</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F313" s="10" t="s">
         <v>26</v>
@@ -19465,7 +19465,7 @@
         <v>46231.668809305556</v>
       </c>
       <c r="E314" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F314" s="6" t="s">
         <v>26</v>
@@ -19518,7 +19518,7 @@
         <v>46231.66880247685</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F315" s="10" t="s">
         <v>26</v>
@@ -19571,7 +19571,7 @@
         <v>46231.66881210648</v>
       </c>
       <c r="E316" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F316" s="6" t="s">
         <v>26</v>
@@ -19624,7 +19624,7 @@
         <v>46231.668805208334</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>26</v>
@@ -19677,7 +19677,7 @@
         <v>46231.668802141205</v>
       </c>
       <c r="E318" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F318" s="6" t="s">
         <v>26</v>
@@ -19840,7 +19840,7 @@
         <v>46231.66971627314</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F321" s="10" t="s">
         <v>26</v>
@@ -19893,7 +19893,7 @@
         <v>46231.66971195602</v>
       </c>
       <c r="E322" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F322" s="6" t="s">
         <v>26</v>
@@ -19946,7 +19946,7 @@
         <v>46231.66970780093</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F323" s="10" t="s">
         <v>26</v>
@@ -19999,7 +19999,7 @@
         <v>46231.669704722226</v>
       </c>
       <c r="E324" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F324" s="6" t="s">
         <v>26</v>
@@ -20052,7 +20052,7 @@
         <v>46231.6697007176</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F325" s="10" t="s">
         <v>26</v>
@@ -20105,7 +20105,7 @@
         <v>46231.66969769676</v>
       </c>
       <c r="E326" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F326" s="6" t="s">
         <v>26</v>
@@ -20158,7 +20158,7 @@
         <v>46231.66969472222</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>26</v>
@@ -20211,7 +20211,7 @@
         <v>46231.669691689814</v>
       </c>
       <c r="E328" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F328" s="6" t="s">
         <v>26</v>
@@ -20264,7 +20264,7 @@
         <v>46231.66968831018</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F329" s="10" t="s">
         <v>26</v>
@@ -20317,7 +20317,7 @@
         <v>46231.66968530093</v>
       </c>
       <c r="E330" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F330" s="6" t="s">
         <v>26</v>
@@ -20370,7 +20370,7 @@
         <v>46231.66968244213</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F331" s="10" t="s">
         <v>26</v>
@@ -20423,7 +20423,7 @@
         <v>46231.669678935184</v>
       </c>
       <c r="E332" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F332" s="6" t="s">
         <v>26</v>
@@ -20476,7 +20476,7 @@
         <v>46231.669675763886</v>
       </c>
       <c r="E333" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F333" s="10" t="s">
         <v>26</v>
@@ -20529,7 +20529,7 @@
         <v>46231.669672777774</v>
       </c>
       <c r="E334" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F334" s="6" t="s">
         <v>26</v>
@@ -20582,7 +20582,7 @@
         <v>46231.66966976852</v>
       </c>
       <c r="E335" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F335" s="10" t="s">
         <v>26</v>
@@ -20635,7 +20635,7 @@
         <v>46231.66966627315</v>
       </c>
       <c r="E336" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F336" s="6" t="s">
         <v>26</v>
@@ -20688,7 +20688,7 @@
         <v>46231.66966341435</v>
       </c>
       <c r="E337" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F337" s="10" t="s">
         <v>26</v>
@@ -20741,7 +20741,7 @@
         <v>46231.669660671294</v>
       </c>
       <c r="E338" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F338" s="6" t="s">
         <v>26</v>
@@ -20794,7 +20794,7 @@
         <v>46231.66965815972</v>
       </c>
       <c r="E339" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F339" s="10" t="s">
         <v>26</v>
@@ -20847,7 +20847,7 @@
         <v>46231.669653634264</v>
       </c>
       <c r="E340" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F340" s="6" t="s">
         <v>26</v>
@@ -20900,7 +20900,7 @@
         <v>46231.669650173615</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F341" s="10" t="s">
         <v>26</v>
@@ -20953,7 +20953,7 @@
         <v>46231.66964695602</v>
       </c>
       <c r="E342" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F342" s="6" t="s">
         <v>26</v>
@@ -21006,7 +21006,7 @@
         <v>46231.669632986115</v>
       </c>
       <c r="E343" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F343" s="10" t="s">
         <v>26</v>
@@ -21059,7 +21059,7 @@
         <v>46231.66963234954</v>
       </c>
       <c r="E344" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F344" s="6" t="s">
         <v>26</v>
@@ -21112,7 +21112,7 @@
         <v>46231.66963550926</v>
       </c>
       <c r="E345" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F345" s="10" t="s">
         <v>26</v>
@@ -21228,7 +21228,7 @@
         <v>46231.670200057866</v>
       </c>
       <c r="E347" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F347" s="10" t="s">
         <v>26</v>
@@ -21258,7 +21258,7 @@
         <v>555</v>
       </c>
       <c r="O347" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P347" s="10" t="s">
         <v>555</v>
@@ -21281,7 +21281,7 @@
         <v>46231.66998844907</v>
       </c>
       <c r="E348" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F348" s="6" t="s">
         <v>26</v>
@@ -21311,7 +21311,7 @@
         <v>555</v>
       </c>
       <c r="O348" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P348" s="6" t="s">
         <v>559</v>
@@ -21334,7 +21334,7 @@
         <v>46231.66998445602</v>
       </c>
       <c r="E349" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F349" s="10" t="s">
         <v>26</v>
@@ -21364,7 +21364,7 @@
         <v>555</v>
       </c>
       <c r="O349" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P349" s="10" t="s">
         <v>561</v>
@@ -21387,7 +21387,7 @@
         <v>46231.669980046296</v>
       </c>
       <c r="E350" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F350" s="6" t="s">
         <v>26</v>
@@ -21417,7 +21417,7 @@
         <v>555</v>
       </c>
       <c r="O350" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P350" s="6" t="s">
         <v>561</v>
@@ -21440,7 +21440,7 @@
         <v>46231.66997524306</v>
       </c>
       <c r="E351" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F351" s="10" t="s">
         <v>26</v>
@@ -21470,7 +21470,7 @@
         <v>555</v>
       </c>
       <c r="O351" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P351" s="10" t="s">
         <v>561</v>
@@ -21493,7 +21493,7 @@
         <v>46231.66997137731</v>
       </c>
       <c r="E352" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F352" s="6" t="s">
         <v>26</v>
@@ -21523,7 +21523,7 @@
         <v>555</v>
       </c>
       <c r="O352" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P352" s="6" t="s">
         <v>561</v>
@@ -21546,7 +21546,7 @@
         <v>46231.66996653935</v>
       </c>
       <c r="E353" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F353" s="10" t="s">
         <v>26</v>
@@ -21576,7 +21576,7 @@
         <v>555</v>
       </c>
       <c r="O353" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P353" s="10" t="s">
         <v>561</v>
@@ -21599,7 +21599,7 @@
         <v>46231.669961064814</v>
       </c>
       <c r="E354" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F354" s="6" t="s">
         <v>26</v>
@@ -21629,7 +21629,7 @@
         <v>555</v>
       </c>
       <c r="O354" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P354" s="6" t="s">
         <v>561</v>
@@ -21652,7 +21652,7 @@
         <v>46231.66995664352</v>
       </c>
       <c r="E355" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F355" s="10" t="s">
         <v>26</v>
@@ -21682,7 +21682,7 @@
         <v>555</v>
       </c>
       <c r="O355" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P355" s="10" t="s">
         <v>559</v>
@@ -21705,7 +21705,7 @@
         <v>46231.669952916665</v>
       </c>
       <c r="E356" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F356" s="6" t="s">
         <v>26</v>
@@ -21735,7 +21735,7 @@
         <v>555</v>
       </c>
       <c r="O356" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P356" s="6" t="s">
         <v>561</v>
@@ -21758,7 +21758,7 @@
         <v>46231.66994847222</v>
       </c>
       <c r="E357" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F357" s="10" t="s">
         <v>26</v>
@@ -21788,7 +21788,7 @@
         <v>555</v>
       </c>
       <c r="O357" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P357" s="10" t="s">
         <v>561</v>
@@ -21811,7 +21811,7 @@
         <v>46231.66994402777</v>
       </c>
       <c r="E358" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F358" s="6" t="s">
         <v>26</v>
@@ -21841,7 +21841,7 @@
         <v>555</v>
       </c>
       <c r="O358" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P358" s="6" t="s">
         <v>559</v>
@@ -21864,7 +21864,7 @@
         <v>46231.66994043981</v>
       </c>
       <c r="E359" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F359" s="10" t="s">
         <v>26</v>
@@ -21894,7 +21894,7 @@
         <v>555</v>
       </c>
       <c r="O359" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P359" s="10" t="s">
         <v>559</v>
@@ -21917,7 +21917,7 @@
         <v>46231.66993686343</v>
       </c>
       <c r="E360" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F360" s="6" t="s">
         <v>26</v>
@@ -21947,7 +21947,7 @@
         <v>555</v>
       </c>
       <c r="O360" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P360" s="6" t="s">
         <v>559</v>
@@ -21970,7 +21970,7 @@
         <v>46231.6699325</v>
       </c>
       <c r="E361" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F361" s="10" t="s">
         <v>26</v>
@@ -22000,7 +22000,7 @@
         <v>555</v>
       </c>
       <c r="O361" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P361" s="10" t="s">
         <v>559</v>
@@ -22023,7 +22023,7 @@
         <v>46231.66992857639</v>
       </c>
       <c r="E362" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F362" s="6" t="s">
         <v>26</v>
@@ -22053,7 +22053,7 @@
         <v>555</v>
       </c>
       <c r="O362" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P362" s="6" t="s">
         <v>575</v>
@@ -22076,7 +22076,7 @@
         <v>46231.66992512731</v>
       </c>
       <c r="E363" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F363" s="10" t="s">
         <v>26</v>
@@ -22106,7 +22106,7 @@
         <v>555</v>
       </c>
       <c r="O363" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P363" s="10" t="s">
         <v>575</v>
@@ -22129,7 +22129,7 @@
         <v>46231.669921064815</v>
       </c>
       <c r="E364" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F364" s="6" t="s">
         <v>26</v>
@@ -22159,7 +22159,7 @@
         <v>555</v>
       </c>
       <c r="O364" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P364" s="6" t="s">
         <v>578</v>
@@ -22182,7 +22182,7 @@
         <v>46231.6699174074</v>
       </c>
       <c r="E365" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F365" s="10" t="s">
         <v>26</v>
@@ -22212,7 +22212,7 @@
         <v>555</v>
       </c>
       <c r="O365" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P365" s="10" t="s">
         <v>578</v>
@@ -22235,7 +22235,7 @@
         <v>46231.66991390046</v>
       </c>
       <c r="E366" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F366" s="6" t="s">
         <v>26</v>
@@ -22265,7 +22265,7 @@
         <v>555</v>
       </c>
       <c r="O366" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P366" s="6" t="s">
         <v>578</v>
@@ -22288,7 +22288,7 @@
         <v>46231.66990978009</v>
       </c>
       <c r="E367" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F367" s="10" t="s">
         <v>26</v>
@@ -22318,7 +22318,7 @@
         <v>555</v>
       </c>
       <c r="O367" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P367" s="10" t="s">
         <v>578</v>
@@ -22341,7 +22341,7 @@
         <v>46231.66990606481</v>
       </c>
       <c r="E368" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F368" s="6" t="s">
         <v>26</v>
@@ -22371,7 +22371,7 @@
         <v>555</v>
       </c>
       <c r="O368" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P368" s="6" t="s">
         <v>578</v>
@@ -22394,7 +22394,7 @@
         <v>46231.66989173611</v>
       </c>
       <c r="E369" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F369" s="10" t="s">
         <v>26</v>
@@ -22424,7 +22424,7 @@
         <v>555</v>
       </c>
       <c r="O369" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P369" s="10" t="s">
         <v>575</v>
@@ -22447,7 +22447,7 @@
         <v>46231.66989118056</v>
       </c>
       <c r="E370" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F370" s="6" t="s">
         <v>26</v>
@@ -22477,7 +22477,7 @@
         <v>555</v>
       </c>
       <c r="O370" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P370" s="6" t="s">
         <v>575</v>
@@ -22500,7 +22500,7 @@
         <v>46231.669893796294</v>
       </c>
       <c r="E371" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F371" s="10" t="s">
         <v>26</v>
@@ -22530,7 +22530,7 @@
         <v>555</v>
       </c>
       <c r="O371" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P371" s="10" t="s">
         <v>578</v>
@@ -22616,7 +22616,7 @@
         <v>46231.67078247685</v>
       </c>
       <c r="E373" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F373" s="10" t="s">
         <v>26</v>
@@ -22669,7 +22669,7 @@
         <v>46231.67077917824</v>
       </c>
       <c r="E374" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F374" s="6" t="s">
         <v>26</v>
@@ -22699,7 +22699,7 @@
         <v>587</v>
       </c>
       <c r="O374" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P374" s="6" t="s">
         <v>591</v>
@@ -22722,7 +22722,7 @@
         <v>46231.6707759375</v>
       </c>
       <c r="E375" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F375" s="10" t="s">
         <v>26</v>
@@ -22752,7 +22752,7 @@
         <v>587</v>
       </c>
       <c r="O375" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P375" s="10" t="s">
         <v>591</v>
@@ -22775,7 +22775,7 @@
         <v>46231.67077253472</v>
       </c>
       <c r="E376" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F376" s="6" t="s">
         <v>26</v>
@@ -22805,7 +22805,7 @@
         <v>587</v>
       </c>
       <c r="O376" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P376" s="6" t="s">
         <v>591</v>
@@ -22828,7 +22828,7 @@
         <v>46231.67076925926</v>
       </c>
       <c r="E377" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F377" s="10" t="s">
         <v>26</v>
@@ -22858,7 +22858,7 @@
         <v>587</v>
       </c>
       <c r="O377" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P377" s="10" t="s">
         <v>591</v>
@@ -22881,7 +22881,7 @@
         <v>46231.670765393515</v>
       </c>
       <c r="E378" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F378" s="6" t="s">
         <v>26</v>
@@ -22911,7 +22911,7 @@
         <v>587</v>
       </c>
       <c r="O378" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P378" s="6" t="s">
         <v>589</v>
@@ -22934,7 +22934,7 @@
         <v>46231.6707622338</v>
       </c>
       <c r="E379" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F379" s="10" t="s">
         <v>26</v>
@@ -22964,7 +22964,7 @@
         <v>587</v>
       </c>
       <c r="O379" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P379" s="10" t="s">
         <v>589</v>
@@ -22987,7 +22987,7 @@
         <v>46231.67075878472</v>
       </c>
       <c r="E380" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F380" s="6" t="s">
         <v>26</v>
@@ -23017,7 +23017,7 @@
         <v>587</v>
       </c>
       <c r="O380" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P380" s="6" t="s">
         <v>591</v>
@@ -23040,7 +23040,7 @@
         <v>46231.670755451385</v>
       </c>
       <c r="E381" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F381" s="10" t="s">
         <v>26</v>
@@ -23070,7 +23070,7 @@
         <v>587</v>
       </c>
       <c r="O381" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P381" s="10" t="s">
         <v>591</v>
@@ -23093,7 +23093,7 @@
         <v>46231.67075229167</v>
       </c>
       <c r="E382" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F382" s="6" t="s">
         <v>26</v>
@@ -23123,7 +23123,7 @@
         <v>587</v>
       </c>
       <c r="O382" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P382" s="6" t="s">
         <v>591</v>
@@ -23146,7 +23146,7 @@
         <v>46231.67074930556</v>
       </c>
       <c r="E383" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F383" s="10" t="s">
         <v>26</v>
@@ -23176,7 +23176,7 @@
         <v>587</v>
       </c>
       <c r="O383" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P383" s="10" t="s">
         <v>591</v>
@@ -23199,7 +23199,7 @@
         <v>46231.67074609954</v>
       </c>
       <c r="E384" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F384" s="6" t="s">
         <v>26</v>
@@ -23229,7 +23229,7 @@
         <v>587</v>
       </c>
       <c r="O384" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P384" s="6" t="s">
         <v>589</v>
@@ -23252,7 +23252,7 @@
         <v>46231.67074238426</v>
       </c>
       <c r="E385" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F385" s="10" t="s">
         <v>26</v>
@@ -23282,7 +23282,7 @@
         <v>587</v>
       </c>
       <c r="O385" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P385" s="10" t="s">
         <v>591</v>
@@ -23305,7 +23305,7 @@
         <v>46231.670739340276</v>
       </c>
       <c r="E386" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F386" s="6" t="s">
         <v>26</v>
@@ -23335,7 +23335,7 @@
         <v>587</v>
       </c>
       <c r="O386" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P386" s="6" t="s">
         <v>591</v>
@@ -23358,7 +23358,7 @@
         <v>46231.67073607639</v>
       </c>
       <c r="E387" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F387" s="10" t="s">
         <v>26</v>
@@ -23388,7 +23388,7 @@
         <v>587</v>
       </c>
       <c r="O387" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P387" s="10" t="s">
         <v>591</v>
@@ -23411,7 +23411,7 @@
         <v>46231.67073236111</v>
       </c>
       <c r="E388" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F388" s="6" t="s">
         <v>26</v>
@@ -23441,7 +23441,7 @@
         <v>587</v>
       </c>
       <c r="O388" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P388" s="6" t="s">
         <v>606</v>
@@ -23464,7 +23464,7 @@
         <v>46231.67072928241</v>
       </c>
       <c r="E389" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F389" s="10" t="s">
         <v>26</v>
@@ -23494,7 +23494,7 @@
         <v>587</v>
       </c>
       <c r="O389" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P389" s="10" t="s">
         <v>608</v>
@@ -23517,7 +23517,7 @@
         <v>46231.67072601852</v>
       </c>
       <c r="E390" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F390" s="6" t="s">
         <v>26</v>
@@ -23547,7 +23547,7 @@
         <v>587</v>
       </c>
       <c r="O390" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P390" s="6" t="s">
         <v>608</v>
@@ -23570,7 +23570,7 @@
         <v>46231.67072258102</v>
       </c>
       <c r="E391" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F391" s="10" t="s">
         <v>26</v>
@@ -23600,7 +23600,7 @@
         <v>587</v>
       </c>
       <c r="O391" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P391" s="10" t="s">
         <v>606</v>
@@ -23623,7 +23623,7 @@
         <v>46231.67071851852</v>
       </c>
       <c r="E392" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F392" s="6" t="s">
         <v>26</v>
@@ -23653,7 +23653,7 @@
         <v>587</v>
       </c>
       <c r="O392" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P392" s="6" t="s">
         <v>608</v>
@@ -23676,7 +23676,7 @@
         <v>46231.67071464121</v>
       </c>
       <c r="E393" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F393" s="10" t="s">
         <v>26</v>
@@ -23706,7 +23706,7 @@
         <v>587</v>
       </c>
       <c r="O393" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P393" s="10" t="s">
         <v>606</v>
@@ -23729,7 +23729,7 @@
         <v>46231.67071099537</v>
       </c>
       <c r="E394" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F394" s="6" t="s">
         <v>26</v>
@@ -23759,7 +23759,7 @@
         <v>587</v>
       </c>
       <c r="O394" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P394" s="6" t="s">
         <v>606</v>
@@ -23782,7 +23782,7 @@
         <v>46231.67070591435</v>
       </c>
       <c r="E395" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F395" s="10" t="s">
         <v>26</v>
@@ -23812,7 +23812,7 @@
         <v>587</v>
       </c>
       <c r="O395" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P395" s="10" t="s">
         <v>608</v>
@@ -23835,7 +23835,7 @@
         <v>46231.67069403935</v>
       </c>
       <c r="E396" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F396" s="6" t="s">
         <v>26</v>
@@ -23865,7 +23865,7 @@
         <v>587</v>
       </c>
       <c r="O396" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P396" s="6" t="s">
         <v>606</v>
@@ -23888,7 +23888,7 @@
         <v>46231.670696319445</v>
       </c>
       <c r="E397" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F397" s="10" t="s">
         <v>26</v>
@@ -23918,7 +23918,7 @@
         <v>587</v>
       </c>
       <c r="O397" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P397" s="10" t="s">
         <v>606</v>
@@ -24004,7 +24004,7 @@
         <v>46231.67106579861</v>
       </c>
       <c r="E399" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F399" s="10" t="s">
         <v>26</v>
@@ -24034,7 +24034,7 @@
         <v>618</v>
       </c>
       <c r="O399" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P399" s="10" t="s">
         <v>621</v>
@@ -24057,7 +24057,7 @@
         <v>46231.671062407404</v>
       </c>
       <c r="E400" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F400" s="6" t="s">
         <v>26</v>
@@ -24087,7 +24087,7 @@
         <v>618</v>
       </c>
       <c r="O400" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P400" s="6" t="s">
         <v>623</v>
@@ -24110,7 +24110,7 @@
         <v>46231.67105903935</v>
       </c>
       <c r="E401" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F401" s="10" t="s">
         <v>26</v>
@@ -24140,7 +24140,7 @@
         <v>618</v>
       </c>
       <c r="O401" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P401" s="10" t="s">
         <v>625</v>
@@ -24163,7 +24163,7 @@
         <v>46231.67105518519</v>
       </c>
       <c r="E402" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F402" s="6" t="s">
         <v>26</v>
@@ -24193,7 +24193,7 @@
         <v>618</v>
       </c>
       <c r="O402" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P402" s="6" t="s">
         <v>618</v>
@@ -24216,7 +24216,7 @@
         <v>46231.671052025464</v>
       </c>
       <c r="E403" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F403" s="10" t="s">
         <v>26</v>
@@ -24246,7 +24246,7 @@
         <v>618</v>
       </c>
       <c r="O403" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P403" s="10" t="s">
         <v>618</v>
@@ -24269,7 +24269,7 @@
         <v>46231.67104925926</v>
       </c>
       <c r="E404" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F404" s="6" t="s">
         <v>26</v>
@@ -24299,7 +24299,7 @@
         <v>618</v>
       </c>
       <c r="O404" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P404" s="6" t="s">
         <v>618</v>
@@ -24322,7 +24322,7 @@
         <v>46231.67104619213</v>
       </c>
       <c r="E405" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F405" s="10" t="s">
         <v>26</v>
@@ -24352,7 +24352,7 @@
         <v>618</v>
       </c>
       <c r="O405" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P405" s="10" t="s">
         <v>618</v>
@@ -24375,7 +24375,7 @@
         <v>46231.67104260417</v>
       </c>
       <c r="E406" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F406" s="6" t="s">
         <v>26</v>
@@ -24405,7 +24405,7 @@
         <v>618</v>
       </c>
       <c r="O406" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P406" s="6" t="s">
         <v>618</v>
@@ -24428,7 +24428,7 @@
         <v>46231.67103974537</v>
       </c>
       <c r="E407" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F407" s="10" t="s">
         <v>26</v>
@@ -24458,7 +24458,7 @@
         <v>618</v>
       </c>
       <c r="O407" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P407" s="10" t="s">
         <v>618</v>
@@ -24481,7 +24481,7 @@
         <v>46231.67103653935</v>
       </c>
       <c r="E408" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F408" s="6" t="s">
         <v>26</v>
@@ -24511,7 +24511,7 @@
         <v>618</v>
       </c>
       <c r="O408" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P408" s="6" t="s">
         <v>618</v>
@@ -24534,7 +24534,7 @@
         <v>46231.671033182865</v>
       </c>
       <c r="E409" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F409" s="10" t="s">
         <v>26</v>
@@ -24564,7 +24564,7 @@
         <v>618</v>
       </c>
       <c r="O409" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P409" s="10" t="s">
         <v>618</v>
@@ -24587,7 +24587,7 @@
         <v>46231.67103011574</v>
       </c>
       <c r="E410" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F410" s="6" t="s">
         <v>26</v>
@@ -24617,7 +24617,7 @@
         <v>618</v>
       </c>
       <c r="O410" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P410" s="6" t="s">
         <v>618</v>
@@ -24640,7 +24640,7 @@
         <v>46231.67102701389</v>
       </c>
       <c r="E411" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F411" s="10" t="s">
         <v>26</v>
@@ -24670,7 +24670,7 @@
         <v>618</v>
       </c>
       <c r="O411" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P411" s="10" t="s">
         <v>618</v>
@@ -24693,7 +24693,7 @@
         <v>46231.671023993054</v>
       </c>
       <c r="E412" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F412" s="6" t="s">
         <v>26</v>
@@ -24723,7 +24723,7 @@
         <v>618</v>
       </c>
       <c r="O412" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P412" s="6" t="s">
         <v>618</v>
@@ -24746,7 +24746,7 @@
         <v>46231.67102047453</v>
       </c>
       <c r="E413" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F413" s="10" t="s">
         <v>26</v>
@@ -24776,7 +24776,7 @@
         <v>618</v>
       </c>
       <c r="O413" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P413" s="10" t="s">
         <v>618</v>
@@ -24799,7 +24799,7 @@
         <v>46231.67101741898</v>
       </c>
       <c r="E414" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F414" s="6" t="s">
         <v>26</v>
@@ -24829,7 +24829,7 @@
         <v>618</v>
       </c>
       <c r="O414" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P414" s="6" t="s">
         <v>618</v>
@@ -24852,7 +24852,7 @@
         <v>46231.671014259264</v>
       </c>
       <c r="E415" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F415" s="10" t="s">
         <v>26</v>
@@ -24882,7 +24882,7 @@
         <v>618</v>
       </c>
       <c r="O415" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P415" s="10" t="s">
         <v>618</v>
@@ -24905,7 +24905,7 @@
         <v>46231.671010289356</v>
       </c>
       <c r="E416" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F416" s="6" t="s">
         <v>26</v>
@@ -24935,7 +24935,7 @@
         <v>618</v>
       </c>
       <c r="O416" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P416" s="6" t="s">
         <v>618</v>
@@ -24958,7 +24958,7 @@
         <v>46231.67100728009</v>
       </c>
       <c r="E417" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F417" s="10" t="s">
         <v>26</v>
@@ -24988,7 +24988,7 @@
         <v>618</v>
       </c>
       <c r="O417" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P417" s="10" t="s">
         <v>618</v>
@@ -25011,7 +25011,7 @@
         <v>46231.67100423611</v>
       </c>
       <c r="E418" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F418" s="6" t="s">
         <v>26</v>
@@ -25041,7 +25041,7 @@
         <v>618</v>
       </c>
       <c r="O418" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P418" s="6" t="s">
         <v>618</v>
@@ -25064,7 +25064,7 @@
         <v>46231.6710006713</v>
       </c>
       <c r="E419" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F419" s="10" t="s">
         <v>26</v>
@@ -25094,7 +25094,7 @@
         <v>618</v>
       </c>
       <c r="O419" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P419" s="10" t="s">
         <v>618</v>
@@ -25117,7 +25117,7 @@
         <v>46231.67099731481</v>
       </c>
       <c r="E420" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F420" s="6" t="s">
         <v>26</v>
@@ -25147,7 +25147,7 @@
         <v>618</v>
       </c>
       <c r="O420" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P420" s="6" t="s">
         <v>618</v>
@@ -25170,7 +25170,7 @@
         <v>46231.67098568287</v>
       </c>
       <c r="E421" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F421" s="10" t="s">
         <v>26</v>
@@ -25200,7 +25200,7 @@
         <v>618</v>
       </c>
       <c r="O421" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P421" s="10" t="s">
         <v>618</v>
@@ -25223,7 +25223,7 @@
         <v>46231.670985115736</v>
       </c>
       <c r="E422" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F422" s="6" t="s">
         <v>26</v>
@@ -25253,7 +25253,7 @@
         <v>618</v>
       </c>
       <c r="O422" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P422" s="6" t="s">
         <v>618</v>
@@ -25276,7 +25276,7 @@
         <v>46231.67098739583</v>
       </c>
       <c r="E423" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F423" s="10" t="s">
         <v>26</v>
@@ -25306,7 +25306,7 @@
         <v>618</v>
       </c>
       <c r="O423" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P423" s="10" t="s">
         <v>618</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -4874,7 +4874,7 @@
         <v>46238.487760937496</v>
       </c>
       <c r="D42" s="5">
-        <v>46238.487772928245</v>
+        <v>46244.205140300925</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>67</v>
@@ -4918,8 +4918,8 @@
       <c r="R42" s="5">
         <v>46251</v>
       </c>
-      <c r="S42" s="7" t="s">
-        <v>32</v>
+      <c r="S42" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -258,6 +258,9 @@
     <t>Generación OC corte laser   OT 4382 - OT 4383 ,Propuesta compras:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
@@ -481,9 +484,6 @@
   </si>
   <si>
     <t>Ingenieria y diseño:,Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216916670896950</t>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46238.48780822917</v>
+        <v>46246.18983402778</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>65</v>
@@ -3479,29 +3479,29 @@
       <c r="R17" s="9">
         <v>46252</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>32</v>
+      <c r="S17" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5">
         <v>46231.56019936343</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46238.48780771991</v>
+        <v>46246.18983418982</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -3534,7 +3534,7 @@
         <v>67</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q18" s="5">
         <v>46253</v>
@@ -3542,29 +3542,29 @@
       <c r="R18" s="5">
         <v>46252</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>32</v>
+      <c r="S18" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" s="9">
         <v>46231.56020403936</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46238.4878086574</v>
+        <v>46246.189833819444</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -3597,7 +3597,7 @@
         <v>67</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="9">
         <v>46253</v>
@@ -3605,29 +3605,29 @@
       <c r="R19" s="9">
         <v>46252</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>32</v>
+      <c r="S19" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" s="5">
         <v>46231.560208518524</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46238.48780771991</v>
+        <v>46246.189833854165</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3660,7 +3660,7 @@
         <v>67</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="5">
         <v>46253</v>
@@ -3668,19 +3668,19 @@
       <c r="R20" s="5">
         <v>46252</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>32</v>
+      <c r="S20" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="9">
         <v>46231.56009197916</v>
@@ -3690,7 +3690,7 @@
         <v>46231.652924166665</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -3714,7 +3714,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" s="5">
         <v>46231.56021390046</v>
@@ -3737,16 +3737,16 @@
         <v>46232.61729246528</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46254</v>
@@ -3764,13 +3764,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q22" s="5">
         <v>46266</v>
@@ -3785,12 +3785,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="9">
         <v>46231.56021947917</v>
@@ -3800,16 +3800,16 @@
         <v>46231.664890995366</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I23" s="9">
         <v>46254</v>
@@ -3827,13 +3827,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3844,12 +3844,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46231.560224166664</v>
@@ -3859,16 +3859,16 @@
         <v>46231.664886238425</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I24" s="5">
         <v>46258</v>
@@ -3886,13 +3886,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3903,12 +3903,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="9">
         <v>46231.56022881945</v>
@@ -3918,16 +3918,16 @@
         <v>46232.617298819445</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I25" s="9">
         <v>46254</v>
@@ -3945,10 +3945,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3966,12 +3966,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46231.560233067124</v>
@@ -3981,16 +3981,16 @@
         <v>46231.66497333333</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I26" s="5">
         <v>46254</v>
@@ -4008,13 +4008,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" s="9">
         <v>46231.56023700231</v>
@@ -4034,16 +4034,16 @@
         <v>46231.66496887732</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I27" s="9">
         <v>46258</v>
@@ -4061,13 +4061,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46231.560240844905</v>
@@ -4087,16 +4087,16 @@
         <v>46232.617300763886</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I28" s="5">
         <v>46254</v>
@@ -4114,10 +4114,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -4135,12 +4135,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="9">
         <v>46231.56025052084</v>
@@ -4150,16 +4150,16 @@
         <v>46231.66504327546</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I29" s="9">
         <v>46254</v>
@@ -4177,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46231.5602546875</v>
@@ -4203,16 +4203,16 @@
         <v>46231.66503913194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I30" s="5">
         <v>46258</v>
@@ -4230,13 +4230,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" s="9">
         <v>46231.56025912037</v>
@@ -4256,16 +4256,16 @@
         <v>46232.617424502314</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I31" s="9">
         <v>46254</v>
@@ -4283,10 +4283,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -4304,12 +4304,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46231.56026384259</v>
@@ -4319,16 +4319,16 @@
         <v>46237.55371688657</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I32" s="5">
         <v>46254</v>
@@ -4346,13 +4346,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" s="9">
         <v>46231.56026863426</v>
@@ -4372,16 +4372,16 @@
         <v>46231.66516560185</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I33" s="9">
         <v>46265</v>
@@ -4399,13 +4399,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -4415,7 +4415,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5">
         <v>46231.56031771991</v>
@@ -4425,16 +4425,16 @@
         <v>46231.66521511574</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46296</v>
@@ -4452,13 +4452,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B35" s="9">
         <v>46231.56032325231</v>
@@ -4478,7 +4478,7 @@
         <v>46238.48777733796</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -4502,7 +4502,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46231.560327893516</v>
@@ -4527,16 +4527,16 @@
         <v>46242.18180460648</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46237</v>
@@ -4554,13 +4554,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="5">
         <v>46241</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46231.5654175463</v>
@@ -4592,16 +4592,16 @@
         <v>46232.578818078706</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -4619,13 +4619,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>45</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46231.56561290509</v>
@@ -4647,16 +4647,16 @@
         <v>46232.5788287037</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I38" s="5">
         <v>46237</v>
@@ -4674,13 +4674,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>45</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="9">
         <v>46231.5603328588</v>
@@ -4702,16 +4702,16 @@
         <v>46241.206588078705</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I39" s="9">
         <v>46244</v>
@@ -4729,13 +4729,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q39" s="9">
         <v>46248</v>
@@ -4744,7 +4744,7 @@
         <v>46244</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4767,16 +4767,16 @@
         <v>46238.487596446765</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I40" s="5">
         <v>46244</v>
@@ -4794,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4822,16 +4822,16 @@
         <v>46238.48760439815</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I41" s="9">
         <v>46244</v>
@@ -4849,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4883,10 +4883,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46251</v>
@@ -4904,7 +4904,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>148</v>
@@ -4919,7 +4919,7 @@
         <v>46251</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -4942,16 +4942,16 @@
         <v>46238.48774091435</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I43" s="9">
         <v>46251</v>
@@ -4972,7 +4972,7 @@
         <v>67</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>67</v>
@@ -4997,16 +4997,16 @@
         <v>46238.4877480787</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I44" s="5">
         <v>46251</v>
@@ -5027,7 +5027,7 @@
         <v>67</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>67</v>
@@ -5077,7 +5077,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>156</v>
@@ -5098,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -5113,7 +5113,7 @@
         <v>46231.66593079861</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -5143,7 +5143,7 @@
         <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>153</v>
@@ -5166,7 +5166,7 @@
         <v>46231.665927685186</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -5196,7 +5196,7 @@
         <v>153</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>160</v>
@@ -5219,7 +5219,7 @@
         <v>46231.66592474537</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -5249,7 +5249,7 @@
         <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>153</v>
@@ -5272,7 +5272,7 @@
         <v>46231.66592186343</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -5302,7 +5302,7 @@
         <v>153</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>153</v>
@@ -5325,7 +5325,7 @@
         <v>46231.66591891204</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -5355,7 +5355,7 @@
         <v>153</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>153</v>
@@ -5378,7 +5378,7 @@
         <v>46231.66591577546</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -5408,7 +5408,7 @@
         <v>153</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>153</v>
@@ -5431,7 +5431,7 @@
         <v>46231.665912372686</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -5461,7 +5461,7 @@
         <v>153</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>153</v>
@@ -5484,7 +5484,7 @@
         <v>46231.66590944445</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -5514,7 +5514,7 @@
         <v>153</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>153</v>
@@ -5537,7 +5537,7 @@
         <v>46231.66590684028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -5567,7 +5567,7 @@
         <v>153</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>153</v>
@@ -5590,7 +5590,7 @@
         <v>46231.66590353009</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -5620,7 +5620,7 @@
         <v>153</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>153</v>
@@ -5643,7 +5643,7 @@
         <v>46231.66590057871</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5673,7 +5673,7 @@
         <v>153</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>153</v>
@@ -5696,7 +5696,7 @@
         <v>46231.66589771991</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5726,7 +5726,7 @@
         <v>153</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>153</v>
@@ -5749,7 +5749,7 @@
         <v>46231.66589495371</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5779,7 +5779,7 @@
         <v>153</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>153</v>
@@ -5802,7 +5802,7 @@
         <v>46231.66589175926</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5832,7 +5832,7 @@
         <v>153</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>153</v>
@@ -5855,7 +5855,7 @@
         <v>46231.6658891088</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5885,7 +5885,7 @@
         <v>153</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>153</v>
@@ -5908,7 +5908,7 @@
         <v>46231.66588648148</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5938,7 +5938,7 @@
         <v>153</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>153</v>
@@ -5961,7 +5961,7 @@
         <v>46231.66588371528</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5991,7 +5991,7 @@
         <v>153</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>153</v>
@@ -6014,7 +6014,7 @@
         <v>46231.665880636574</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -6044,7 +6044,7 @@
         <v>153</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>153</v>
@@ -6067,7 +6067,7 @@
         <v>46231.66587766204</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -6097,7 +6097,7 @@
         <v>153</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>153</v>
@@ -6120,7 +6120,7 @@
         <v>46231.66587439815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -6150,7 +6150,7 @@
         <v>153</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>153</v>
@@ -6173,7 +6173,7 @@
         <v>46231.66587150463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -6203,7 +6203,7 @@
         <v>153</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>153</v>
@@ -6226,7 +6226,7 @@
         <v>46231.665866979165</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -6256,7 +6256,7 @@
         <v>153</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>153</v>
@@ -6279,7 +6279,7 @@
         <v>46231.66585614583</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -6309,7 +6309,7 @@
         <v>153</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>153</v>
@@ -6332,7 +6332,7 @@
         <v>46231.66585559028</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -6362,7 +6362,7 @@
         <v>153</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>153</v>
@@ -6385,7 +6385,7 @@
         <v>46231.665857326385</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -6415,7 +6415,7 @@
         <v>153</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>153</v>
@@ -6515,7 +6515,7 @@
         <v>185</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>191</v>
@@ -6533,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6578,7 +6578,7 @@
         <v>185</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>194</v>
@@ -6596,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6641,7 +6641,7 @@
         <v>185</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>197</v>
@@ -6659,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6680,10 +6680,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I75" s="9">
         <v>46268</v>
@@ -6722,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6743,10 +6743,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I76" s="5">
         <v>46268</v>
@@ -6785,7 +6785,7 @@
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6806,10 +6806,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I77" s="9">
         <v>46268</v>
@@ -6848,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6910,7 +6910,7 @@
         <v>46231.66610032407</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6940,7 +6940,7 @@
         <v>207</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>212</v>
@@ -6958,7 +6958,7 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -7036,7 +7036,7 @@
         <v>46238.48778015046</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -7089,7 +7089,7 @@
         <v>46238.48777791667</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -7142,7 +7142,7 @@
         <v>46238.48776831018</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -7195,7 +7195,7 @@
         <v>46238.48778649306</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -7248,7 +7248,7 @@
         <v>46238.48778996528</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -7301,7 +7301,7 @@
         <v>46238.48778768518</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -7354,7 +7354,7 @@
         <v>46238.48778834491</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -7407,7 +7407,7 @@
         <v>46238.48778460648</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7460,7 +7460,7 @@
         <v>46238.48779039352</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -7513,7 +7513,7 @@
         <v>46238.4877950463</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7566,7 +7566,7 @@
         <v>46238.48779283564</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7619,7 +7619,7 @@
         <v>46238.487791493055</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7672,7 +7672,7 @@
         <v>46238.48778605324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7725,7 +7725,7 @@
         <v>46238.48778420139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7778,7 +7778,7 @@
         <v>46238.48779195602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7831,7 +7831,7 @@
         <v>46238.487793657405</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7884,7 +7884,7 @@
         <v>46238.48779326389</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7937,7 +7937,7 @@
         <v>46238.48778962963</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7990,7 +7990,7 @@
         <v>46238.48778335648</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -8043,7 +8043,7 @@
         <v>46238.48778688657</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -8096,7 +8096,7 @@
         <v>46238.487783749995</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -8149,7 +8149,7 @@
         <v>46238.48779547453</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -8202,7 +8202,7 @@
         <v>46238.48778292824</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -8255,7 +8255,7 @@
         <v>46238.487793900465</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8308,7 +8308,7 @@
         <v>46238.48778729167</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -8367,10 +8367,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I106" s="5">
         <v>46281</v>
@@ -8409,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -8424,16 +8424,16 @@
         <v>46238.48777921296</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I107" s="9">
         <v>46281</v>
@@ -8477,16 +8477,16 @@
         <v>46238.487780752315</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I108" s="5">
         <v>46281</v>
@@ -8530,16 +8530,16 @@
         <v>46238.4877812037</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I109" s="9">
         <v>46281</v>
@@ -8583,16 +8583,16 @@
         <v>46231.66672795139</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I110" s="5">
         <v>46281</v>
@@ -8613,7 +8613,7 @@
         <v>251</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>259</v>
@@ -8636,16 +8636,16 @@
         <v>46238.487785000005</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I111" s="9">
         <v>46281</v>
@@ -8689,16 +8689,16 @@
         <v>46231.66672108797</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I112" s="5">
         <v>46281</v>
@@ -8742,16 +8742,16 @@
         <v>46238.48779480324</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I113" s="9">
         <v>46281</v>
@@ -8795,16 +8795,16 @@
         <v>46231.66671467593</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I114" s="5">
         <v>46281</v>
@@ -8825,7 +8825,7 @@
         <v>251</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>259</v>
@@ -8848,16 +8848,16 @@
         <v>46231.66671130787</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I115" s="9">
         <v>46281</v>
@@ -8901,16 +8901,16 @@
         <v>46238.487792395834</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I116" s="5">
         <v>46281</v>
@@ -8954,16 +8954,16 @@
         <v>46238.487790949075</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I117" s="9">
         <v>46281</v>
@@ -9007,16 +9007,16 @@
         <v>46231.66670135417</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I118" s="5">
         <v>46281</v>
@@ -9037,7 +9037,7 @@
         <v>251</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>259</v>
@@ -9060,16 +9060,16 @@
         <v>46238.48779597222</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I119" s="9">
         <v>46281</v>
@@ -9113,16 +9113,16 @@
         <v>46231.66669519676</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I120" s="5">
         <v>46281</v>
@@ -9143,7 +9143,7 @@
         <v>251</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>259</v>
@@ -9166,16 +9166,16 @@
         <v>46231.66669142361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I121" s="9">
         <v>46281</v>
@@ -9196,7 +9196,7 @@
         <v>251</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>259</v>
@@ -9219,16 +9219,16 @@
         <v>46231.66668751158</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I122" s="5">
         <v>46281</v>
@@ -9249,7 +9249,7 @@
         <v>251</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>273</v>
@@ -9272,16 +9272,16 @@
         <v>46231.66668429398</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I123" s="9">
         <v>46281</v>
@@ -9302,7 +9302,7 @@
         <v>251</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>273</v>
@@ -9325,16 +9325,16 @@
         <v>46231.66667890047</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I124" s="5">
         <v>46281</v>
@@ -9355,7 +9355,7 @@
         <v>251</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>273</v>
@@ -9378,16 +9378,16 @@
         <v>46231.66666850694</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I125" s="9">
         <v>46281</v>
@@ -9408,7 +9408,7 @@
         <v>251</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>273</v>
@@ -9431,16 +9431,16 @@
         <v>46231.66667090278</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I126" s="5">
         <v>46281</v>
@@ -9461,7 +9461,7 @@
         <v>251</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>273</v>
@@ -9484,16 +9484,16 @@
         <v>46240.823163877314</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I127" s="9">
         <v>46281</v>
@@ -9537,16 +9537,16 @@
         <v>46240.82316032407</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I128" s="5">
         <v>46281</v>
@@ -9567,7 +9567,7 @@
         <v>251</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>273</v>
@@ -9590,16 +9590,16 @@
         <v>46240.8231571412</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I129" s="9">
         <v>46281</v>
@@ -9620,7 +9620,7 @@
         <v>251</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>273</v>
@@ -9643,16 +9643,16 @@
         <v>46240.823153680554</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I130" s="5">
         <v>46281</v>
@@ -9696,16 +9696,16 @@
         <v>46240.82315002315</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I131" s="9">
         <v>46281</v>
@@ -9844,7 +9844,7 @@
         <v>0</v>
       </c>
       <c r="U133" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="U134" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
@@ -9970,7 +9970,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -10080,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -10095,7 +10095,7 @@
         <v>46231.66768597222</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10125,7 +10125,7 @@
         <v>301</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>304</v>
@@ -10148,7 +10148,7 @@
         <v>46231.66769336806</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -10178,7 +10178,7 @@
         <v>301</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>306</v>
@@ -10201,7 +10201,7 @@
         <v>46231.667685312495</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10231,7 +10231,7 @@
         <v>301</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>308</v>
@@ -10254,7 +10254,7 @@
         <v>46231.66768938657</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10284,7 +10284,7 @@
         <v>301</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>310</v>
@@ -10307,7 +10307,7 @@
         <v>46231.667695219905</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10337,7 +10337,7 @@
         <v>301</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>301</v>
@@ -10360,7 +10360,7 @@
         <v>46231.6676892824</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10390,7 +10390,7 @@
         <v>301</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>301</v>
@@ -10413,7 +10413,7 @@
         <v>46231.667685821754</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10443,7 +10443,7 @@
         <v>301</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>301</v>
@@ -10466,7 +10466,7 @@
         <v>46231.66768554398</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10496,7 +10496,7 @@
         <v>301</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P145" s="10" t="s">
         <v>301</v>
@@ -10519,7 +10519,7 @@
         <v>46231.6676859838</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10549,7 +10549,7 @@
         <v>301</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>301</v>
@@ -10572,7 +10572,7 @@
         <v>46231.66768939815</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10602,7 +10602,7 @@
         <v>301</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P147" s="10" t="s">
         <v>301</v>
@@ -10625,7 +10625,7 @@
         <v>46231.667693055555</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10655,7 +10655,7 @@
         <v>301</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>301</v>
@@ -10678,7 +10678,7 @@
         <v>46231.66769350694</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10708,7 +10708,7 @@
         <v>301</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>301</v>
@@ -10731,7 +10731,7 @@
         <v>46231.66769018519</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10761,7 +10761,7 @@
         <v>301</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>301</v>
@@ -10784,7 +10784,7 @@
         <v>46231.66768600694</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10814,7 +10814,7 @@
         <v>301</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>301</v>
@@ -10837,7 +10837,7 @@
         <v>46231.66768511574</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10867,7 +10867,7 @@
         <v>301</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>301</v>
@@ -10890,7 +10890,7 @@
         <v>46231.66771173611</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10920,7 +10920,7 @@
         <v>301</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P153" s="10" t="s">
         <v>301</v>
@@ -10943,7 +10943,7 @@
         <v>46231.66768918981</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10973,7 +10973,7 @@
         <v>301</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>301</v>
@@ -10996,7 +10996,7 @@
         <v>46231.66768920139</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -11026,7 +11026,7 @@
         <v>301</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>301</v>
@@ -11049,7 +11049,7 @@
         <v>46231.66768591435</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -11079,7 +11079,7 @@
         <v>301</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>301</v>
@@ -11102,7 +11102,7 @@
         <v>46231.66768583334</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -11132,7 +11132,7 @@
         <v>301</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>301</v>
@@ -11155,7 +11155,7 @@
         <v>46231.66768583334</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11185,7 +11185,7 @@
         <v>301</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>301</v>
@@ -11208,7 +11208,7 @@
         <v>46231.66768945602</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -11238,7 +11238,7 @@
         <v>301</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>301</v>
@@ -11261,7 +11261,7 @@
         <v>46231.66768604166</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11291,7 +11291,7 @@
         <v>301</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>301</v>
@@ -11314,7 +11314,7 @@
         <v>46231.66768939815</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11344,7 +11344,7 @@
         <v>301</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>301</v>
@@ -11367,7 +11367,7 @@
         <v>46231.66769310185</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11397,7 +11397,7 @@
         <v>301</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>301</v>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="U163" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -11483,7 +11483,7 @@
         <v>46238.48777972222</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11536,7 +11536,7 @@
         <v>46238.487781620366</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11589,7 +11589,7 @@
         <v>46238.487778553244</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11642,7 +11642,7 @@
         <v>46231.667831597224</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11695,7 +11695,7 @@
         <v>46231.667839699076</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11748,7 +11748,7 @@
         <v>46231.667835925924</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11801,7 +11801,7 @@
         <v>46231.667833680556</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11854,7 +11854,7 @@
         <v>46231.667830844905</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11907,7 +11907,7 @@
         <v>46231.66784657407</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11960,7 +11960,7 @@
         <v>46231.66782869213</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -12013,7 +12013,7 @@
         <v>46231.667833217594</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -12066,7 +12066,7 @@
         <v>46231.66783061343</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -12119,7 +12119,7 @@
         <v>46231.66784224537</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -12172,7 +12172,7 @@
         <v>46231.66783100694</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -12225,7 +12225,7 @@
         <v>46231.667828958336</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -12278,7 +12278,7 @@
         <v>46231.66783663194</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -12331,7 +12331,7 @@
         <v>46231.66783365741</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12384,7 +12384,7 @@
         <v>46231.66783075231</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12437,7 +12437,7 @@
         <v>46231.66782876157</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12490,7 +12490,7 @@
         <v>46231.66783196759</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12543,7 +12543,7 @@
         <v>46231.66783085648</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12596,7 +12596,7 @@
         <v>46231.6678306713</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12649,7 +12649,7 @@
         <v>46231.66784248843</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12702,7 +12702,7 @@
         <v>46231.667834085645</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12755,7 +12755,7 @@
         <v>46231.6678331713</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12856,7 +12856,7 @@
         <v>0</v>
       </c>
       <c r="U189" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
@@ -12871,7 +12871,7 @@
         <v>46231.66826131944</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12924,7 +12924,7 @@
         <v>46231.667989050926</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12977,7 +12977,7 @@
         <v>46231.6679641088</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -13030,7 +13030,7 @@
         <v>46231.66796936342</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -13083,7 +13083,7 @@
         <v>46231.66796449074</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -13136,7 +13136,7 @@
         <v>46231.66796210648</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -13189,7 +13189,7 @@
         <v>46231.66797386574</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -13242,7 +13242,7 @@
         <v>46231.66796228009</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -13295,7 +13295,7 @@
         <v>46231.66796244213</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -13348,7 +13348,7 @@
         <v>46231.66801194444</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -13401,7 +13401,7 @@
         <v>46231.668014675924</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13454,7 +13454,7 @@
         <v>46231.66801396991</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13507,7 +13507,7 @@
         <v>46231.66801421296</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13560,7 +13560,7 @@
         <v>46231.668014097224</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13613,7 +13613,7 @@
         <v>46231.66801686343</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13666,7 +13666,7 @@
         <v>46231.66801703704</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13719,7 +13719,7 @@
         <v>46231.668013946764</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13772,7 +13772,7 @@
         <v>46231.66801465278</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13825,7 +13825,7 @@
         <v>46231.66801458334</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13878,7 +13878,7 @@
         <v>46231.66796421296</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13931,7 +13931,7 @@
         <v>46231.6679640625</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13984,7 +13984,7 @@
         <v>46231.66796466435</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -14037,7 +14037,7 @@
         <v>46231.66796478009</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -14090,7 +14090,7 @@
         <v>46231.66796820602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -14143,7 +14143,7 @@
         <v>46231.667986134256</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -14244,7 +14244,7 @@
         <v>0</v>
       </c>
       <c r="U215" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
@@ -14259,7 +14259,7 @@
         <v>46231.66839868056</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -14312,7 +14312,7 @@
         <v>46238.48778229167</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -14365,7 +14365,7 @@
         <v>46231.668395995366</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -14418,7 +14418,7 @@
         <v>46231.66839239583</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14471,7 +14471,7 @@
         <v>46231.668395671295</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14524,7 +14524,7 @@
         <v>46231.66839586805</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14577,7 +14577,7 @@
         <v>46231.66839528935</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14630,7 +14630,7 @@
         <v>46231.66839170139</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
@@ -14683,7 +14683,7 @@
         <v>46231.66839528935</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
@@ -14736,7 +14736,7 @@
         <v>46231.66839199074</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
@@ -14789,7 +14789,7 @@
         <v>46231.668389108796</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
@@ -14842,7 +14842,7 @@
         <v>46231.668388935184</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
@@ -14895,7 +14895,7 @@
         <v>46231.66839212963</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
@@ -14948,7 +14948,7 @@
         <v>46231.66839202546</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
@@ -15001,7 +15001,7 @@
         <v>46231.66839535879</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
@@ -15054,7 +15054,7 @@
         <v>46231.66839859953</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
@@ -15107,7 +15107,7 @@
         <v>46231.668392141204</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -15160,7 +15160,7 @@
         <v>46231.66838898148</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
@@ -15213,7 +15213,7 @@
         <v>46231.66839825231</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
@@ -15266,7 +15266,7 @@
         <v>46231.668391851854</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
@@ -15319,7 +15319,7 @@
         <v>46231.668389583334</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
@@ -15372,7 +15372,7 @@
         <v>46231.668389074075</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15425,7 +15425,7 @@
         <v>46231.66838769676</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
@@ -15478,7 +15478,7 @@
         <v>46231.6683890162</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15531,7 +15531,7 @@
         <v>46231.66838675926</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="T241" s="10"/>
       <c r="U241" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
@@ -15641,7 +15641,7 @@
         <v>46231.66850771991</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
@@ -15694,7 +15694,7 @@
         <v>46231.66851130787</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
@@ -15747,7 +15747,7 @@
         <v>46231.66851420139</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
@@ -15800,7 +15800,7 @@
         <v>46231.66851157407</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
@@ -15853,7 +15853,7 @@
         <v>46231.66850605324</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
@@ -15906,7 +15906,7 @@
         <v>46231.66851423611</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>26</v>
@@ -15959,7 +15959,7 @@
         <v>46231.66850797454</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>26</v>
@@ -16012,7 +16012,7 @@
         <v>46231.66850921296</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
@@ -16065,7 +16065,7 @@
         <v>46231.668514537036</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F250" s="6" t="s">
         <v>26</v>
@@ -16118,7 +16118,7 @@
         <v>46231.66850494213</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F251" s="10" t="s">
         <v>26</v>
@@ -16171,7 +16171,7 @@
         <v>46231.6685083912</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F252" s="6" t="s">
         <v>26</v>
@@ -16224,7 +16224,7 @@
         <v>46231.66850829861</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F253" s="10" t="s">
         <v>26</v>
@@ -16277,7 +16277,7 @@
         <v>46231.668502939814</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F254" s="6" t="s">
         <v>26</v>
@@ -16330,7 +16330,7 @@
         <v>46231.66851447917</v>
       </c>
       <c r="E255" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F255" s="10" t="s">
         <v>26</v>
@@ -16383,7 +16383,7 @@
         <v>46231.668505520836</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>26</v>
@@ -16436,7 +16436,7 @@
         <v>46231.66850818287</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>26</v>
@@ -16489,7 +16489,7 @@
         <v>46231.66851451389</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>26</v>
@@ -16542,7 +16542,7 @@
         <v>46231.6685082176</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F259" s="10" t="s">
         <v>26</v>
@@ -16595,7 +16595,7 @@
         <v>46231.66850509259</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>26</v>
@@ -16648,7 +16648,7 @@
         <v>46231.66851416667</v>
       </c>
       <c r="E261" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F261" s="10" t="s">
         <v>26</v>
@@ -16701,7 +16701,7 @@
         <v>46231.66851125</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F262" s="6" t="s">
         <v>26</v>
@@ -16754,7 +16754,7 @@
         <v>46231.66851166666</v>
       </c>
       <c r="E263" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F263" s="10" t="s">
         <v>26</v>
@@ -16807,7 +16807,7 @@
         <v>46231.668511192125</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F264" s="6" t="s">
         <v>26</v>
@@ -16860,7 +16860,7 @@
         <v>46231.66850479167</v>
       </c>
       <c r="E265" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F265" s="10" t="s">
         <v>26</v>
@@ -16913,7 +16913,7 @@
         <v>46231.66851174769</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>26</v>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="T267" s="10"/>
       <c r="U267" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
@@ -17023,7 +17023,7 @@
         <v>46231.6686428588</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>26</v>
@@ -17076,7 +17076,7 @@
         <v>46231.668646087965</v>
       </c>
       <c r="E269" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F269" s="10" t="s">
         <v>26</v>
@@ -17129,7 +17129,7 @@
         <v>46231.66864605324</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>26</v>
@@ -17182,7 +17182,7 @@
         <v>46231.66864655093</v>
       </c>
       <c r="E271" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F271" s="10" t="s">
         <v>26</v>
@@ -17235,7 +17235,7 @@
         <v>46231.668646261576</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>26</v>
@@ -17288,7 +17288,7 @@
         <v>46231.668647604165</v>
       </c>
       <c r="E273" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F273" s="10" t="s">
         <v>26</v>
@@ -17341,7 +17341,7 @@
         <v>46231.66865532407</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>26</v>
@@ -17394,7 +17394,7 @@
         <v>46231.66864230324</v>
       </c>
       <c r="E275" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F275" s="10" t="s">
         <v>26</v>
@@ -17447,7 +17447,7 @@
         <v>46231.66865127315</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F276" s="6" t="s">
         <v>26</v>
@@ -17500,7 +17500,7 @@
         <v>46231.66864081018</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F277" s="10" t="s">
         <v>26</v>
@@ -17553,7 +17553,7 @@
         <v>46231.668640868054</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F278" s="6" t="s">
         <v>26</v>
@@ -17606,7 +17606,7 @@
         <v>46231.66864261574</v>
       </c>
       <c r="E279" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F279" s="10" t="s">
         <v>26</v>
@@ -17659,7 +17659,7 @@
         <v>46231.668640648146</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F280" s="6" t="s">
         <v>26</v>
@@ -17712,7 +17712,7 @@
         <v>46231.668646122685</v>
       </c>
       <c r="E281" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F281" s="10" t="s">
         <v>26</v>
@@ -17765,7 +17765,7 @@
         <v>46231.66864037037</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F282" s="6" t="s">
         <v>26</v>
@@ -17818,7 +17818,7 @@
         <v>46231.66863724537</v>
       </c>
       <c r="E283" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F283" s="10" t="s">
         <v>26</v>
@@ -17871,7 +17871,7 @@
         <v>46231.66864261574</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
@@ -17924,7 +17924,7 @@
         <v>46231.66864297454</v>
       </c>
       <c r="E285" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F285" s="10" t="s">
         <v>26</v>
@@ -17977,7 +17977,7 @@
         <v>46231.66863702546</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F286" s="6" t="s">
         <v>26</v>
@@ -18030,7 +18030,7 @@
         <v>46231.66864275463</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F287" s="10" t="s">
         <v>26</v>
@@ -18083,7 +18083,7 @@
         <v>46231.66864267361</v>
       </c>
       <c r="E288" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F288" s="6" t="s">
         <v>26</v>
@@ -18136,7 +18136,7 @@
         <v>46231.66863684027</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F289" s="10" t="s">
         <v>26</v>
@@ -18189,7 +18189,7 @@
         <v>46231.66864052083</v>
       </c>
       <c r="E290" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F290" s="6" t="s">
         <v>26</v>
@@ -18242,7 +18242,7 @@
         <v>46231.66864081018</v>
       </c>
       <c r="E291" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F291" s="10" t="s">
         <v>26</v>
@@ -18295,7 +18295,7 @@
         <v>46231.668645937505</v>
       </c>
       <c r="E292" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F292" s="6" t="s">
         <v>26</v>
@@ -18390,7 +18390,7 @@
       </c>
       <c r="T293" s="10"/>
       <c r="U293" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="294" spans="1:21" x14ac:dyDescent="0.25">
@@ -18405,7 +18405,7 @@
         <v>46231.66880484954</v>
       </c>
       <c r="E294" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F294" s="6" t="s">
         <v>26</v>
@@ -18458,7 +18458,7 @@
         <v>46231.66880197916</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>26</v>
@@ -18511,7 +18511,7 @@
         <v>46231.66881472222</v>
       </c>
       <c r="E296" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F296" s="6" t="s">
         <v>26</v>
@@ -18564,7 +18564,7 @@
         <v>46231.66881128472</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F297" s="10" t="s">
         <v>26</v>
@@ -18617,7 +18617,7 @@
         <v>46231.66880478009</v>
       </c>
       <c r="E298" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F298" s="6" t="s">
         <v>26</v>
@@ -18670,7 +18670,7 @@
         <v>46231.668812268515</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F299" s="10" t="s">
         <v>26</v>
@@ -18723,7 +18723,7 @@
         <v>46231.66880841435</v>
       </c>
       <c r="E300" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F300" s="6" t="s">
         <v>26</v>
@@ -18776,7 +18776,7 @@
         <v>46231.66880237269</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F301" s="10" t="s">
         <v>26</v>
@@ -18829,7 +18829,7 @@
         <v>46231.66881479167</v>
       </c>
       <c r="E302" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F302" s="6" t="s">
         <v>26</v>
@@ -18882,7 +18882,7 @@
         <v>46231.66880479167</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F303" s="10" t="s">
         <v>26</v>
@@ -18935,7 +18935,7 @@
         <v>46231.66880506944</v>
       </c>
       <c r="E304" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F304" s="6" t="s">
         <v>26</v>
@@ -18988,7 +18988,7 @@
         <v>46231.668814432865</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F305" s="10" t="s">
         <v>26</v>
@@ -19041,7 +19041,7 @@
         <v>46231.66880857639</v>
       </c>
       <c r="E306" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F306" s="6" t="s">
         <v>26</v>
@@ -19094,7 +19094,7 @@
         <v>46231.66880244213</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>26</v>
@@ -19147,7 +19147,7 @@
         <v>46231.6688147338</v>
       </c>
       <c r="E308" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F308" s="6" t="s">
         <v>26</v>
@@ -19200,7 +19200,7 @@
         <v>46231.66880950231</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F309" s="10" t="s">
         <v>26</v>
@@ -19253,7 +19253,7 @@
         <v>46231.668803611115</v>
       </c>
       <c r="E310" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F310" s="6" t="s">
         <v>26</v>
@@ -19306,7 +19306,7 @@
         <v>46231.66881472222</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F311" s="10" t="s">
         <v>26</v>
@@ -19359,7 +19359,7 @@
         <v>46231.66880457176</v>
       </c>
       <c r="E312" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F312" s="6" t="s">
         <v>26</v>
@@ -19412,7 +19412,7 @@
         <v>46231.66881471065</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F313" s="10" t="s">
         <v>26</v>
@@ -19465,7 +19465,7 @@
         <v>46231.668809305556</v>
       </c>
       <c r="E314" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F314" s="6" t="s">
         <v>26</v>
@@ -19518,7 +19518,7 @@
         <v>46231.66880247685</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F315" s="10" t="s">
         <v>26</v>
@@ -19571,7 +19571,7 @@
         <v>46231.66881210648</v>
       </c>
       <c r="E316" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F316" s="6" t="s">
         <v>26</v>
@@ -19624,7 +19624,7 @@
         <v>46231.668805208334</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>26</v>
@@ -19677,7 +19677,7 @@
         <v>46231.668802141205</v>
       </c>
       <c r="E318" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F318" s="6" t="s">
         <v>26</v>
@@ -19825,7 +19825,7 @@
         <v>0</v>
       </c>
       <c r="U320" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="321" spans="1:21" x14ac:dyDescent="0.25">
@@ -19840,7 +19840,7 @@
         <v>46231.66971627314</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F321" s="10" t="s">
         <v>26</v>
@@ -19893,7 +19893,7 @@
         <v>46231.66971195602</v>
       </c>
       <c r="E322" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F322" s="6" t="s">
         <v>26</v>
@@ -19946,7 +19946,7 @@
         <v>46231.66970780093</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F323" s="10" t="s">
         <v>26</v>
@@ -19999,7 +19999,7 @@
         <v>46231.669704722226</v>
       </c>
       <c r="E324" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F324" s="6" t="s">
         <v>26</v>
@@ -20052,7 +20052,7 @@
         <v>46231.6697007176</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F325" s="10" t="s">
         <v>26</v>
@@ -20105,7 +20105,7 @@
         <v>46231.66969769676</v>
       </c>
       <c r="E326" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F326" s="6" t="s">
         <v>26</v>
@@ -20158,7 +20158,7 @@
         <v>46231.66969472222</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>26</v>
@@ -20211,7 +20211,7 @@
         <v>46231.669691689814</v>
       </c>
       <c r="E328" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F328" s="6" t="s">
         <v>26</v>
@@ -20264,7 +20264,7 @@
         <v>46231.66968831018</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F329" s="10" t="s">
         <v>26</v>
@@ -20317,7 +20317,7 @@
         <v>46231.66968530093</v>
       </c>
       <c r="E330" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F330" s="6" t="s">
         <v>26</v>
@@ -20370,7 +20370,7 @@
         <v>46231.66968244213</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F331" s="10" t="s">
         <v>26</v>
@@ -20423,7 +20423,7 @@
         <v>46231.669678935184</v>
       </c>
       <c r="E332" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F332" s="6" t="s">
         <v>26</v>
@@ -20476,7 +20476,7 @@
         <v>46231.669675763886</v>
       </c>
       <c r="E333" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F333" s="10" t="s">
         <v>26</v>
@@ -20529,7 +20529,7 @@
         <v>46231.669672777774</v>
       </c>
       <c r="E334" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F334" s="6" t="s">
         <v>26</v>
@@ -20582,7 +20582,7 @@
         <v>46231.66966976852</v>
       </c>
       <c r="E335" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F335" s="10" t="s">
         <v>26</v>
@@ -20635,7 +20635,7 @@
         <v>46231.66966627315</v>
       </c>
       <c r="E336" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F336" s="6" t="s">
         <v>26</v>
@@ -20688,7 +20688,7 @@
         <v>46231.66966341435</v>
       </c>
       <c r="E337" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F337" s="10" t="s">
         <v>26</v>
@@ -20741,7 +20741,7 @@
         <v>46231.669660671294</v>
       </c>
       <c r="E338" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F338" s="6" t="s">
         <v>26</v>
@@ -20794,7 +20794,7 @@
         <v>46231.66965815972</v>
       </c>
       <c r="E339" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F339" s="10" t="s">
         <v>26</v>
@@ -20847,7 +20847,7 @@
         <v>46231.669653634264</v>
       </c>
       <c r="E340" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F340" s="6" t="s">
         <v>26</v>
@@ -20900,7 +20900,7 @@
         <v>46231.669650173615</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F341" s="10" t="s">
         <v>26</v>
@@ -20953,7 +20953,7 @@
         <v>46231.66964695602</v>
       </c>
       <c r="E342" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F342" s="6" t="s">
         <v>26</v>
@@ -21006,7 +21006,7 @@
         <v>46231.669632986115</v>
       </c>
       <c r="E343" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F343" s="10" t="s">
         <v>26</v>
@@ -21059,7 +21059,7 @@
         <v>46231.66963234954</v>
       </c>
       <c r="E344" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F344" s="6" t="s">
         <v>26</v>
@@ -21112,7 +21112,7 @@
         <v>46231.66963550926</v>
       </c>
       <c r="E345" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F345" s="10" t="s">
         <v>26</v>
@@ -21213,7 +21213,7 @@
         <v>0</v>
       </c>
       <c r="U346" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.25">
@@ -21228,7 +21228,7 @@
         <v>46231.670200057866</v>
       </c>
       <c r="E347" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F347" s="10" t="s">
         <v>26</v>
@@ -21258,7 +21258,7 @@
         <v>555</v>
       </c>
       <c r="O347" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P347" s="10" t="s">
         <v>555</v>
@@ -21281,7 +21281,7 @@
         <v>46231.66998844907</v>
       </c>
       <c r="E348" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F348" s="6" t="s">
         <v>26</v>
@@ -21311,7 +21311,7 @@
         <v>555</v>
       </c>
       <c r="O348" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P348" s="6" t="s">
         <v>559</v>
@@ -21334,7 +21334,7 @@
         <v>46231.66998445602</v>
       </c>
       <c r="E349" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F349" s="10" t="s">
         <v>26</v>
@@ -21364,7 +21364,7 @@
         <v>555</v>
       </c>
       <c r="O349" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P349" s="10" t="s">
         <v>561</v>
@@ -21387,7 +21387,7 @@
         <v>46231.669980046296</v>
       </c>
       <c r="E350" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F350" s="6" t="s">
         <v>26</v>
@@ -21417,7 +21417,7 @@
         <v>555</v>
       </c>
       <c r="O350" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P350" s="6" t="s">
         <v>561</v>
@@ -21440,7 +21440,7 @@
         <v>46231.66997524306</v>
       </c>
       <c r="E351" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F351" s="10" t="s">
         <v>26</v>
@@ -21470,7 +21470,7 @@
         <v>555</v>
       </c>
       <c r="O351" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P351" s="10" t="s">
         <v>561</v>
@@ -21493,7 +21493,7 @@
         <v>46231.66997137731</v>
       </c>
       <c r="E352" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F352" s="6" t="s">
         <v>26</v>
@@ -21523,7 +21523,7 @@
         <v>555</v>
       </c>
       <c r="O352" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P352" s="6" t="s">
         <v>561</v>
@@ -21546,7 +21546,7 @@
         <v>46231.66996653935</v>
       </c>
       <c r="E353" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F353" s="10" t="s">
         <v>26</v>
@@ -21576,7 +21576,7 @@
         <v>555</v>
       </c>
       <c r="O353" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P353" s="10" t="s">
         <v>561</v>
@@ -21599,7 +21599,7 @@
         <v>46231.669961064814</v>
       </c>
       <c r="E354" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F354" s="6" t="s">
         <v>26</v>
@@ -21629,7 +21629,7 @@
         <v>555</v>
       </c>
       <c r="O354" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P354" s="6" t="s">
         <v>561</v>
@@ -21652,7 +21652,7 @@
         <v>46231.66995664352</v>
       </c>
       <c r="E355" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F355" s="10" t="s">
         <v>26</v>
@@ -21682,7 +21682,7 @@
         <v>555</v>
       </c>
       <c r="O355" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P355" s="10" t="s">
         <v>559</v>
@@ -21705,7 +21705,7 @@
         <v>46231.669952916665</v>
       </c>
       <c r="E356" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F356" s="6" t="s">
         <v>26</v>
@@ -21735,7 +21735,7 @@
         <v>555</v>
       </c>
       <c r="O356" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P356" s="6" t="s">
         <v>561</v>
@@ -21758,7 +21758,7 @@
         <v>46231.66994847222</v>
       </c>
       <c r="E357" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F357" s="10" t="s">
         <v>26</v>
@@ -21788,7 +21788,7 @@
         <v>555</v>
       </c>
       <c r="O357" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P357" s="10" t="s">
         <v>561</v>
@@ -21811,7 +21811,7 @@
         <v>46231.66994402777</v>
       </c>
       <c r="E358" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F358" s="6" t="s">
         <v>26</v>
@@ -21841,7 +21841,7 @@
         <v>555</v>
       </c>
       <c r="O358" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P358" s="6" t="s">
         <v>559</v>
@@ -21864,7 +21864,7 @@
         <v>46231.66994043981</v>
       </c>
       <c r="E359" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F359" s="10" t="s">
         <v>26</v>
@@ -21894,7 +21894,7 @@
         <v>555</v>
       </c>
       <c r="O359" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P359" s="10" t="s">
         <v>559</v>
@@ -21917,7 +21917,7 @@
         <v>46231.66993686343</v>
       </c>
       <c r="E360" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F360" s="6" t="s">
         <v>26</v>
@@ -21947,7 +21947,7 @@
         <v>555</v>
       </c>
       <c r="O360" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P360" s="6" t="s">
         <v>559</v>
@@ -21970,7 +21970,7 @@
         <v>46231.6699325</v>
       </c>
       <c r="E361" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F361" s="10" t="s">
         <v>26</v>
@@ -22000,7 +22000,7 @@
         <v>555</v>
       </c>
       <c r="O361" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P361" s="10" t="s">
         <v>559</v>
@@ -22023,7 +22023,7 @@
         <v>46231.66992857639</v>
       </c>
       <c r="E362" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F362" s="6" t="s">
         <v>26</v>
@@ -22053,7 +22053,7 @@
         <v>555</v>
       </c>
       <c r="O362" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P362" s="6" t="s">
         <v>575</v>
@@ -22076,7 +22076,7 @@
         <v>46231.66992512731</v>
       </c>
       <c r="E363" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F363" s="10" t="s">
         <v>26</v>
@@ -22106,7 +22106,7 @@
         <v>555</v>
       </c>
       <c r="O363" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P363" s="10" t="s">
         <v>575</v>
@@ -22129,7 +22129,7 @@
         <v>46231.669921064815</v>
       </c>
       <c r="E364" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F364" s="6" t="s">
         <v>26</v>
@@ -22159,7 +22159,7 @@
         <v>555</v>
       </c>
       <c r="O364" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P364" s="6" t="s">
         <v>578</v>
@@ -22182,7 +22182,7 @@
         <v>46231.6699174074</v>
       </c>
       <c r="E365" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F365" s="10" t="s">
         <v>26</v>
@@ -22212,7 +22212,7 @@
         <v>555</v>
       </c>
       <c r="O365" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P365" s="10" t="s">
         <v>578</v>
@@ -22235,7 +22235,7 @@
         <v>46231.66991390046</v>
       </c>
       <c r="E366" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F366" s="6" t="s">
         <v>26</v>
@@ -22265,7 +22265,7 @@
         <v>555</v>
       </c>
       <c r="O366" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P366" s="6" t="s">
         <v>578</v>
@@ -22288,7 +22288,7 @@
         <v>46231.66990978009</v>
       </c>
       <c r="E367" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F367" s="10" t="s">
         <v>26</v>
@@ -22318,7 +22318,7 @@
         <v>555</v>
       </c>
       <c r="O367" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P367" s="10" t="s">
         <v>578</v>
@@ -22341,7 +22341,7 @@
         <v>46231.66990606481</v>
       </c>
       <c r="E368" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F368" s="6" t="s">
         <v>26</v>
@@ -22371,7 +22371,7 @@
         <v>555</v>
       </c>
       <c r="O368" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P368" s="6" t="s">
         <v>578</v>
@@ -22394,7 +22394,7 @@
         <v>46231.66989173611</v>
       </c>
       <c r="E369" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F369" s="10" t="s">
         <v>26</v>
@@ -22424,7 +22424,7 @@
         <v>555</v>
       </c>
       <c r="O369" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P369" s="10" t="s">
         <v>575</v>
@@ -22447,7 +22447,7 @@
         <v>46231.66989118056</v>
       </c>
       <c r="E370" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F370" s="6" t="s">
         <v>26</v>
@@ -22477,7 +22477,7 @@
         <v>555</v>
       </c>
       <c r="O370" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P370" s="6" t="s">
         <v>575</v>
@@ -22500,7 +22500,7 @@
         <v>46231.669893796294</v>
       </c>
       <c r="E371" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F371" s="10" t="s">
         <v>26</v>
@@ -22530,7 +22530,7 @@
         <v>555</v>
       </c>
       <c r="O371" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P371" s="10" t="s">
         <v>578</v>
@@ -22601,7 +22601,7 @@
         <v>0</v>
       </c>
       <c r="U372" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="373" spans="1:21" x14ac:dyDescent="0.25">
@@ -22616,7 +22616,7 @@
         <v>46231.67078247685</v>
       </c>
       <c r="E373" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F373" s="10" t="s">
         <v>26</v>
@@ -22669,7 +22669,7 @@
         <v>46231.67077917824</v>
       </c>
       <c r="E374" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F374" s="6" t="s">
         <v>26</v>
@@ -22699,7 +22699,7 @@
         <v>587</v>
       </c>
       <c r="O374" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P374" s="6" t="s">
         <v>591</v>
@@ -22722,7 +22722,7 @@
         <v>46231.6707759375</v>
       </c>
       <c r="E375" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F375" s="10" t="s">
         <v>26</v>
@@ -22752,7 +22752,7 @@
         <v>587</v>
       </c>
       <c r="O375" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P375" s="10" t="s">
         <v>591</v>
@@ -22775,7 +22775,7 @@
         <v>46231.67077253472</v>
       </c>
       <c r="E376" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F376" s="6" t="s">
         <v>26</v>
@@ -22805,7 +22805,7 @@
         <v>587</v>
       </c>
       <c r="O376" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P376" s="6" t="s">
         <v>591</v>
@@ -22828,7 +22828,7 @@
         <v>46231.67076925926</v>
       </c>
       <c r="E377" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F377" s="10" t="s">
         <v>26</v>
@@ -22858,7 +22858,7 @@
         <v>587</v>
       </c>
       <c r="O377" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P377" s="10" t="s">
         <v>591</v>
@@ -22881,7 +22881,7 @@
         <v>46231.670765393515</v>
       </c>
       <c r="E378" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F378" s="6" t="s">
         <v>26</v>
@@ -22911,7 +22911,7 @@
         <v>587</v>
       </c>
       <c r="O378" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P378" s="6" t="s">
         <v>589</v>
@@ -22934,7 +22934,7 @@
         <v>46231.6707622338</v>
       </c>
       <c r="E379" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F379" s="10" t="s">
         <v>26</v>
@@ -22964,7 +22964,7 @@
         <v>587</v>
       </c>
       <c r="O379" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P379" s="10" t="s">
         <v>589</v>
@@ -22987,7 +22987,7 @@
         <v>46231.67075878472</v>
       </c>
       <c r="E380" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F380" s="6" t="s">
         <v>26</v>
@@ -23017,7 +23017,7 @@
         <v>587</v>
       </c>
       <c r="O380" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P380" s="6" t="s">
         <v>591</v>
@@ -23040,7 +23040,7 @@
         <v>46231.670755451385</v>
       </c>
       <c r="E381" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F381" s="10" t="s">
         <v>26</v>
@@ -23070,7 +23070,7 @@
         <v>587</v>
       </c>
       <c r="O381" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P381" s="10" t="s">
         <v>591</v>
@@ -23093,7 +23093,7 @@
         <v>46231.67075229167</v>
       </c>
       <c r="E382" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F382" s="6" t="s">
         <v>26</v>
@@ -23123,7 +23123,7 @@
         <v>587</v>
       </c>
       <c r="O382" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P382" s="6" t="s">
         <v>591</v>
@@ -23146,7 +23146,7 @@
         <v>46231.67074930556</v>
       </c>
       <c r="E383" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F383" s="10" t="s">
         <v>26</v>
@@ -23176,7 +23176,7 @@
         <v>587</v>
       </c>
       <c r="O383" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P383" s="10" t="s">
         <v>591</v>
@@ -23199,7 +23199,7 @@
         <v>46231.67074609954</v>
       </c>
       <c r="E384" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F384" s="6" t="s">
         <v>26</v>
@@ -23229,7 +23229,7 @@
         <v>587</v>
       </c>
       <c r="O384" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P384" s="6" t="s">
         <v>589</v>
@@ -23252,7 +23252,7 @@
         <v>46231.67074238426</v>
       </c>
       <c r="E385" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F385" s="10" t="s">
         <v>26</v>
@@ -23282,7 +23282,7 @@
         <v>587</v>
       </c>
       <c r="O385" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P385" s="10" t="s">
         <v>591</v>
@@ -23305,7 +23305,7 @@
         <v>46231.670739340276</v>
       </c>
       <c r="E386" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F386" s="6" t="s">
         <v>26</v>
@@ -23335,7 +23335,7 @@
         <v>587</v>
       </c>
       <c r="O386" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P386" s="6" t="s">
         <v>591</v>
@@ -23358,7 +23358,7 @@
         <v>46231.67073607639</v>
       </c>
       <c r="E387" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F387" s="10" t="s">
         <v>26</v>
@@ -23388,7 +23388,7 @@
         <v>587</v>
       </c>
       <c r="O387" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P387" s="10" t="s">
         <v>591</v>
@@ -23411,7 +23411,7 @@
         <v>46231.67073236111</v>
       </c>
       <c r="E388" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F388" s="6" t="s">
         <v>26</v>
@@ -23441,7 +23441,7 @@
         <v>587</v>
       </c>
       <c r="O388" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P388" s="6" t="s">
         <v>606</v>
@@ -23464,7 +23464,7 @@
         <v>46231.67072928241</v>
       </c>
       <c r="E389" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F389" s="10" t="s">
         <v>26</v>
@@ -23494,7 +23494,7 @@
         <v>587</v>
       </c>
       <c r="O389" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P389" s="10" t="s">
         <v>608</v>
@@ -23517,7 +23517,7 @@
         <v>46231.67072601852</v>
       </c>
       <c r="E390" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F390" s="6" t="s">
         <v>26</v>
@@ -23547,7 +23547,7 @@
         <v>587</v>
       </c>
       <c r="O390" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P390" s="6" t="s">
         <v>608</v>
@@ -23570,7 +23570,7 @@
         <v>46231.67072258102</v>
       </c>
       <c r="E391" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F391" s="10" t="s">
         <v>26</v>
@@ -23600,7 +23600,7 @@
         <v>587</v>
       </c>
       <c r="O391" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P391" s="10" t="s">
         <v>606</v>
@@ -23623,7 +23623,7 @@
         <v>46231.67071851852</v>
       </c>
       <c r="E392" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F392" s="6" t="s">
         <v>26</v>
@@ -23653,7 +23653,7 @@
         <v>587</v>
       </c>
       <c r="O392" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P392" s="6" t="s">
         <v>608</v>
@@ -23676,7 +23676,7 @@
         <v>46231.67071464121</v>
       </c>
       <c r="E393" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F393" s="10" t="s">
         <v>26</v>
@@ -23706,7 +23706,7 @@
         <v>587</v>
       </c>
       <c r="O393" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P393" s="10" t="s">
         <v>606</v>
@@ -23729,7 +23729,7 @@
         <v>46231.67071099537</v>
       </c>
       <c r="E394" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F394" s="6" t="s">
         <v>26</v>
@@ -23759,7 +23759,7 @@
         <v>587</v>
       </c>
       <c r="O394" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P394" s="6" t="s">
         <v>606</v>
@@ -23782,7 +23782,7 @@
         <v>46231.67070591435</v>
       </c>
       <c r="E395" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F395" s="10" t="s">
         <v>26</v>
@@ -23812,7 +23812,7 @@
         <v>587</v>
       </c>
       <c r="O395" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P395" s="10" t="s">
         <v>608</v>
@@ -23835,7 +23835,7 @@
         <v>46231.67069403935</v>
       </c>
       <c r="E396" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F396" s="6" t="s">
         <v>26</v>
@@ -23865,7 +23865,7 @@
         <v>587</v>
       </c>
       <c r="O396" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P396" s="6" t="s">
         <v>606</v>
@@ -23888,7 +23888,7 @@
         <v>46231.670696319445</v>
       </c>
       <c r="E397" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F397" s="10" t="s">
         <v>26</v>
@@ -23918,7 +23918,7 @@
         <v>587</v>
       </c>
       <c r="O397" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P397" s="10" t="s">
         <v>606</v>
@@ -23989,7 +23989,7 @@
         <v>0</v>
       </c>
       <c r="U398" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="399" spans="1:21" x14ac:dyDescent="0.25">
@@ -24004,7 +24004,7 @@
         <v>46231.67106579861</v>
       </c>
       <c r="E399" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F399" s="10" t="s">
         <v>26</v>
@@ -24034,7 +24034,7 @@
         <v>618</v>
       </c>
       <c r="O399" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P399" s="10" t="s">
         <v>621</v>
@@ -24057,7 +24057,7 @@
         <v>46231.671062407404</v>
       </c>
       <c r="E400" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F400" s="6" t="s">
         <v>26</v>
@@ -24087,7 +24087,7 @@
         <v>618</v>
       </c>
       <c r="O400" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P400" s="6" t="s">
         <v>623</v>
@@ -24110,7 +24110,7 @@
         <v>46231.67105903935</v>
       </c>
       <c r="E401" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F401" s="10" t="s">
         <v>26</v>
@@ -24140,7 +24140,7 @@
         <v>618</v>
       </c>
       <c r="O401" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P401" s="10" t="s">
         <v>625</v>
@@ -24163,7 +24163,7 @@
         <v>46231.67105518519</v>
       </c>
       <c r="E402" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F402" s="6" t="s">
         <v>26</v>
@@ -24193,7 +24193,7 @@
         <v>618</v>
       </c>
       <c r="O402" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P402" s="6" t="s">
         <v>618</v>
@@ -24216,7 +24216,7 @@
         <v>46231.671052025464</v>
       </c>
       <c r="E403" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F403" s="10" t="s">
         <v>26</v>
@@ -24246,7 +24246,7 @@
         <v>618</v>
       </c>
       <c r="O403" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P403" s="10" t="s">
         <v>618</v>
@@ -24269,7 +24269,7 @@
         <v>46231.67104925926</v>
       </c>
       <c r="E404" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F404" s="6" t="s">
         <v>26</v>
@@ -24299,7 +24299,7 @@
         <v>618</v>
       </c>
       <c r="O404" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P404" s="6" t="s">
         <v>618</v>
@@ -24322,7 +24322,7 @@
         <v>46231.67104619213</v>
       </c>
       <c r="E405" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F405" s="10" t="s">
         <v>26</v>
@@ -24352,7 +24352,7 @@
         <v>618</v>
       </c>
       <c r="O405" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P405" s="10" t="s">
         <v>618</v>
@@ -24375,7 +24375,7 @@
         <v>46231.67104260417</v>
       </c>
       <c r="E406" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F406" s="6" t="s">
         <v>26</v>
@@ -24405,7 +24405,7 @@
         <v>618</v>
       </c>
       <c r="O406" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P406" s="6" t="s">
         <v>618</v>
@@ -24428,7 +24428,7 @@
         <v>46231.67103974537</v>
       </c>
       <c r="E407" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F407" s="10" t="s">
         <v>26</v>
@@ -24458,7 +24458,7 @@
         <v>618</v>
       </c>
       <c r="O407" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P407" s="10" t="s">
         <v>618</v>
@@ -24481,7 +24481,7 @@
         <v>46231.67103653935</v>
       </c>
       <c r="E408" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F408" s="6" t="s">
         <v>26</v>
@@ -24511,7 +24511,7 @@
         <v>618</v>
       </c>
       <c r="O408" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P408" s="6" t="s">
         <v>618</v>
@@ -24534,7 +24534,7 @@
         <v>46231.671033182865</v>
       </c>
       <c r="E409" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F409" s="10" t="s">
         <v>26</v>
@@ -24564,7 +24564,7 @@
         <v>618</v>
       </c>
       <c r="O409" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P409" s="10" t="s">
         <v>618</v>
@@ -24587,7 +24587,7 @@
         <v>46231.67103011574</v>
       </c>
       <c r="E410" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F410" s="6" t="s">
         <v>26</v>
@@ -24617,7 +24617,7 @@
         <v>618</v>
       </c>
       <c r="O410" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P410" s="6" t="s">
         <v>618</v>
@@ -24640,7 +24640,7 @@
         <v>46231.67102701389</v>
       </c>
       <c r="E411" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F411" s="10" t="s">
         <v>26</v>
@@ -24670,7 +24670,7 @@
         <v>618</v>
       </c>
       <c r="O411" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P411" s="10" t="s">
         <v>618</v>
@@ -24693,7 +24693,7 @@
         <v>46231.671023993054</v>
       </c>
       <c r="E412" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F412" s="6" t="s">
         <v>26</v>
@@ -24723,7 +24723,7 @@
         <v>618</v>
       </c>
       <c r="O412" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P412" s="6" t="s">
         <v>618</v>
@@ -24746,7 +24746,7 @@
         <v>46231.67102047453</v>
       </c>
       <c r="E413" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F413" s="10" t="s">
         <v>26</v>
@@ -24776,7 +24776,7 @@
         <v>618</v>
       </c>
       <c r="O413" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P413" s="10" t="s">
         <v>618</v>
@@ -24799,7 +24799,7 @@
         <v>46231.67101741898</v>
       </c>
       <c r="E414" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F414" s="6" t="s">
         <v>26</v>
@@ -24829,7 +24829,7 @@
         <v>618</v>
       </c>
       <c r="O414" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P414" s="6" t="s">
         <v>618</v>
@@ -24852,7 +24852,7 @@
         <v>46231.671014259264</v>
       </c>
       <c r="E415" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F415" s="10" t="s">
         <v>26</v>
@@ -24882,7 +24882,7 @@
         <v>618</v>
       </c>
       <c r="O415" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P415" s="10" t="s">
         <v>618</v>
@@ -24905,7 +24905,7 @@
         <v>46231.671010289356</v>
       </c>
       <c r="E416" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F416" s="6" t="s">
         <v>26</v>
@@ -24935,7 +24935,7 @@
         <v>618</v>
       </c>
       <c r="O416" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P416" s="6" t="s">
         <v>618</v>
@@ -24958,7 +24958,7 @@
         <v>46231.67100728009</v>
       </c>
       <c r="E417" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F417" s="10" t="s">
         <v>26</v>
@@ -24988,7 +24988,7 @@
         <v>618</v>
       </c>
       <c r="O417" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P417" s="10" t="s">
         <v>618</v>
@@ -25011,7 +25011,7 @@
         <v>46231.67100423611</v>
       </c>
       <c r="E418" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F418" s="6" t="s">
         <v>26</v>
@@ -25041,7 +25041,7 @@
         <v>618</v>
       </c>
       <c r="O418" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P418" s="6" t="s">
         <v>618</v>
@@ -25064,7 +25064,7 @@
         <v>46231.6710006713</v>
       </c>
       <c r="E419" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F419" s="10" t="s">
         <v>26</v>
@@ -25094,7 +25094,7 @@
         <v>618</v>
       </c>
       <c r="O419" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P419" s="10" t="s">
         <v>618</v>
@@ -25117,7 +25117,7 @@
         <v>46231.67099731481</v>
       </c>
       <c r="E420" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F420" s="6" t="s">
         <v>26</v>
@@ -25147,7 +25147,7 @@
         <v>618</v>
       </c>
       <c r="O420" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P420" s="6" t="s">
         <v>618</v>
@@ -25170,7 +25170,7 @@
         <v>46231.67098568287</v>
       </c>
       <c r="E421" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F421" s="10" t="s">
         <v>26</v>
@@ -25200,7 +25200,7 @@
         <v>618</v>
       </c>
       <c r="O421" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P421" s="10" t="s">
         <v>618</v>
@@ -25223,7 +25223,7 @@
         <v>46231.670985115736</v>
       </c>
       <c r="E422" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F422" s="6" t="s">
         <v>26</v>
@@ -25253,7 +25253,7 @@
         <v>618</v>
       </c>
       <c r="O422" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P422" s="6" t="s">
         <v>618</v>
@@ -25276,7 +25276,7 @@
         <v>46231.67098739583</v>
       </c>
       <c r="E423" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F423" s="10" t="s">
         <v>26</v>
@@ -25306,7 +25306,7 @@
         <v>618</v>
       </c>
       <c r="O423" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P423" s="10" t="s">
         <v>618</v>
@@ -25424,7 +25424,7 @@
         <v>0</v>
       </c>
       <c r="U425" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="426" spans="1:21" x14ac:dyDescent="0.25">
@@ -25487,7 +25487,7 @@
         <v>0</v>
       </c>
       <c r="U426" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -4699,7 +4699,7 @@
         <v>46238.48761943287</v>
       </c>
       <c r="D39" s="9">
-        <v>46241.206588078705</v>
+        <v>46249.186783240744</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>142</v>
@@ -4743,8 +4743,8 @@
       <c r="R39" s="9">
         <v>46244</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>69</v>
+      <c r="S39" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -4874,7 +4874,7 @@
         <v>46238.487760937496</v>
       </c>
       <c r="D42" s="5">
-        <v>46244.205140300925</v>
+        <v>46252.19006140046</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>67</v>
@@ -4918,8 +4918,8 @@
       <c r="R42" s="5">
         <v>46251</v>
       </c>
-      <c r="S42" s="12" t="s">
-        <v>69</v>
+      <c r="S42" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46246.18983402778</v>
+        <v>46253.169885474534</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>65</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46246.18983418982</v>
+        <v>46253.16988677083</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46246.189833819444</v>
+        <v>46253.16988230324</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>75</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46246.189833854165</v>
+        <v>46253.16988435185</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -399,7 +399,7 @@
     <t xml:space="preserve">Generacion Oc OT 4382 - OT 4383 </t>
   </si>
   <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
   </si>
   <si>
     <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   ,Armado  OT 4382 - OT 4383 OT 4381 </t>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46237.55371688657</v>
+        <v>46254.6473084375</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>115</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -3794,7 +3794,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46231.664890995366</v>
+        <v>46255.170812743054</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>88</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46231.66497333333</v>
+        <v>46255.170814513884</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>72</v>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46231.66504327546</v>
+        <v>46255.170821168984</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>78</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -4313,7 +4313,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46254.6473084375</v>
+        <v>46255.62865383102</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>115</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46232.61812457176</v>
+        <v>46260.18368119213</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>188</v>
@@ -6526,8 +6526,8 @@
       <c r="R72" s="5">
         <v>46267</v>
       </c>
-      <c r="S72" s="7" t="s">
-        <v>32</v>
+      <c r="S72" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46232.618130312505</v>
+        <v>46260.18368162037</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>193</v>
@@ -6589,8 +6589,8 @@
       <c r="R73" s="9">
         <v>46267</v>
       </c>
-      <c r="S73" s="7" t="s">
-        <v>32</v>
+      <c r="S73" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46232.618130821764</v>
+        <v>46260.183681400464</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>196</v>
@@ -6652,8 +6652,8 @@
       <c r="R74" s="5">
         <v>46267</v>
       </c>
-      <c r="S74" s="7" t="s">
-        <v>32</v>
+      <c r="S74" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -258,436 +258,436 @@
     <t>Generación OC corte laser   OT 4382 - OT 4383 ,Propuesta compras:</t>
   </si>
   <si>
+    <t>1216950957012359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Corte plasma  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion OC Corte plasma   OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950828650074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa   OT 4381OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparacion materiales OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>1216950828650087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Mecanizado  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC mecanizado  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216916625315581</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte Laser  OT 4382 - OT 4383  1 </t>
+  </si>
+  <si>
+    <t>1216950739448511</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC corte laser   OT 4382 - OT 4383 ,Fabricacion corte laser  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1216950739448529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC corte laser   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte Laser  OT 4382 - OT 4383  1 ,Fabricacion corte laser  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216951179352081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion corte laser  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  ,Corte Laser  OT 4382 - OT 4383  1 </t>
+  </si>
+  <si>
+    <t>1216951179352102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion OC Corte plasma   OT 4382 - OT 4383  ,Fabricación corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950739466470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma   OT 4382 - OT 4383 ,Fabricación corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950739466488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma   OT 4382 - OT 4383 ,Corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950957054599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC mecanizado  OT 4382 - OT 4383 ,Fabricación Mecanizado  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950957054612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4382 - OT 4383  ,Fabricación Mecanizado  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950957064236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Mecanizado  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion mecanizado  OT 4382 - OT 4383  ,Mecanizado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950739515250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 ,Generacion Oc OT 4382 - OT 4383 ,Armado  OT 4382 - OT 4383 OT 4381 </t>
+  </si>
+  <si>
+    <t>1216950739515263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   ,Armado  OT 4382 - OT 4383 OT 4381 </t>
+  </si>
+  <si>
+    <t>1216950739515281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado  OT 4382 - OT 4383 OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 ,Fabricación externa   OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>1216950739385453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216950739385471</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check pruebas FAT  OT 4382 - OT 4383   ,Plano Preliminar  OT 4382 - OT 4383  ,Check Planos  OT 4382 - OT 4383 ,Plano Definitivos  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950828707841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Preliminar  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216916670896948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216916670896949</t>
+  </si>
+  <si>
+    <t>ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216950828707864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>Plano Preliminar  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216916670896950</t>
+  </si>
+  <si>
+    <t>1216916670896951</t>
+  </si>
+  <si>
+    <t>1216951179437504</t>
+  </si>
+  <si>
+    <t>Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Propuesta Fabricación externa   OT 4381OT 4382 - OT 4383   ,Propuesta Mecanizado  OT 4382 - OT 4383 ,Propuesta Corte plasma  OT 4382 - OT 4383 ,propuesta Corte laser  OT 4382 - OT 4383 ,Ingenieria y diseño:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216916670896952</t>
+  </si>
+  <si>
+    <t>1216916670896953</t>
+  </si>
+  <si>
+    <t>1216950828716752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check pruebas FAT  OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseño:,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950739592745</t>
+  </si>
+  <si>
+    <t>1216950739592758</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales,Check pruebas FAT  OT 4382 - OT 4383   ,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1216950739611887</t>
+  </si>
+  <si>
+    <t>1216950807684439</t>
+  </si>
+  <si>
+    <t>1216916670896954</t>
+  </si>
+  <si>
+    <t>1216916670896955</t>
+  </si>
+  <si>
+    <t>1216916670896956</t>
+  </si>
+  <si>
+    <t>1216916670896957</t>
+  </si>
+  <si>
+    <t>1216916670896958</t>
+  </si>
+  <si>
+    <t>1216916670896959</t>
+  </si>
+  <si>
+    <t>1216916670896960</t>
+  </si>
+  <si>
+    <t>1216916670896961</t>
+  </si>
+  <si>
+    <t>1216916670896962</t>
+  </si>
+  <si>
+    <t>1216916670896963</t>
+  </si>
+  <si>
+    <t>1216916670896964</t>
+  </si>
+  <si>
+    <t>1216916670896965</t>
+  </si>
+  <si>
+    <t>1216916670896966</t>
+  </si>
+  <si>
+    <t>1216916670896967</t>
+  </si>
+  <si>
+    <t>1216916670896968</t>
+  </si>
+  <si>
+    <t>1216916670896969</t>
+  </si>
+  <si>
+    <t>1216916670896972</t>
+  </si>
+  <si>
+    <t>1216916670896973</t>
+  </si>
+  <si>
+    <t>1216916670896974</t>
+  </si>
+  <si>
+    <t>1216916670896970</t>
+  </si>
+  <si>
+    <t>1216916670896971</t>
+  </si>
+  <si>
+    <t>1216950807684452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  ,Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Mecanizado  OT 4382 - OT 4383 ,Recepcion corte plasma   OT 4382 - OT 4383 ,Recepcion mecanizado  OT 4382 - OT 4383  ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950739647056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad corte Laser OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950739647079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950828741855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion mecanizado  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad Mecanizado  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950739657964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte Laser OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950739657987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216951179504781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950807714118</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado OT 4382 - OT 4383  ,Preparacion materiales OT 4382 - OT 4383   ,Armado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950807714130</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Caldereria,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216950957012359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Corte plasma  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion OC Corte plasma   OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950828650074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa   OT 4381OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparacion materiales OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>1216950828650087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Mecanizado  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC mecanizado  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216916625315581</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte Laser  OT 4382 - OT 4383  1 </t>
-  </si>
-  <si>
-    <t>1216950739448511</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC corte laser   OT 4382 - OT 4383 ,Fabricacion corte laser  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1216950739448529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC corte laser   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte Laser  OT 4382 - OT 4383  1 ,Fabricacion corte laser  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216951179352081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion corte laser  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  ,Corte Laser  OT 4382 - OT 4383  1 </t>
-  </si>
-  <si>
-    <t>1216951179352102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion OC Corte plasma   OT 4382 - OT 4383  ,Fabricación corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950739466470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma   OT 4382 - OT 4383 ,Fabricación corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950739466488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma   OT 4382 - OT 4383 ,Corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950957054599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC mecanizado  OT 4382 - OT 4383 ,Fabricación Mecanizado  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950957054612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4382 - OT 4383  ,Fabricación Mecanizado  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950957064236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Mecanizado  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion mecanizado  OT 4382 - OT 4383  ,Mecanizado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950739515250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 ,Generacion Oc OT 4382 - OT 4383 ,Armado  OT 4382 - OT 4383 OT 4381 </t>
-  </si>
-  <si>
-    <t>1216950739515263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   ,Armado  OT 4382 - OT 4383 OT 4381 </t>
-  </si>
-  <si>
-    <t>1216950739515281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado  OT 4382 - OT 4383 OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 ,Fabricación externa   OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>1216950739385453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216950739385471</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check pruebas FAT  OT 4382 - OT 4383   ,Plano Preliminar  OT 4382 - OT 4383  ,Check Planos  OT 4382 - OT 4383 ,Plano Definitivos  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950828707841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Preliminar  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216916670896948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216916670896949</t>
-  </si>
-  <si>
-    <t>ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216950828707864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>Plano Preliminar  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216916670896950</t>
-  </si>
-  <si>
-    <t>1216916670896951</t>
-  </si>
-  <si>
-    <t>1216951179437504</t>
-  </si>
-  <si>
-    <t>Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Propuesta Fabricación externa   OT 4381OT 4382 - OT 4383   ,Propuesta Mecanizado  OT 4382 - OT 4383 ,Propuesta Corte plasma  OT 4382 - OT 4383 ,propuesta Corte laser  OT 4382 - OT 4383 ,Ingenieria y diseño:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216916670896952</t>
-  </si>
-  <si>
-    <t>1216916670896953</t>
-  </si>
-  <si>
-    <t>1216950828716752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check pruebas FAT  OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseño:,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950739592745</t>
-  </si>
-  <si>
-    <t>1216950739592758</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales,Check pruebas FAT  OT 4382 - OT 4383   ,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1216950739611887</t>
-  </si>
-  <si>
-    <t>1216950807684439</t>
-  </si>
-  <si>
-    <t>1216916670896954</t>
-  </si>
-  <si>
-    <t>1216916670896955</t>
-  </si>
-  <si>
-    <t>1216916670896956</t>
-  </si>
-  <si>
-    <t>1216916670896957</t>
-  </si>
-  <si>
-    <t>1216916670896958</t>
-  </si>
-  <si>
-    <t>1216916670896959</t>
-  </si>
-  <si>
-    <t>1216916670896960</t>
-  </si>
-  <si>
-    <t>1216916670896961</t>
-  </si>
-  <si>
-    <t>1216916670896962</t>
-  </si>
-  <si>
-    <t>1216916670896963</t>
-  </si>
-  <si>
-    <t>1216916670896964</t>
-  </si>
-  <si>
-    <t>1216916670896965</t>
-  </si>
-  <si>
-    <t>1216916670896966</t>
-  </si>
-  <si>
-    <t>1216916670896967</t>
-  </si>
-  <si>
-    <t>1216916670896968</t>
-  </si>
-  <si>
-    <t>1216916670896969</t>
-  </si>
-  <si>
-    <t>1216916670896972</t>
-  </si>
-  <si>
-    <t>1216916670896973</t>
-  </si>
-  <si>
-    <t>1216916670896974</t>
-  </si>
-  <si>
-    <t>1216916670896970</t>
-  </si>
-  <si>
-    <t>1216916670896971</t>
-  </si>
-  <si>
-    <t>1216950807684452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  ,Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Mecanizado  OT 4382 - OT 4383 ,Recepcion corte plasma   OT 4382 - OT 4383 ,Recepcion mecanizado  OT 4382 - OT 4383  ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950739647056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad corte Laser OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950739647079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950828741855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion mecanizado  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad Mecanizado  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950739657964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte Laser OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950739657987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216951179504781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950807714118</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado OT 4382 - OT 4383  ,Preparacion materiales OT 4382 - OT 4383   ,Armado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950807714130</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Caldereria,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1216950828770257</t>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46254.20411431713</v>
+        <v>46260.59776207176</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>65</v>
@@ -3485,23 +3485,23 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>69</v>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="5">
         <v>46231.56019936343</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46254.20411496528</v>
+        <v>46260.59777702546</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -3534,7 +3534,7 @@
         <v>67</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q18" s="5">
         <v>46253</v>
@@ -3548,23 +3548,23 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>69</v>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="9">
         <v>46231.56020403936</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46254.2041144213</v>
+        <v>46260.597811458334</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -3597,7 +3597,7 @@
         <v>67</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q19" s="9">
         <v>46253</v>
@@ -3611,23 +3611,23 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>69</v>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" s="5">
         <v>46231.560208518524</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46254.20411569445</v>
+        <v>46260.5981228125</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3660,7 +3660,7 @@
         <v>67</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q20" s="5">
         <v>46253</v>
@@ -3674,13 +3674,13 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="12" t="s">
-        <v>69</v>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B21" s="9">
         <v>46231.56009197916</v>
@@ -3690,7 +3690,7 @@
         <v>46231.652924166665</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -3714,7 +3714,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" s="5">
         <v>46231.56021390046</v>
@@ -3737,16 +3737,16 @@
         <v>46259.192767395834</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="I22" s="5">
         <v>46254</v>
@@ -3764,13 +3764,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q22" s="5">
         <v>46266</v>
@@ -3779,18 +3779,18 @@
         <v>46254</v>
       </c>
       <c r="S22" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" s="9">
         <v>46231.56021947917</v>
@@ -3800,16 +3800,16 @@
         <v>46255.170812743054</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="I23" s="9">
         <v>46254</v>
@@ -3827,13 +3827,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3844,12 +3844,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5">
         <v>46231.560224166664</v>
@@ -3859,16 +3859,16 @@
         <v>46231.664886238425</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="I24" s="5">
         <v>46258</v>
@@ -3886,13 +3886,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3903,12 +3903,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="9">
         <v>46231.56022881945</v>
@@ -3918,16 +3918,16 @@
         <v>46259.19276744213</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="I25" s="9">
         <v>46254</v>
@@ -3945,10 +3945,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3960,18 +3960,18 @@
         <v>46254</v>
       </c>
       <c r="S25" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46231.560233067124</v>
@@ -3981,16 +3981,16 @@
         <v>46255.170814513884</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="I26" s="5">
         <v>46254</v>
@@ -4008,13 +4008,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B27" s="9">
         <v>46231.56023700231</v>
@@ -4034,16 +4034,16 @@
         <v>46231.66496887732</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="I27" s="9">
         <v>46258</v>
@@ -4061,13 +4061,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B28" s="5">
         <v>46231.560240844905</v>
@@ -4087,16 +4087,16 @@
         <v>46259.19276731482</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="I28" s="5">
         <v>46254</v>
@@ -4114,10 +4114,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -4129,18 +4129,18 @@
         <v>46254</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" s="9">
         <v>46231.56025052084</v>
@@ -4150,16 +4150,16 @@
         <v>46255.170821168984</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="I29" s="9">
         <v>46254</v>
@@ -4177,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="5">
         <v>46231.5602546875</v>
@@ -4203,16 +4203,16 @@
         <v>46231.66503913194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="I30" s="5">
         <v>46258</v>
@@ -4230,13 +4230,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B31" s="9">
         <v>46231.56025912037</v>
@@ -4256,16 +4256,16 @@
         <v>46232.617424502314</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="I31" s="9">
         <v>46254</v>
@@ -4283,10 +4283,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -4304,12 +4304,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" s="5">
         <v>46231.56026384259</v>
@@ -4319,16 +4319,16 @@
         <v>46255.62865383102</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="I32" s="5">
         <v>46254</v>
@@ -4346,13 +4346,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B33" s="9">
         <v>46231.56026863426</v>
@@ -4372,16 +4372,16 @@
         <v>46231.66516560185</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="I33" s="9">
         <v>46265</v>
@@ -4399,13 +4399,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -4415,7 +4415,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B34" s="5">
         <v>46231.56031771991</v>
@@ -4425,16 +4425,16 @@
         <v>46231.66521511574</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46296</v>
@@ -4452,13 +4452,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B35" s="9">
         <v>46231.56032325231</v>
@@ -4478,7 +4478,7 @@
         <v>46238.48777733796</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -4502,7 +4502,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B36" s="5">
         <v>46231.560327893516</v>
@@ -4527,16 +4527,16 @@
         <v>46242.18180460648</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46237</v>
@@ -4554,13 +4554,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O36" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="P36" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="Q36" s="5">
         <v>46241</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9">
         <v>46231.5654175463</v>
@@ -4592,16 +4592,16 @@
         <v>46232.578818078706</v>
       </c>
       <c r="E37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="H37" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -4619,13 +4619,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>45</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46231.56561290509</v>
@@ -4647,16 +4647,16 @@
         <v>46232.5788287037</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I38" s="5">
         <v>46237</v>
@@ -4674,13 +4674,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>45</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B39" s="9">
         <v>46231.5603328588</v>
@@ -4702,16 +4702,16 @@
         <v>46249.186783240744</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I39" s="9">
         <v>46244</v>
@@ -4729,13 +4729,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O39" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="P39" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="Q39" s="9">
         <v>46248</v>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46231.56590239583</v>
@@ -4767,16 +4767,16 @@
         <v>46238.487596446765</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I40" s="5">
         <v>46244</v>
@@ -4794,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B41" s="9">
         <v>46231.56595512731</v>
@@ -4822,16 +4822,16 @@
         <v>46238.48760439815</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I41" s="9">
         <v>46244</v>
@@ -4849,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B42" s="5">
         <v>46231.56033739583</v>
@@ -4883,10 +4883,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46251</v>
@@ -4904,13 +4904,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="Q42" s="5">
         <v>46251</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B43" s="9">
         <v>46231.56604482639</v>
@@ -4942,16 +4942,16 @@
         <v>46238.48774091435</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I43" s="9">
         <v>46251</v>
@@ -4972,7 +4972,7 @@
         <v>67</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>67</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B44" s="5">
         <v>46231.56614040509</v>
@@ -4997,16 +4997,16 @@
         <v>46238.4877480787</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I44" s="5">
         <v>46251</v>
@@ -5027,7 +5027,7 @@
         <v>67</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>67</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B45" s="9">
         <v>46231.56035158565</v>
@@ -5050,16 +5050,16 @@
         <v>46232.61799056713</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I45" s="9">
         <v>46297</v>
@@ -5077,13 +5077,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O45" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="Q45" s="9">
         <v>46297</v>
@@ -5098,12 +5098,12 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B46" s="5">
         <v>46231.56035648148</v>
@@ -5113,16 +5113,16 @@
         <v>46231.66593079861</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I46" s="5">
         <v>46297</v>
@@ -5140,13 +5140,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B47" s="9">
         <v>46231.560360868054</v>
@@ -5166,16 +5166,16 @@
         <v>46231.665927685186</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I47" s="9">
         <v>46297</v>
@@ -5193,13 +5193,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B48" s="5">
         <v>46231.56038497685</v>
@@ -5219,16 +5219,16 @@
         <v>46231.66592474537</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I48" s="5">
         <v>46297</v>
@@ -5246,13 +5246,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B49" s="9">
         <v>46231.560389074075</v>
@@ -5272,16 +5272,16 @@
         <v>46231.66592186343</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I49" s="9">
         <v>46297</v>
@@ -5299,13 +5299,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -5315,7 +5315,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B50" s="5">
         <v>46231.56638483796</v>
@@ -5325,16 +5325,16 @@
         <v>46231.66591891204</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I50" s="5">
         <v>46297</v>
@@ -5352,13 +5352,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5368,7 +5368,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B51" s="9">
         <v>46231.56639422454</v>
@@ -5378,16 +5378,16 @@
         <v>46231.66591577546</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I51" s="9">
         <v>46297</v>
@@ -5405,13 +5405,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B52" s="5">
         <v>46231.56640576389</v>
@@ -5431,16 +5431,16 @@
         <v>46231.665912372686</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I52" s="5">
         <v>46297</v>
@@ -5458,13 +5458,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B53" s="9">
         <v>46231.566415312496</v>
@@ -5484,16 +5484,16 @@
         <v>46231.66590944445</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I53" s="9">
         <v>46297</v>
@@ -5511,13 +5511,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B54" s="5">
         <v>46231.566423993056</v>
@@ -5537,16 +5537,16 @@
         <v>46231.66590684028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I54" s="5">
         <v>46297</v>
@@ -5564,13 +5564,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B55" s="9">
         <v>46231.56643305556</v>
@@ -5590,16 +5590,16 @@
         <v>46231.66590353009</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I55" s="9">
         <v>46297</v>
@@ -5617,13 +5617,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B56" s="5">
         <v>46231.56644292824</v>
@@ -5643,16 +5643,16 @@
         <v>46231.66590057871</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I56" s="5">
         <v>46297</v>
@@ -5670,13 +5670,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5686,7 +5686,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B57" s="9">
         <v>46231.56645200231</v>
@@ -5696,16 +5696,16 @@
         <v>46231.66589771991</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I57" s="9">
         <v>46297</v>
@@ -5723,13 +5723,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B58" s="5">
         <v>46231.5664612963</v>
@@ -5749,16 +5749,16 @@
         <v>46231.66589495371</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I58" s="5">
         <v>46297</v>
@@ -5776,13 +5776,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B59" s="9">
         <v>46231.56647178241</v>
@@ -5802,16 +5802,16 @@
         <v>46231.66589175926</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I59" s="9">
         <v>46297</v>
@@ -5829,13 +5829,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5845,7 +5845,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B60" s="5">
         <v>46231.56650526621</v>
@@ -5855,16 +5855,16 @@
         <v>46231.6658891088</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I60" s="5">
         <v>46297</v>
@@ -5882,13 +5882,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B61" s="9">
         <v>46231.56663635417</v>
@@ -5908,16 +5908,16 @@
         <v>46231.66588648148</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I61" s="9">
         <v>46297</v>
@@ -5935,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5951,7 +5951,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B62" s="5">
         <v>46231.56664680556</v>
@@ -5961,16 +5961,16 @@
         <v>46231.66588371528</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I62" s="5">
         <v>46297</v>
@@ -5988,13 +5988,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -6004,7 +6004,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B63" s="9">
         <v>46231.566655925926</v>
@@ -6014,16 +6014,16 @@
         <v>46231.665880636574</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I63" s="9">
         <v>46297</v>
@@ -6041,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B64" s="5">
         <v>46231.56666523148</v>
@@ -6067,16 +6067,16 @@
         <v>46231.66587766204</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I64" s="5">
         <v>46297</v>
@@ -6094,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B65" s="9">
         <v>46231.56667483796</v>
@@ -6120,16 +6120,16 @@
         <v>46231.66587439815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I65" s="9">
         <v>46297</v>
@@ -6147,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B66" s="5">
         <v>46231.566713113425</v>
@@ -6173,16 +6173,16 @@
         <v>46231.66587150463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I66" s="5">
         <v>46297</v>
@@ -6200,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B67" s="9">
         <v>46231.56672204861</v>
@@ -6226,16 +6226,16 @@
         <v>46231.665866979165</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I67" s="9">
         <v>46297</v>
@@ -6253,13 +6253,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -6269,7 +6269,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B68" s="5">
         <v>46231.56673428241</v>
@@ -6279,16 +6279,16 @@
         <v>46231.66585614583</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I68" s="5">
         <v>46297</v>
@@ -6306,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B69" s="9">
         <v>46231.56668040509</v>
@@ -6332,16 +6332,16 @@
         <v>46231.66585559028</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="I69" s="9">
         <v>46297</v>
@@ -6359,13 +6359,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -6375,7 +6375,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B70" s="5">
         <v>46231.56668668981</v>
@@ -6385,16 +6385,16 @@
         <v>46231.665857326385</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I70" s="5">
         <v>46297</v>
@@ -6412,13 +6412,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6428,7 +6428,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B71" s="9">
         <v>46231.56039302083</v>
@@ -6438,7 +6438,7 @@
         <v>46231.65302678241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -6462,7 +6462,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -6475,7 +6475,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B72" s="5">
         <v>46231.56039640046</v>
@@ -6485,16 +6485,16 @@
         <v>46260.18368119213</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
+      <c r="H72" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -6512,13 +6512,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="5">
         <v>46267</v>
@@ -6527,18 +6527,18 @@
         <v>46267</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B73" s="9">
         <v>46231.56040099537</v>
@@ -6548,16 +6548,16 @@
         <v>46260.18368162037</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -6575,13 +6575,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q73" s="9">
         <v>46267</v>
@@ -6590,18 +6590,18 @@
         <v>46267</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B74" s="5">
         <v>46231.56041240741</v>
@@ -6611,16 +6611,16 @@
         <v>46260.183681400464</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="I74" s="5">
         <v>46267</v>
@@ -6638,13 +6638,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q74" s="5">
         <v>46267</v>
@@ -6653,18 +6653,18 @@
         <v>46267</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B75" s="9">
         <v>46231.560417534725</v>
@@ -6674,16 +6674,16 @@
         <v>46232.61821685186</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I75" s="9">
         <v>46268</v>
@@ -6701,13 +6701,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q75" s="9">
         <v>46268</v>
@@ -6722,12 +6722,12 @@
         <v>0</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B76" s="5">
         <v>46231.560422361115</v>
@@ -6737,16 +6737,16 @@
         <v>46232.61822394676</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I76" s="5">
         <v>46268</v>
@@ -6764,13 +6764,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q76" s="5">
         <v>46268</v>
@@ -6785,12 +6785,12 @@
         <v>0</v>
       </c>
       <c r="U76" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B77" s="9">
         <v>46231.56042736111</v>
@@ -6800,16 +6800,16 @@
         <v>46232.61822422454</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I77" s="9">
         <v>46268</v>
@@ -6827,13 +6827,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q77" s="9">
         <v>46268</v>
@@ -6848,12 +6848,12 @@
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B78" s="5">
         <v>46231.560432708335</v>
@@ -6863,7 +6863,7 @@
         <v>46231.65338133102</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6887,7 +6887,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6900,26 +6900,26 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B79" s="9">
         <v>46231.5604353588</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46259.19276777778</v>
+        <v>46260.59824628472</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I79" s="9">
         <v>46269</v>
@@ -6937,13 +6937,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q79" s="9">
         <v>46266</v>
@@ -6952,13 +6952,13 @@
         <v>46262</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T79" s="10">
         <v>0</v>
       </c>
-      <c r="U79" s="11" t="s">
-        <v>87</v>
+      <c r="U79" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46231.666402939816</v>
+        <v>46260.599156944445</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>214</v>
@@ -6979,10 +6979,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I80" s="5">
         <v>46274</v>
@@ -7000,13 +7000,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q80" s="5">
         <v>46273</v>
@@ -7020,8 +7020,8 @@
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="11" t="s">
-        <v>87</v>
+      <c r="U80" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -7036,16 +7036,16 @@
         <v>46238.48778015046</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -7089,16 +7089,16 @@
         <v>46238.48777791667</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I82" s="5">
         <v>46274</v>
@@ -7142,16 +7142,16 @@
         <v>46238.48776831018</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I83" s="9">
         <v>46274</v>
@@ -7195,16 +7195,16 @@
         <v>46238.48778649306</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I84" s="5">
         <v>46274</v>
@@ -7248,16 +7248,16 @@
         <v>46238.48778996528</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I85" s="9">
         <v>46274</v>
@@ -7301,16 +7301,16 @@
         <v>46238.48778768518</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I86" s="5">
         <v>46274</v>
@@ -7354,16 +7354,16 @@
         <v>46238.48778834491</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I87" s="9">
         <v>46274</v>
@@ -7407,16 +7407,16 @@
         <v>46238.48778460648</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I88" s="5">
         <v>46274</v>
@@ -7460,16 +7460,16 @@
         <v>46238.48779039352</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I89" s="9">
         <v>46274</v>
@@ -7513,16 +7513,16 @@
         <v>46238.4877950463</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I90" s="5">
         <v>46274</v>
@@ -7566,16 +7566,16 @@
         <v>46238.48779283564</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7619,16 +7619,16 @@
         <v>46238.487791493055</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7672,16 +7672,16 @@
         <v>46238.48778605324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7725,16 +7725,16 @@
         <v>46238.48778420139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7778,16 +7778,16 @@
         <v>46238.48779195602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7831,16 +7831,16 @@
         <v>46238.487793657405</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7884,16 +7884,16 @@
         <v>46238.48779326389</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7937,16 +7937,16 @@
         <v>46238.48778962963</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7990,16 +7990,16 @@
         <v>46238.48778335648</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -8043,16 +8043,16 @@
         <v>46238.48778688657</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -8096,16 +8096,16 @@
         <v>46238.487783749995</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -8149,16 +8149,16 @@
         <v>46238.48779547453</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I102" s="5">
         <v>46274</v>
@@ -8202,16 +8202,16 @@
         <v>46238.48778292824</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I103" s="9">
         <v>46274</v>
@@ -8255,16 +8255,16 @@
         <v>46238.487793900465</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I104" s="5">
         <v>46274</v>
@@ -8308,16 +8308,16 @@
         <v>46238.48778729167</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I105" s="9">
         <v>46274</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46231.66668917824</v>
+        <v>46260.59919144676</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>251</v>
@@ -8367,10 +8367,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I106" s="5">
         <v>46281</v>
@@ -8388,13 +8388,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>252</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q106" s="5">
         <v>46274</v>
@@ -8408,8 +8408,8 @@
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="11" t="s">
-        <v>87</v>
+      <c r="U106" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -8424,16 +8424,16 @@
         <v>46238.48777921296</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I107" s="9">
         <v>46281</v>
@@ -8477,16 +8477,16 @@
         <v>46238.487780752315</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I108" s="5">
         <v>46281</v>
@@ -8530,16 +8530,16 @@
         <v>46238.4877812037</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I109" s="9">
         <v>46281</v>
@@ -8583,16 +8583,16 @@
         <v>46231.66672795139</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I110" s="5">
         <v>46281</v>
@@ -8613,7 +8613,7 @@
         <v>251</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>259</v>
@@ -8636,16 +8636,16 @@
         <v>46238.487785000005</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I111" s="9">
         <v>46281</v>
@@ -8689,16 +8689,16 @@
         <v>46231.66672108797</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I112" s="5">
         <v>46281</v>
@@ -8742,16 +8742,16 @@
         <v>46238.48779480324</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I113" s="9">
         <v>46281</v>
@@ -8795,16 +8795,16 @@
         <v>46231.66671467593</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I114" s="5">
         <v>46281</v>
@@ -8825,7 +8825,7 @@
         <v>251</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>259</v>
@@ -8848,16 +8848,16 @@
         <v>46231.66671130787</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I115" s="9">
         <v>46281</v>
@@ -8901,16 +8901,16 @@
         <v>46238.487792395834</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I116" s="5">
         <v>46281</v>
@@ -8954,16 +8954,16 @@
         <v>46238.487790949075</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I117" s="9">
         <v>46281</v>
@@ -9007,16 +9007,16 @@
         <v>46231.66670135417</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I118" s="5">
         <v>46281</v>
@@ -9037,7 +9037,7 @@
         <v>251</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>259</v>
@@ -9060,16 +9060,16 @@
         <v>46238.48779597222</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I119" s="9">
         <v>46281</v>
@@ -9113,16 +9113,16 @@
         <v>46231.66669519676</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I120" s="5">
         <v>46281</v>
@@ -9143,7 +9143,7 @@
         <v>251</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>259</v>
@@ -9166,16 +9166,16 @@
         <v>46231.66669142361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I121" s="9">
         <v>46281</v>
@@ -9196,7 +9196,7 @@
         <v>251</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>259</v>
@@ -9219,16 +9219,16 @@
         <v>46231.66668751158</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I122" s="5">
         <v>46281</v>
@@ -9249,7 +9249,7 @@
         <v>251</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>273</v>
@@ -9272,16 +9272,16 @@
         <v>46231.66668429398</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I123" s="9">
         <v>46281</v>
@@ -9302,7 +9302,7 @@
         <v>251</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>273</v>
@@ -9325,16 +9325,16 @@
         <v>46231.66667890047</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I124" s="5">
         <v>46281</v>
@@ -9355,7 +9355,7 @@
         <v>251</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>273</v>
@@ -9378,16 +9378,16 @@
         <v>46231.66666850694</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I125" s="9">
         <v>46281</v>
@@ -9408,7 +9408,7 @@
         <v>251</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>273</v>
@@ -9431,16 +9431,16 @@
         <v>46231.66667090278</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I126" s="5">
         <v>46281</v>
@@ -9461,7 +9461,7 @@
         <v>251</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>273</v>
@@ -9484,16 +9484,16 @@
         <v>46240.823163877314</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I127" s="9">
         <v>46281</v>
@@ -9537,16 +9537,16 @@
         <v>46240.82316032407</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I128" s="5">
         <v>46281</v>
@@ -9567,7 +9567,7 @@
         <v>251</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>273</v>
@@ -9590,16 +9590,16 @@
         <v>46240.8231571412</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I129" s="9">
         <v>46281</v>
@@ -9620,7 +9620,7 @@
         <v>251</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>273</v>
@@ -9643,16 +9643,16 @@
         <v>46240.823153680554</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I130" s="5">
         <v>46281</v>
@@ -9696,16 +9696,16 @@
         <v>46240.82315002315</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I131" s="9">
         <v>46281</v>
@@ -9802,10 +9802,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="I133" s="9">
         <v>46237</v>
@@ -9844,7 +9844,7 @@
         <v>0</v>
       </c>
       <c r="U133" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
@@ -9865,10 +9865,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="I134" s="5">
         <v>46237</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="U134" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
@@ -9928,10 +9928,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="I135" s="9">
         <v>46237</v>
@@ -9970,7 +9970,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -10080,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -10095,7 +10095,7 @@
         <v>46231.66768597222</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10125,7 +10125,7 @@
         <v>301</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>304</v>
@@ -10148,7 +10148,7 @@
         <v>46231.66769336806</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -10178,7 +10178,7 @@
         <v>301</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>306</v>
@@ -10201,7 +10201,7 @@
         <v>46231.667685312495</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10231,7 +10231,7 @@
         <v>301</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>308</v>
@@ -10254,7 +10254,7 @@
         <v>46231.66768938657</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10284,7 +10284,7 @@
         <v>301</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>310</v>
@@ -10307,7 +10307,7 @@
         <v>46231.667695219905</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10337,7 +10337,7 @@
         <v>301</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>301</v>
@@ -10360,7 +10360,7 @@
         <v>46231.6676892824</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10390,7 +10390,7 @@
         <v>301</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>301</v>
@@ -10413,7 +10413,7 @@
         <v>46231.667685821754</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10443,7 +10443,7 @@
         <v>301</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>301</v>
@@ -10466,7 +10466,7 @@
         <v>46231.66768554398</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10496,7 +10496,7 @@
         <v>301</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P145" s="10" t="s">
         <v>301</v>
@@ -10519,7 +10519,7 @@
         <v>46231.6676859838</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10549,7 +10549,7 @@
         <v>301</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>301</v>
@@ -10572,7 +10572,7 @@
         <v>46231.66768939815</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10602,7 +10602,7 @@
         <v>301</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P147" s="10" t="s">
         <v>301</v>
@@ -10625,7 +10625,7 @@
         <v>46231.667693055555</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10655,7 +10655,7 @@
         <v>301</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>301</v>
@@ -10678,7 +10678,7 @@
         <v>46231.66769350694</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10708,7 +10708,7 @@
         <v>301</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>301</v>
@@ -10731,7 +10731,7 @@
         <v>46231.66769018519</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10761,7 +10761,7 @@
         <v>301</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>301</v>
@@ -10784,7 +10784,7 @@
         <v>46231.66768600694</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10814,7 +10814,7 @@
         <v>301</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>301</v>
@@ -10837,7 +10837,7 @@
         <v>46231.66768511574</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10867,7 +10867,7 @@
         <v>301</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>301</v>
@@ -10890,7 +10890,7 @@
         <v>46231.66771173611</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10920,7 +10920,7 @@
         <v>301</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P153" s="10" t="s">
         <v>301</v>
@@ -10943,7 +10943,7 @@
         <v>46231.66768918981</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10973,7 +10973,7 @@
         <v>301</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>301</v>
@@ -10996,7 +10996,7 @@
         <v>46231.66768920139</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -11026,7 +11026,7 @@
         <v>301</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>301</v>
@@ -11049,7 +11049,7 @@
         <v>46231.66768591435</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -11079,7 +11079,7 @@
         <v>301</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>301</v>
@@ -11102,7 +11102,7 @@
         <v>46231.66768583334</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -11132,7 +11132,7 @@
         <v>301</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>301</v>
@@ -11155,7 +11155,7 @@
         <v>46231.66768583334</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11185,7 +11185,7 @@
         <v>301</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>301</v>
@@ -11208,7 +11208,7 @@
         <v>46231.66768945602</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -11238,7 +11238,7 @@
         <v>301</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>301</v>
@@ -11261,7 +11261,7 @@
         <v>46231.66768604166</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11291,7 +11291,7 @@
         <v>301</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>301</v>
@@ -11314,7 +11314,7 @@
         <v>46231.66768939815</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11344,7 +11344,7 @@
         <v>301</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>301</v>
@@ -11367,7 +11367,7 @@
         <v>46231.66769310185</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11397,7 +11397,7 @@
         <v>301</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>301</v>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="U163" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -11483,7 +11483,7 @@
         <v>46238.48777972222</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11536,7 +11536,7 @@
         <v>46238.487781620366</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11589,7 +11589,7 @@
         <v>46238.487778553244</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11642,7 +11642,7 @@
         <v>46231.667831597224</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11695,7 +11695,7 @@
         <v>46231.667839699076</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11748,7 +11748,7 @@
         <v>46231.667835925924</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11801,7 +11801,7 @@
         <v>46231.667833680556</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11854,7 +11854,7 @@
         <v>46231.667830844905</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11907,7 +11907,7 @@
         <v>46231.66784657407</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11960,7 +11960,7 @@
         <v>46231.66782869213</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -12013,7 +12013,7 @@
         <v>46231.667833217594</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -12066,7 +12066,7 @@
         <v>46231.66783061343</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -12119,7 +12119,7 @@
         <v>46231.66784224537</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -12172,7 +12172,7 @@
         <v>46231.66783100694</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -12225,7 +12225,7 @@
         <v>46231.667828958336</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -12278,7 +12278,7 @@
         <v>46231.66783663194</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -12331,7 +12331,7 @@
         <v>46231.66783365741</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12384,7 +12384,7 @@
         <v>46231.66783075231</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12437,7 +12437,7 @@
         <v>46231.66782876157</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12490,7 +12490,7 @@
         <v>46231.66783196759</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12543,7 +12543,7 @@
         <v>46231.66783085648</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12596,7 +12596,7 @@
         <v>46231.6678306713</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12649,7 +12649,7 @@
         <v>46231.66784248843</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12702,7 +12702,7 @@
         <v>46231.667834085645</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12755,7 +12755,7 @@
         <v>46231.6678331713</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12856,7 +12856,7 @@
         <v>0</v>
       </c>
       <c r="U189" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
@@ -12871,7 +12871,7 @@
         <v>46231.66826131944</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12924,7 +12924,7 @@
         <v>46231.667989050926</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12977,7 +12977,7 @@
         <v>46231.6679641088</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -13030,7 +13030,7 @@
         <v>46231.66796936342</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -13083,7 +13083,7 @@
         <v>46231.66796449074</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -13136,7 +13136,7 @@
         <v>46231.66796210648</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -13189,7 +13189,7 @@
         <v>46231.66797386574</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -13242,7 +13242,7 @@
         <v>46231.66796228009</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -13295,7 +13295,7 @@
         <v>46231.66796244213</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -13348,7 +13348,7 @@
         <v>46231.66801194444</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -13401,7 +13401,7 @@
         <v>46231.668014675924</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13454,7 +13454,7 @@
         <v>46231.66801396991</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13507,7 +13507,7 @@
         <v>46231.66801421296</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13560,7 +13560,7 @@
         <v>46231.668014097224</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13613,7 +13613,7 @@
         <v>46231.66801686343</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13666,7 +13666,7 @@
         <v>46231.66801703704</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13719,7 +13719,7 @@
         <v>46231.668013946764</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13772,7 +13772,7 @@
         <v>46231.66801465278</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13825,7 +13825,7 @@
         <v>46231.66801458334</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13878,7 +13878,7 @@
         <v>46231.66796421296</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13931,7 +13931,7 @@
         <v>46231.6679640625</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13984,7 +13984,7 @@
         <v>46231.66796466435</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -14037,7 +14037,7 @@
         <v>46231.66796478009</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -14090,7 +14090,7 @@
         <v>46231.66796820602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -14143,7 +14143,7 @@
         <v>46231.667986134256</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -14244,7 +14244,7 @@
         <v>0</v>
       </c>
       <c r="U215" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
@@ -14259,7 +14259,7 @@
         <v>46231.66839868056</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -14312,7 +14312,7 @@
         <v>46238.48778229167</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -14365,7 +14365,7 @@
         <v>46231.668395995366</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -14418,7 +14418,7 @@
         <v>46231.66839239583</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14471,7 +14471,7 @@
         <v>46231.668395671295</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14524,7 +14524,7 @@
         <v>46231.66839586805</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14577,7 +14577,7 @@
         <v>46231.66839528935</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14630,7 +14630,7 @@
         <v>46231.66839170139</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
@@ -14683,7 +14683,7 @@
         <v>46231.66839528935</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
@@ -14736,7 +14736,7 @@
         <v>46231.66839199074</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
@@ -14789,7 +14789,7 @@
         <v>46231.668389108796</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
@@ -14842,7 +14842,7 @@
         <v>46231.668388935184</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
@@ -14895,7 +14895,7 @@
         <v>46231.66839212963</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
@@ -14948,7 +14948,7 @@
         <v>46231.66839202546</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
@@ -15001,7 +15001,7 @@
         <v>46231.66839535879</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
@@ -15054,7 +15054,7 @@
         <v>46231.66839859953</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
@@ -15107,7 +15107,7 @@
         <v>46231.668392141204</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -15160,7 +15160,7 @@
         <v>46231.66838898148</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
@@ -15213,7 +15213,7 @@
         <v>46231.66839825231</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
@@ -15266,7 +15266,7 @@
         <v>46231.668391851854</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
@@ -15319,7 +15319,7 @@
         <v>46231.668389583334</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
@@ -15372,7 +15372,7 @@
         <v>46231.668389074075</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15425,7 +15425,7 @@
         <v>46231.66838769676</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
@@ -15478,7 +15478,7 @@
         <v>46231.6683890162</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15531,7 +15531,7 @@
         <v>46231.66838675926</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="T241" s="10"/>
       <c r="U241" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
@@ -15641,7 +15641,7 @@
         <v>46231.66850771991</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
@@ -15694,7 +15694,7 @@
         <v>46231.66851130787</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
@@ -15747,7 +15747,7 @@
         <v>46231.66851420139</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
@@ -15800,7 +15800,7 @@
         <v>46231.66851157407</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
@@ -15853,7 +15853,7 @@
         <v>46231.66850605324</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
@@ -15906,7 +15906,7 @@
         <v>46231.66851423611</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>26</v>
@@ -15959,7 +15959,7 @@
         <v>46231.66850797454</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>26</v>
@@ -16012,7 +16012,7 @@
         <v>46231.66850921296</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
@@ -16065,7 +16065,7 @@
         <v>46231.668514537036</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F250" s="6" t="s">
         <v>26</v>
@@ -16118,7 +16118,7 @@
         <v>46231.66850494213</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F251" s="10" t="s">
         <v>26</v>
@@ -16171,7 +16171,7 @@
         <v>46231.6685083912</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F252" s="6" t="s">
         <v>26</v>
@@ -16224,7 +16224,7 @@
         <v>46231.66850829861</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F253" s="10" t="s">
         <v>26</v>
@@ -16277,7 +16277,7 @@
         <v>46231.668502939814</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F254" s="6" t="s">
         <v>26</v>
@@ -16330,7 +16330,7 @@
         <v>46231.66851447917</v>
       </c>
       <c r="E255" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F255" s="10" t="s">
         <v>26</v>
@@ -16383,7 +16383,7 @@
         <v>46231.668505520836</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>26</v>
@@ -16436,7 +16436,7 @@
         <v>46231.66850818287</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>26</v>
@@ -16489,7 +16489,7 @@
         <v>46231.66851451389</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>26</v>
@@ -16542,7 +16542,7 @@
         <v>46231.6685082176</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F259" s="10" t="s">
         <v>26</v>
@@ -16595,7 +16595,7 @@
         <v>46231.66850509259</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>26</v>
@@ -16648,7 +16648,7 @@
         <v>46231.66851416667</v>
       </c>
       <c r="E261" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F261" s="10" t="s">
         <v>26</v>
@@ -16701,7 +16701,7 @@
         <v>46231.66851125</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F262" s="6" t="s">
         <v>26</v>
@@ -16754,7 +16754,7 @@
         <v>46231.66851166666</v>
       </c>
       <c r="E263" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F263" s="10" t="s">
         <v>26</v>
@@ -16807,7 +16807,7 @@
         <v>46231.668511192125</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F264" s="6" t="s">
         <v>26</v>
@@ -16860,7 +16860,7 @@
         <v>46231.66850479167</v>
       </c>
       <c r="E265" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F265" s="10" t="s">
         <v>26</v>
@@ -16913,7 +16913,7 @@
         <v>46231.66851174769</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>26</v>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="T267" s="10"/>
       <c r="U267" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
@@ -17023,7 +17023,7 @@
         <v>46231.6686428588</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>26</v>
@@ -17076,7 +17076,7 @@
         <v>46231.668646087965</v>
       </c>
       <c r="E269" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F269" s="10" t="s">
         <v>26</v>
@@ -17129,7 +17129,7 @@
         <v>46231.66864605324</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>26</v>
@@ -17182,7 +17182,7 @@
         <v>46231.66864655093</v>
       </c>
       <c r="E271" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F271" s="10" t="s">
         <v>26</v>
@@ -17235,7 +17235,7 @@
         <v>46231.668646261576</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>26</v>
@@ -17288,7 +17288,7 @@
         <v>46231.668647604165</v>
       </c>
       <c r="E273" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F273" s="10" t="s">
         <v>26</v>
@@ -17341,7 +17341,7 @@
         <v>46231.66865532407</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>26</v>
@@ -17394,7 +17394,7 @@
         <v>46231.66864230324</v>
       </c>
       <c r="E275" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F275" s="10" t="s">
         <v>26</v>
@@ -17447,7 +17447,7 @@
         <v>46231.66865127315</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F276" s="6" t="s">
         <v>26</v>
@@ -17500,7 +17500,7 @@
         <v>46231.66864081018</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F277" s="10" t="s">
         <v>26</v>
@@ -17553,7 +17553,7 @@
         <v>46231.668640868054</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F278" s="6" t="s">
         <v>26</v>
@@ -17606,7 +17606,7 @@
         <v>46231.66864261574</v>
       </c>
       <c r="E279" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F279" s="10" t="s">
         <v>26</v>
@@ -17659,7 +17659,7 @@
         <v>46231.668640648146</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F280" s="6" t="s">
         <v>26</v>
@@ -17712,7 +17712,7 @@
         <v>46231.668646122685</v>
       </c>
       <c r="E281" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F281" s="10" t="s">
         <v>26</v>
@@ -17765,7 +17765,7 @@
         <v>46231.66864037037</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F282" s="6" t="s">
         <v>26</v>
@@ -17818,7 +17818,7 @@
         <v>46231.66863724537</v>
       </c>
       <c r="E283" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F283" s="10" t="s">
         <v>26</v>
@@ -17871,7 +17871,7 @@
         <v>46231.66864261574</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
@@ -17924,7 +17924,7 @@
         <v>46231.66864297454</v>
       </c>
       <c r="E285" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F285" s="10" t="s">
         <v>26</v>
@@ -17977,7 +17977,7 @@
         <v>46231.66863702546</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F286" s="6" t="s">
         <v>26</v>
@@ -18030,7 +18030,7 @@
         <v>46231.66864275463</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F287" s="10" t="s">
         <v>26</v>
@@ -18083,7 +18083,7 @@
         <v>46231.66864267361</v>
       </c>
       <c r="E288" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F288" s="6" t="s">
         <v>26</v>
@@ -18136,7 +18136,7 @@
         <v>46231.66863684027</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F289" s="10" t="s">
         <v>26</v>
@@ -18189,7 +18189,7 @@
         <v>46231.66864052083</v>
       </c>
       <c r="E290" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F290" s="6" t="s">
         <v>26</v>
@@ -18242,7 +18242,7 @@
         <v>46231.66864081018</v>
       </c>
       <c r="E291" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F291" s="10" t="s">
         <v>26</v>
@@ -18295,7 +18295,7 @@
         <v>46231.668645937505</v>
       </c>
       <c r="E292" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F292" s="6" t="s">
         <v>26</v>
@@ -18390,7 +18390,7 @@
       </c>
       <c r="T293" s="10"/>
       <c r="U293" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="294" spans="1:21" x14ac:dyDescent="0.25">
@@ -18405,7 +18405,7 @@
         <v>46231.66880484954</v>
       </c>
       <c r="E294" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F294" s="6" t="s">
         <v>26</v>
@@ -18435,7 +18435,7 @@
         <v>489</v>
       </c>
       <c r="O294" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P294" s="6" t="s">
         <v>489</v>
@@ -18458,7 +18458,7 @@
         <v>46231.66880197916</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>26</v>
@@ -18488,7 +18488,7 @@
         <v>489</v>
       </c>
       <c r="O295" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P295" s="10" t="s">
         <v>489</v>
@@ -18511,7 +18511,7 @@
         <v>46231.66881472222</v>
       </c>
       <c r="E296" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F296" s="6" t="s">
         <v>26</v>
@@ -18541,7 +18541,7 @@
         <v>489</v>
       </c>
       <c r="O296" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P296" s="6" t="s">
         <v>489</v>
@@ -18564,7 +18564,7 @@
         <v>46231.66881128472</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F297" s="10" t="s">
         <v>26</v>
@@ -18594,7 +18594,7 @@
         <v>489</v>
       </c>
       <c r="O297" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P297" s="10" t="s">
         <v>489</v>
@@ -18617,7 +18617,7 @@
         <v>46231.66880478009</v>
       </c>
       <c r="E298" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F298" s="6" t="s">
         <v>26</v>
@@ -18647,7 +18647,7 @@
         <v>489</v>
       </c>
       <c r="O298" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P298" s="6" t="s">
         <v>489</v>
@@ -18670,7 +18670,7 @@
         <v>46231.668812268515</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F299" s="10" t="s">
         <v>26</v>
@@ -18700,7 +18700,7 @@
         <v>489</v>
       </c>
       <c r="O299" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P299" s="10" t="s">
         <v>489</v>
@@ -18723,7 +18723,7 @@
         <v>46231.66880841435</v>
       </c>
       <c r="E300" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F300" s="6" t="s">
         <v>26</v>
@@ -18753,7 +18753,7 @@
         <v>489</v>
       </c>
       <c r="O300" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P300" s="6" t="s">
         <v>489</v>
@@ -18776,7 +18776,7 @@
         <v>46231.66880237269</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F301" s="10" t="s">
         <v>26</v>
@@ -18806,7 +18806,7 @@
         <v>489</v>
       </c>
       <c r="O301" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P301" s="10" t="s">
         <v>489</v>
@@ -18829,7 +18829,7 @@
         <v>46231.66881479167</v>
       </c>
       <c r="E302" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F302" s="6" t="s">
         <v>26</v>
@@ -18859,7 +18859,7 @@
         <v>489</v>
       </c>
       <c r="O302" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P302" s="6" t="s">
         <v>489</v>
@@ -18882,7 +18882,7 @@
         <v>46231.66880479167</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F303" s="10" t="s">
         <v>26</v>
@@ -18912,7 +18912,7 @@
         <v>489</v>
       </c>
       <c r="O303" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P303" s="10" t="s">
         <v>489</v>
@@ -18935,7 +18935,7 @@
         <v>46231.66880506944</v>
       </c>
       <c r="E304" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F304" s="6" t="s">
         <v>26</v>
@@ -18988,7 +18988,7 @@
         <v>46231.668814432865</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F305" s="10" t="s">
         <v>26</v>
@@ -19018,7 +19018,7 @@
         <v>489</v>
       </c>
       <c r="O305" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P305" s="10" t="s">
         <v>489</v>
@@ -19041,7 +19041,7 @@
         <v>46231.66880857639</v>
       </c>
       <c r="E306" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F306" s="6" t="s">
         <v>26</v>
@@ -19071,7 +19071,7 @@
         <v>489</v>
       </c>
       <c r="O306" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P306" s="6" t="s">
         <v>489</v>
@@ -19094,7 +19094,7 @@
         <v>46231.66880244213</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>26</v>
@@ -19124,7 +19124,7 @@
         <v>489</v>
       </c>
       <c r="O307" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P307" s="10" t="s">
         <v>489</v>
@@ -19147,7 +19147,7 @@
         <v>46231.6688147338</v>
       </c>
       <c r="E308" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F308" s="6" t="s">
         <v>26</v>
@@ -19200,7 +19200,7 @@
         <v>46231.66880950231</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F309" s="10" t="s">
         <v>26</v>
@@ -19230,7 +19230,7 @@
         <v>489</v>
       </c>
       <c r="O309" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P309" s="10" t="s">
         <v>489</v>
@@ -19253,7 +19253,7 @@
         <v>46231.668803611115</v>
       </c>
       <c r="E310" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F310" s="6" t="s">
         <v>26</v>
@@ -19283,7 +19283,7 @@
         <v>489</v>
       </c>
       <c r="O310" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P310" s="6" t="s">
         <v>489</v>
@@ -19306,7 +19306,7 @@
         <v>46231.66881472222</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F311" s="10" t="s">
         <v>26</v>
@@ -19336,7 +19336,7 @@
         <v>489</v>
       </c>
       <c r="O311" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P311" s="10" t="s">
         <v>489</v>
@@ -19359,7 +19359,7 @@
         <v>46231.66880457176</v>
       </c>
       <c r="E312" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F312" s="6" t="s">
         <v>26</v>
@@ -19389,7 +19389,7 @@
         <v>489</v>
       </c>
       <c r="O312" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P312" s="6" t="s">
         <v>489</v>
@@ -19412,7 +19412,7 @@
         <v>46231.66881471065</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F313" s="10" t="s">
         <v>26</v>
@@ -19442,7 +19442,7 @@
         <v>489</v>
       </c>
       <c r="O313" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P313" s="10" t="s">
         <v>489</v>
@@ -19465,7 +19465,7 @@
         <v>46231.668809305556</v>
       </c>
       <c r="E314" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F314" s="6" t="s">
         <v>26</v>
@@ -19495,7 +19495,7 @@
         <v>489</v>
       </c>
       <c r="O314" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P314" s="6" t="s">
         <v>489</v>
@@ -19518,7 +19518,7 @@
         <v>46231.66880247685</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F315" s="10" t="s">
         <v>26</v>
@@ -19548,7 +19548,7 @@
         <v>489</v>
       </c>
       <c r="O315" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P315" s="10" t="s">
         <v>489</v>
@@ -19571,7 +19571,7 @@
         <v>46231.66881210648</v>
       </c>
       <c r="E316" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F316" s="6" t="s">
         <v>26</v>
@@ -19601,7 +19601,7 @@
         <v>489</v>
       </c>
       <c r="O316" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P316" s="6" t="s">
         <v>489</v>
@@ -19624,7 +19624,7 @@
         <v>46231.668805208334</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>26</v>
@@ -19654,7 +19654,7 @@
         <v>489</v>
       </c>
       <c r="O317" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P317" s="10" t="s">
         <v>489</v>
@@ -19677,7 +19677,7 @@
         <v>46231.668802141205</v>
       </c>
       <c r="E318" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F318" s="6" t="s">
         <v>26</v>
@@ -19707,7 +19707,7 @@
         <v>489</v>
       </c>
       <c r="O318" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P318" s="6" t="s">
         <v>489</v>
@@ -19825,7 +19825,7 @@
         <v>0</v>
       </c>
       <c r="U320" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="321" spans="1:21" x14ac:dyDescent="0.25">
@@ -19840,7 +19840,7 @@
         <v>46231.66971627314</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F321" s="10" t="s">
         <v>26</v>
@@ -19893,7 +19893,7 @@
         <v>46231.66971195602</v>
       </c>
       <c r="E322" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F322" s="6" t="s">
         <v>26</v>
@@ -19946,7 +19946,7 @@
         <v>46231.66970780093</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F323" s="10" t="s">
         <v>26</v>
@@ -19999,7 +19999,7 @@
         <v>46231.669704722226</v>
       </c>
       <c r="E324" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F324" s="6" t="s">
         <v>26</v>
@@ -20052,7 +20052,7 @@
         <v>46231.6697007176</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F325" s="10" t="s">
         <v>26</v>
@@ -20105,7 +20105,7 @@
         <v>46231.66969769676</v>
       </c>
       <c r="E326" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F326" s="6" t="s">
         <v>26</v>
@@ -20158,7 +20158,7 @@
         <v>46231.66969472222</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>26</v>
@@ -20211,7 +20211,7 @@
         <v>46231.669691689814</v>
       </c>
       <c r="E328" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F328" s="6" t="s">
         <v>26</v>
@@ -20264,7 +20264,7 @@
         <v>46231.66968831018</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F329" s="10" t="s">
         <v>26</v>
@@ -20317,7 +20317,7 @@
         <v>46231.66968530093</v>
       </c>
       <c r="E330" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F330" s="6" t="s">
         <v>26</v>
@@ -20370,7 +20370,7 @@
         <v>46231.66968244213</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F331" s="10" t="s">
         <v>26</v>
@@ -20423,7 +20423,7 @@
         <v>46231.669678935184</v>
       </c>
       <c r="E332" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F332" s="6" t="s">
         <v>26</v>
@@ -20476,7 +20476,7 @@
         <v>46231.669675763886</v>
       </c>
       <c r="E333" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F333" s="10" t="s">
         <v>26</v>
@@ -20529,7 +20529,7 @@
         <v>46231.669672777774</v>
       </c>
       <c r="E334" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F334" s="6" t="s">
         <v>26</v>
@@ -20582,7 +20582,7 @@
         <v>46231.66966976852</v>
       </c>
       <c r="E335" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F335" s="10" t="s">
         <v>26</v>
@@ -20635,7 +20635,7 @@
         <v>46231.66966627315</v>
       </c>
       <c r="E336" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F336" s="6" t="s">
         <v>26</v>
@@ -20688,7 +20688,7 @@
         <v>46231.66966341435</v>
       </c>
       <c r="E337" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F337" s="10" t="s">
         <v>26</v>
@@ -20741,7 +20741,7 @@
         <v>46231.669660671294</v>
       </c>
       <c r="E338" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F338" s="6" t="s">
         <v>26</v>
@@ -20794,7 +20794,7 @@
         <v>46231.66965815972</v>
       </c>
       <c r="E339" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F339" s="10" t="s">
         <v>26</v>
@@ -20847,7 +20847,7 @@
         <v>46231.669653634264</v>
       </c>
       <c r="E340" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F340" s="6" t="s">
         <v>26</v>
@@ -20900,7 +20900,7 @@
         <v>46231.669650173615</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F341" s="10" t="s">
         <v>26</v>
@@ -20953,7 +20953,7 @@
         <v>46231.66964695602</v>
       </c>
       <c r="E342" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F342" s="6" t="s">
         <v>26</v>
@@ -21006,7 +21006,7 @@
         <v>46231.669632986115</v>
       </c>
       <c r="E343" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F343" s="10" t="s">
         <v>26</v>
@@ -21059,7 +21059,7 @@
         <v>46231.66963234954</v>
       </c>
       <c r="E344" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F344" s="6" t="s">
         <v>26</v>
@@ -21112,7 +21112,7 @@
         <v>46231.66963550926</v>
       </c>
       <c r="E345" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F345" s="10" t="s">
         <v>26</v>
@@ -21213,7 +21213,7 @@
         <v>0</v>
       </c>
       <c r="U346" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.25">
@@ -21228,7 +21228,7 @@
         <v>46231.670200057866</v>
       </c>
       <c r="E347" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F347" s="10" t="s">
         <v>26</v>
@@ -21258,7 +21258,7 @@
         <v>555</v>
       </c>
       <c r="O347" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P347" s="10" t="s">
         <v>555</v>
@@ -21281,7 +21281,7 @@
         <v>46231.66998844907</v>
       </c>
       <c r="E348" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F348" s="6" t="s">
         <v>26</v>
@@ -21311,7 +21311,7 @@
         <v>555</v>
       </c>
       <c r="O348" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P348" s="6" t="s">
         <v>559</v>
@@ -21334,7 +21334,7 @@
         <v>46231.66998445602</v>
       </c>
       <c r="E349" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F349" s="10" t="s">
         <v>26</v>
@@ -21364,7 +21364,7 @@
         <v>555</v>
       </c>
       <c r="O349" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P349" s="10" t="s">
         <v>561</v>
@@ -21387,7 +21387,7 @@
         <v>46231.669980046296</v>
       </c>
       <c r="E350" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F350" s="6" t="s">
         <v>26</v>
@@ -21417,7 +21417,7 @@
         <v>555</v>
       </c>
       <c r="O350" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P350" s="6" t="s">
         <v>561</v>
@@ -21440,7 +21440,7 @@
         <v>46231.66997524306</v>
       </c>
       <c r="E351" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F351" s="10" t="s">
         <v>26</v>
@@ -21470,7 +21470,7 @@
         <v>555</v>
       </c>
       <c r="O351" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P351" s="10" t="s">
         <v>561</v>
@@ -21493,7 +21493,7 @@
         <v>46231.66997137731</v>
       </c>
       <c r="E352" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F352" s="6" t="s">
         <v>26</v>
@@ -21523,7 +21523,7 @@
         <v>555</v>
       </c>
       <c r="O352" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P352" s="6" t="s">
         <v>561</v>
@@ -21546,7 +21546,7 @@
         <v>46231.66996653935</v>
       </c>
       <c r="E353" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F353" s="10" t="s">
         <v>26</v>
@@ -21576,7 +21576,7 @@
         <v>555</v>
       </c>
       <c r="O353" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P353" s="10" t="s">
         <v>561</v>
@@ -21599,7 +21599,7 @@
         <v>46231.669961064814</v>
       </c>
       <c r="E354" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F354" s="6" t="s">
         <v>26</v>
@@ -21629,7 +21629,7 @@
         <v>555</v>
       </c>
       <c r="O354" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P354" s="6" t="s">
         <v>561</v>
@@ -21652,7 +21652,7 @@
         <v>46231.66995664352</v>
       </c>
       <c r="E355" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F355" s="10" t="s">
         <v>26</v>
@@ -21682,7 +21682,7 @@
         <v>555</v>
       </c>
       <c r="O355" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P355" s="10" t="s">
         <v>559</v>
@@ -21705,7 +21705,7 @@
         <v>46231.669952916665</v>
       </c>
       <c r="E356" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F356" s="6" t="s">
         <v>26</v>
@@ -21735,7 +21735,7 @@
         <v>555</v>
       </c>
       <c r="O356" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P356" s="6" t="s">
         <v>561</v>
@@ -21758,7 +21758,7 @@
         <v>46231.66994847222</v>
       </c>
       <c r="E357" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F357" s="10" t="s">
         <v>26</v>
@@ -21788,7 +21788,7 @@
         <v>555</v>
       </c>
       <c r="O357" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P357" s="10" t="s">
         <v>561</v>
@@ -21811,7 +21811,7 @@
         <v>46231.66994402777</v>
       </c>
       <c r="E358" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F358" s="6" t="s">
         <v>26</v>
@@ -21841,7 +21841,7 @@
         <v>555</v>
       </c>
       <c r="O358" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P358" s="6" t="s">
         <v>559</v>
@@ -21864,7 +21864,7 @@
         <v>46231.66994043981</v>
       </c>
       <c r="E359" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F359" s="10" t="s">
         <v>26</v>
@@ -21894,7 +21894,7 @@
         <v>555</v>
       </c>
       <c r="O359" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P359" s="10" t="s">
         <v>559</v>
@@ -21917,7 +21917,7 @@
         <v>46231.66993686343</v>
       </c>
       <c r="E360" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F360" s="6" t="s">
         <v>26</v>
@@ -21947,7 +21947,7 @@
         <v>555</v>
       </c>
       <c r="O360" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P360" s="6" t="s">
         <v>559</v>
@@ -21970,7 +21970,7 @@
         <v>46231.6699325</v>
       </c>
       <c r="E361" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F361" s="10" t="s">
         <v>26</v>
@@ -22000,7 +22000,7 @@
         <v>555</v>
       </c>
       <c r="O361" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P361" s="10" t="s">
         <v>559</v>
@@ -22023,7 +22023,7 @@
         <v>46231.66992857639</v>
       </c>
       <c r="E362" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F362" s="6" t="s">
         <v>26</v>
@@ -22053,7 +22053,7 @@
         <v>555</v>
       </c>
       <c r="O362" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P362" s="6" t="s">
         <v>575</v>
@@ -22076,7 +22076,7 @@
         <v>46231.66992512731</v>
       </c>
       <c r="E363" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F363" s="10" t="s">
         <v>26</v>
@@ -22106,7 +22106,7 @@
         <v>555</v>
       </c>
       <c r="O363" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P363" s="10" t="s">
         <v>575</v>
@@ -22129,7 +22129,7 @@
         <v>46231.669921064815</v>
       </c>
       <c r="E364" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F364" s="6" t="s">
         <v>26</v>
@@ -22159,7 +22159,7 @@
         <v>555</v>
       </c>
       <c r="O364" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P364" s="6" t="s">
         <v>578</v>
@@ -22182,7 +22182,7 @@
         <v>46231.6699174074</v>
       </c>
       <c r="E365" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F365" s="10" t="s">
         <v>26</v>
@@ -22212,7 +22212,7 @@
         <v>555</v>
       </c>
       <c r="O365" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P365" s="10" t="s">
         <v>578</v>
@@ -22235,7 +22235,7 @@
         <v>46231.66991390046</v>
       </c>
       <c r="E366" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F366" s="6" t="s">
         <v>26</v>
@@ -22265,7 +22265,7 @@
         <v>555</v>
       </c>
       <c r="O366" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P366" s="6" t="s">
         <v>578</v>
@@ -22288,7 +22288,7 @@
         <v>46231.66990978009</v>
       </c>
       <c r="E367" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F367" s="10" t="s">
         <v>26</v>
@@ -22318,7 +22318,7 @@
         <v>555</v>
       </c>
       <c r="O367" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P367" s="10" t="s">
         <v>578</v>
@@ -22341,7 +22341,7 @@
         <v>46231.66990606481</v>
       </c>
       <c r="E368" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F368" s="6" t="s">
         <v>26</v>
@@ -22371,7 +22371,7 @@
         <v>555</v>
       </c>
       <c r="O368" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P368" s="6" t="s">
         <v>578</v>
@@ -22394,7 +22394,7 @@
         <v>46231.66989173611</v>
       </c>
       <c r="E369" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F369" s="10" t="s">
         <v>26</v>
@@ -22424,7 +22424,7 @@
         <v>555</v>
       </c>
       <c r="O369" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P369" s="10" t="s">
         <v>575</v>
@@ -22447,7 +22447,7 @@
         <v>46231.66989118056</v>
       </c>
       <c r="E370" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F370" s="6" t="s">
         <v>26</v>
@@ -22477,7 +22477,7 @@
         <v>555</v>
       </c>
       <c r="O370" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P370" s="6" t="s">
         <v>575</v>
@@ -22500,7 +22500,7 @@
         <v>46231.669893796294</v>
       </c>
       <c r="E371" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F371" s="10" t="s">
         <v>26</v>
@@ -22530,7 +22530,7 @@
         <v>555</v>
       </c>
       <c r="O371" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P371" s="10" t="s">
         <v>578</v>
@@ -22559,10 +22559,10 @@
         <v>26</v>
       </c>
       <c r="G372" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H372" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H372" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I372" s="5">
         <v>46303</v>
@@ -22601,7 +22601,7 @@
         <v>0</v>
       </c>
       <c r="U372" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="373" spans="1:21" x14ac:dyDescent="0.25">
@@ -22616,16 +22616,16 @@
         <v>46231.67078247685</v>
       </c>
       <c r="E373" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F373" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G373" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H373" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H373" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I373" s="9">
         <v>46303</v>
@@ -22669,16 +22669,16 @@
         <v>46231.67077917824</v>
       </c>
       <c r="E374" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F374" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G374" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H374" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H374" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I374" s="5">
         <v>46303</v>
@@ -22699,7 +22699,7 @@
         <v>587</v>
       </c>
       <c r="O374" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P374" s="6" t="s">
         <v>591</v>
@@ -22722,16 +22722,16 @@
         <v>46231.6707759375</v>
       </c>
       <c r="E375" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F375" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G375" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H375" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H375" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I375" s="9">
         <v>46303</v>
@@ -22752,7 +22752,7 @@
         <v>587</v>
       </c>
       <c r="O375" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P375" s="10" t="s">
         <v>591</v>
@@ -22775,16 +22775,16 @@
         <v>46231.67077253472</v>
       </c>
       <c r="E376" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F376" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G376" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H376" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H376" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I376" s="5">
         <v>46303</v>
@@ -22805,7 +22805,7 @@
         <v>587</v>
       </c>
       <c r="O376" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P376" s="6" t="s">
         <v>591</v>
@@ -22828,16 +22828,16 @@
         <v>46231.67076925926</v>
       </c>
       <c r="E377" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F377" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G377" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H377" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H377" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I377" s="9">
         <v>46303</v>
@@ -22858,7 +22858,7 @@
         <v>587</v>
       </c>
       <c r="O377" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P377" s="10" t="s">
         <v>591</v>
@@ -22881,16 +22881,16 @@
         <v>46231.670765393515</v>
       </c>
       <c r="E378" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F378" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G378" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H378" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H378" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I378" s="5">
         <v>46303</v>
@@ -22911,7 +22911,7 @@
         <v>587</v>
       </c>
       <c r="O378" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P378" s="6" t="s">
         <v>589</v>
@@ -22934,16 +22934,16 @@
         <v>46231.6707622338</v>
       </c>
       <c r="E379" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F379" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G379" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H379" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H379" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I379" s="9">
         <v>46303</v>
@@ -22964,7 +22964,7 @@
         <v>587</v>
       </c>
       <c r="O379" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P379" s="10" t="s">
         <v>589</v>
@@ -22987,16 +22987,16 @@
         <v>46231.67075878472</v>
       </c>
       <c r="E380" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F380" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G380" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H380" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H380" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I380" s="5">
         <v>46303</v>
@@ -23017,7 +23017,7 @@
         <v>587</v>
       </c>
       <c r="O380" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P380" s="6" t="s">
         <v>591</v>
@@ -23040,16 +23040,16 @@
         <v>46231.670755451385</v>
       </c>
       <c r="E381" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F381" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G381" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H381" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H381" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I381" s="9">
         <v>46303</v>
@@ -23070,7 +23070,7 @@
         <v>587</v>
       </c>
       <c r="O381" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P381" s="10" t="s">
         <v>591</v>
@@ -23093,16 +23093,16 @@
         <v>46231.67075229167</v>
       </c>
       <c r="E382" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F382" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G382" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H382" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H382" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I382" s="5">
         <v>46303</v>
@@ -23123,7 +23123,7 @@
         <v>587</v>
       </c>
       <c r="O382" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P382" s="6" t="s">
         <v>591</v>
@@ -23146,16 +23146,16 @@
         <v>46231.67074930556</v>
       </c>
       <c r="E383" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F383" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G383" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H383" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H383" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I383" s="9">
         <v>46303</v>
@@ -23176,7 +23176,7 @@
         <v>587</v>
       </c>
       <c r="O383" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P383" s="10" t="s">
         <v>591</v>
@@ -23199,16 +23199,16 @@
         <v>46231.67074609954</v>
       </c>
       <c r="E384" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F384" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G384" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H384" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H384" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I384" s="5">
         <v>46303</v>
@@ -23229,7 +23229,7 @@
         <v>587</v>
       </c>
       <c r="O384" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P384" s="6" t="s">
         <v>589</v>
@@ -23252,16 +23252,16 @@
         <v>46231.67074238426</v>
       </c>
       <c r="E385" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F385" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G385" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H385" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H385" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I385" s="9">
         <v>46303</v>
@@ -23282,7 +23282,7 @@
         <v>587</v>
       </c>
       <c r="O385" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P385" s="10" t="s">
         <v>591</v>
@@ -23305,16 +23305,16 @@
         <v>46231.670739340276</v>
       </c>
       <c r="E386" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F386" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G386" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H386" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H386" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I386" s="5">
         <v>46303</v>
@@ -23335,7 +23335,7 @@
         <v>587</v>
       </c>
       <c r="O386" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P386" s="6" t="s">
         <v>591</v>
@@ -23358,16 +23358,16 @@
         <v>46231.67073607639</v>
       </c>
       <c r="E387" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F387" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G387" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H387" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H387" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I387" s="9">
         <v>46303</v>
@@ -23388,7 +23388,7 @@
         <v>587</v>
       </c>
       <c r="O387" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P387" s="10" t="s">
         <v>591</v>
@@ -23411,16 +23411,16 @@
         <v>46231.67073236111</v>
       </c>
       <c r="E388" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F388" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G388" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H388" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H388" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I388" s="5">
         <v>46303</v>
@@ -23441,7 +23441,7 @@
         <v>587</v>
       </c>
       <c r="O388" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P388" s="6" t="s">
         <v>606</v>
@@ -23464,16 +23464,16 @@
         <v>46231.67072928241</v>
       </c>
       <c r="E389" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F389" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G389" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H389" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H389" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I389" s="9">
         <v>46303</v>
@@ -23494,7 +23494,7 @@
         <v>587</v>
       </c>
       <c r="O389" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P389" s="10" t="s">
         <v>608</v>
@@ -23517,16 +23517,16 @@
         <v>46231.67072601852</v>
       </c>
       <c r="E390" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F390" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G390" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H390" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H390" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I390" s="5">
         <v>46303</v>
@@ -23547,7 +23547,7 @@
         <v>587</v>
       </c>
       <c r="O390" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P390" s="6" t="s">
         <v>608</v>
@@ -23570,16 +23570,16 @@
         <v>46231.67072258102</v>
       </c>
       <c r="E391" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F391" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G391" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H391" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H391" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I391" s="9">
         <v>46303</v>
@@ -23600,7 +23600,7 @@
         <v>587</v>
       </c>
       <c r="O391" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P391" s="10" t="s">
         <v>606</v>
@@ -23623,16 +23623,16 @@
         <v>46231.67071851852</v>
       </c>
       <c r="E392" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F392" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G392" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H392" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H392" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I392" s="5">
         <v>46303</v>
@@ -23653,7 +23653,7 @@
         <v>587</v>
       </c>
       <c r="O392" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P392" s="6" t="s">
         <v>608</v>
@@ -23676,16 +23676,16 @@
         <v>46231.67071464121</v>
       </c>
       <c r="E393" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F393" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G393" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H393" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H393" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I393" s="9">
         <v>46303</v>
@@ -23706,7 +23706,7 @@
         <v>587</v>
       </c>
       <c r="O393" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P393" s="10" t="s">
         <v>606</v>
@@ -23729,16 +23729,16 @@
         <v>46231.67071099537</v>
       </c>
       <c r="E394" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F394" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G394" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H394" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H394" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I394" s="5">
         <v>46303</v>
@@ -23759,7 +23759,7 @@
         <v>587</v>
       </c>
       <c r="O394" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P394" s="6" t="s">
         <v>606</v>
@@ -23782,16 +23782,16 @@
         <v>46231.67070591435</v>
       </c>
       <c r="E395" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F395" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G395" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H395" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H395" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I395" s="9">
         <v>46303</v>
@@ -23812,7 +23812,7 @@
         <v>587</v>
       </c>
       <c r="O395" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P395" s="10" t="s">
         <v>608</v>
@@ -23835,16 +23835,16 @@
         <v>46231.67069403935</v>
       </c>
       <c r="E396" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F396" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G396" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H396" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H396" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I396" s="5">
         <v>46303</v>
@@ -23865,7 +23865,7 @@
         <v>587</v>
       </c>
       <c r="O396" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P396" s="6" t="s">
         <v>606</v>
@@ -23888,16 +23888,16 @@
         <v>46231.670696319445</v>
       </c>
       <c r="E397" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F397" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G397" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H397" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H397" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I397" s="9">
         <v>46303</v>
@@ -23918,7 +23918,7 @@
         <v>587</v>
       </c>
       <c r="O397" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P397" s="10" t="s">
         <v>606</v>
@@ -23947,10 +23947,10 @@
         <v>26</v>
       </c>
       <c r="G398" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H398" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H398" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I398" s="5">
         <v>46304</v>
@@ -23989,7 +23989,7 @@
         <v>0</v>
       </c>
       <c r="U398" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="399" spans="1:21" x14ac:dyDescent="0.25">
@@ -24004,16 +24004,16 @@
         <v>46231.67106579861</v>
       </c>
       <c r="E399" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F399" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G399" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H399" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H399" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I399" s="9">
         <v>46304</v>
@@ -24034,7 +24034,7 @@
         <v>618</v>
       </c>
       <c r="O399" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P399" s="10" t="s">
         <v>621</v>
@@ -24057,16 +24057,16 @@
         <v>46231.671062407404</v>
       </c>
       <c r="E400" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F400" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G400" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H400" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H400" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I400" s="5">
         <v>46304</v>
@@ -24087,7 +24087,7 @@
         <v>618</v>
       </c>
       <c r="O400" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P400" s="6" t="s">
         <v>623</v>
@@ -24110,16 +24110,16 @@
         <v>46231.67105903935</v>
       </c>
       <c r="E401" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F401" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G401" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H401" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H401" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I401" s="9">
         <v>46304</v>
@@ -24140,7 +24140,7 @@
         <v>618</v>
       </c>
       <c r="O401" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P401" s="10" t="s">
         <v>625</v>
@@ -24163,16 +24163,16 @@
         <v>46231.67105518519</v>
       </c>
       <c r="E402" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F402" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G402" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H402" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H402" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I402" s="5">
         <v>46304</v>
@@ -24193,7 +24193,7 @@
         <v>618</v>
       </c>
       <c r="O402" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P402" s="6" t="s">
         <v>618</v>
@@ -24216,16 +24216,16 @@
         <v>46231.671052025464</v>
       </c>
       <c r="E403" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F403" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G403" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H403" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H403" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I403" s="9">
         <v>46304</v>
@@ -24246,7 +24246,7 @@
         <v>618</v>
       </c>
       <c r="O403" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P403" s="10" t="s">
         <v>618</v>
@@ -24269,16 +24269,16 @@
         <v>46231.67104925926</v>
       </c>
       <c r="E404" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F404" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G404" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H404" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H404" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I404" s="5">
         <v>46304</v>
@@ -24299,7 +24299,7 @@
         <v>618</v>
       </c>
       <c r="O404" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P404" s="6" t="s">
         <v>618</v>
@@ -24322,16 +24322,16 @@
         <v>46231.67104619213</v>
       </c>
       <c r="E405" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F405" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G405" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H405" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H405" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I405" s="9">
         <v>46304</v>
@@ -24352,7 +24352,7 @@
         <v>618</v>
       </c>
       <c r="O405" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P405" s="10" t="s">
         <v>618</v>
@@ -24375,16 +24375,16 @@
         <v>46231.67104260417</v>
       </c>
       <c r="E406" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F406" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G406" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H406" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H406" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I406" s="5">
         <v>46304</v>
@@ -24405,7 +24405,7 @@
         <v>618</v>
       </c>
       <c r="O406" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P406" s="6" t="s">
         <v>618</v>
@@ -24428,16 +24428,16 @@
         <v>46231.67103974537</v>
       </c>
       <c r="E407" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F407" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G407" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H407" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H407" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I407" s="9">
         <v>46304</v>
@@ -24458,7 +24458,7 @@
         <v>618</v>
       </c>
       <c r="O407" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P407" s="10" t="s">
         <v>618</v>
@@ -24481,16 +24481,16 @@
         <v>46231.67103653935</v>
       </c>
       <c r="E408" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F408" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G408" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H408" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H408" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I408" s="5">
         <v>46304</v>
@@ -24511,7 +24511,7 @@
         <v>618</v>
       </c>
       <c r="O408" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P408" s="6" t="s">
         <v>618</v>
@@ -24534,16 +24534,16 @@
         <v>46231.671033182865</v>
       </c>
       <c r="E409" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F409" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G409" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H409" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H409" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I409" s="9">
         <v>46304</v>
@@ -24564,7 +24564,7 @@
         <v>618</v>
       </c>
       <c r="O409" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P409" s="10" t="s">
         <v>618</v>
@@ -24587,16 +24587,16 @@
         <v>46231.67103011574</v>
       </c>
       <c r="E410" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F410" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G410" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H410" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H410" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I410" s="5">
         <v>46304</v>
@@ -24617,7 +24617,7 @@
         <v>618</v>
       </c>
       <c r="O410" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P410" s="6" t="s">
         <v>618</v>
@@ -24640,16 +24640,16 @@
         <v>46231.67102701389</v>
       </c>
       <c r="E411" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F411" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G411" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H411" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H411" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I411" s="9">
         <v>46304</v>
@@ -24670,7 +24670,7 @@
         <v>618</v>
       </c>
       <c r="O411" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P411" s="10" t="s">
         <v>618</v>
@@ -24693,16 +24693,16 @@
         <v>46231.671023993054</v>
       </c>
       <c r="E412" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F412" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G412" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H412" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H412" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I412" s="5">
         <v>46304</v>
@@ -24723,7 +24723,7 @@
         <v>618</v>
       </c>
       <c r="O412" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P412" s="6" t="s">
         <v>618</v>
@@ -24746,16 +24746,16 @@
         <v>46231.67102047453</v>
       </c>
       <c r="E413" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F413" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G413" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H413" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H413" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I413" s="9">
         <v>46304</v>
@@ -24776,7 +24776,7 @@
         <v>618</v>
       </c>
       <c r="O413" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P413" s="10" t="s">
         <v>618</v>
@@ -24799,16 +24799,16 @@
         <v>46231.67101741898</v>
       </c>
       <c r="E414" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F414" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G414" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H414" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H414" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I414" s="5">
         <v>46304</v>
@@ -24829,7 +24829,7 @@
         <v>618</v>
       </c>
       <c r="O414" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P414" s="6" t="s">
         <v>618</v>
@@ -24852,16 +24852,16 @@
         <v>46231.671014259264</v>
       </c>
       <c r="E415" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F415" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G415" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H415" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H415" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I415" s="9">
         <v>46304</v>
@@ -24882,7 +24882,7 @@
         <v>618</v>
       </c>
       <c r="O415" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P415" s="10" t="s">
         <v>618</v>
@@ -24905,16 +24905,16 @@
         <v>46231.671010289356</v>
       </c>
       <c r="E416" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F416" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G416" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H416" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H416" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I416" s="5">
         <v>46304</v>
@@ -24935,7 +24935,7 @@
         <v>618</v>
       </c>
       <c r="O416" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P416" s="6" t="s">
         <v>618</v>
@@ -24958,16 +24958,16 @@
         <v>46231.67100728009</v>
       </c>
       <c r="E417" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F417" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G417" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H417" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H417" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I417" s="9">
         <v>46304</v>
@@ -24988,7 +24988,7 @@
         <v>618</v>
       </c>
       <c r="O417" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P417" s="10" t="s">
         <v>618</v>
@@ -25011,16 +25011,16 @@
         <v>46231.67100423611</v>
       </c>
       <c r="E418" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F418" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G418" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H418" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H418" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I418" s="5">
         <v>46304</v>
@@ -25041,7 +25041,7 @@
         <v>618</v>
       </c>
       <c r="O418" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P418" s="6" t="s">
         <v>618</v>
@@ -25064,16 +25064,16 @@
         <v>46231.6710006713</v>
       </c>
       <c r="E419" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F419" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G419" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H419" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H419" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I419" s="9">
         <v>46304</v>
@@ -25094,7 +25094,7 @@
         <v>618</v>
       </c>
       <c r="O419" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P419" s="10" t="s">
         <v>618</v>
@@ -25117,16 +25117,16 @@
         <v>46231.67099731481</v>
       </c>
       <c r="E420" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F420" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G420" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H420" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H420" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I420" s="5">
         <v>46304</v>
@@ -25147,7 +25147,7 @@
         <v>618</v>
       </c>
       <c r="O420" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P420" s="6" t="s">
         <v>618</v>
@@ -25170,16 +25170,16 @@
         <v>46231.67098568287</v>
       </c>
       <c r="E421" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F421" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G421" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H421" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H421" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I421" s="9">
         <v>46304</v>
@@ -25200,7 +25200,7 @@
         <v>618</v>
       </c>
       <c r="O421" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P421" s="10" t="s">
         <v>618</v>
@@ -25223,16 +25223,16 @@
         <v>46231.670985115736</v>
       </c>
       <c r="E422" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F422" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G422" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H422" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H422" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I422" s="5">
         <v>46304</v>
@@ -25253,7 +25253,7 @@
         <v>618</v>
       </c>
       <c r="O422" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P422" s="6" t="s">
         <v>618</v>
@@ -25276,16 +25276,16 @@
         <v>46231.67098739583</v>
       </c>
       <c r="E423" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F423" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G423" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H423" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H423" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I423" s="9">
         <v>46304</v>
@@ -25306,7 +25306,7 @@
         <v>618</v>
       </c>
       <c r="O423" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P423" s="10" t="s">
         <v>618</v>
@@ -25424,7 +25424,7 @@
         <v>0</v>
       </c>
       <c r="U425" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="426" spans="1:21" x14ac:dyDescent="0.25">
@@ -25487,7 +25487,7 @@
         <v>0</v>
       </c>
       <c r="U426" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46231.65302678241</v>
+        <v>46260.662351446765</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>184</v>
@@ -6732,9 +6732,11 @@
       <c r="B76" s="5">
         <v>46231.560422361115</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46260.662343703705</v>
+      </c>
       <c r="D76" s="5">
-        <v>46232.61822394676</v>
+        <v>46260.66236099537</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>201</v>
@@ -6782,10 +6784,10 @@
         <v>32</v>
       </c>
       <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="11" t="s">
-        <v>86</v>
+        <v>1</v>
+      </c>
+      <c r="U76" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -7033,7 +7035,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46238.48778015046</v>
+        <v>46260.6623522338</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>135</v>
@@ -7086,7 +7088,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46238.48777791667</v>
+        <v>46260.662350914354</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>135</v>
@@ -7139,7 +7141,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46238.48776831018</v>
+        <v>46260.662350370374</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>135</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46232.61821685186</v>
+        <v>46261.19540744213</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>198</v>
@@ -6715,8 +6715,8 @@
       <c r="R75" s="9">
         <v>46268</v>
       </c>
-      <c r="S75" s="7" t="s">
-        <v>32</v>
+      <c r="S75" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="T75" s="10">
         <v>0</v>
@@ -6736,7 +6736,7 @@
         <v>46260.662343703705</v>
       </c>
       <c r="D76" s="5">
-        <v>46260.66236099537</v>
+        <v>46261.19540667824</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>201</v>
@@ -6780,8 +6780,8 @@
       <c r="R76" s="5">
         <v>46268</v>
       </c>
-      <c r="S76" s="7" t="s">
-        <v>32</v>
+      <c r="S76" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46232.61822422454</v>
+        <v>46261.19540776621</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>204</v>
@@ -6843,8 +6843,8 @@
       <c r="R77" s="9">
         <v>46268</v>
       </c>
-      <c r="S77" s="7" t="s">
-        <v>32</v>
+      <c r="S77" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -4316,7 +4316,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46255.62865383102</v>
+        <v>46262.170702118055</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>115</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46259.192767395834</v>
+        <v>46266.16977670139</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>80</v>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46231.664886238425</v>
+        <v>46266.16978236111</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46259.19276744213</v>
+        <v>46266.16978337963</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>94</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46231.66496887732</v>
+        <v>46266.169778888885</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>99</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46259.19276731482</v>
+        <v>46266.16978005787</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>102</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46231.66503913194</v>
+        <v>46266.1697812037</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>107</v>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46260.599156944445</v>
+        <v>46266.20265497685</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>214</v>
@@ -7016,8 +7016,8 @@
       <c r="R80" s="5">
         <v>46267</v>
       </c>
-      <c r="S80" s="7" t="s">
-        <v>32</v>
+      <c r="S80" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -306,322 +306,322 @@
     <t xml:space="preserve">Generación OC corte laser   OT 4382 - OT 4383 ,Fabricacion corte laser  OT 4382 - OT 4383  </t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1216950739448529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC corte laser   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte Laser  OT 4382 - OT 4383  1 ,Fabricacion corte laser  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216951179352081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion corte laser  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  ,Corte Laser  OT 4382 - OT 4383  1 </t>
+  </si>
+  <si>
+    <t>1216951179352102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion OC Corte plasma   OT 4382 - OT 4383  ,Fabricación corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950739466470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma   OT 4382 - OT 4383 ,Fabricación corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950739466488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma   OT 4382 - OT 4383 ,Corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950957054599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC mecanizado  OT 4382 - OT 4383 ,Fabricación Mecanizado  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950957054612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado OT 4382 - OT 4383  ,Fabricación Mecanizado  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950957064236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Mecanizado  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion mecanizado  OT 4382 - OT 4383  ,Mecanizado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950739515250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 ,Generacion Oc OT 4382 - OT 4383 ,Armado  OT 4382 - OT 4383 OT 4381 </t>
+  </si>
+  <si>
+    <t>1216950739515263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   ,Armado  OT 4382 - OT 4383 OT 4381 </t>
+  </si>
+  <si>
+    <t>1216950739515281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado  OT 4382 - OT 4383 OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 ,Fabricación externa   OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>1216950739385453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216950739385471</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check pruebas FAT  OT 4382 - OT 4383   ,Plano Preliminar  OT 4382 - OT 4383  ,Check Planos  OT 4382 - OT 4383 ,Plano Definitivos  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950828707841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Preliminar  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216916670896948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216916670896949</t>
+  </si>
+  <si>
+    <t>ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216950828707864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>Plano Preliminar  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216916670896950</t>
+  </si>
+  <si>
+    <t>1216916670896951</t>
+  </si>
+  <si>
+    <t>1216951179437504</t>
+  </si>
+  <si>
+    <t>Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Propuesta Fabricación externa   OT 4381OT 4382 - OT 4383   ,Propuesta Mecanizado  OT 4382 - OT 4383 ,Propuesta Corte plasma  OT 4382 - OT 4383 ,propuesta Corte laser  OT 4382 - OT 4383 ,Ingenieria y diseño:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216916670896952</t>
+  </si>
+  <si>
+    <t>1216916670896953</t>
+  </si>
+  <si>
+    <t>1216950828716752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check pruebas FAT  OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseño:,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950739592745</t>
+  </si>
+  <si>
+    <t>1216950739592758</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales,Check pruebas FAT  OT 4382 - OT 4383   ,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1216950739611887</t>
+  </si>
+  <si>
+    <t>1216950807684439</t>
+  </si>
+  <si>
+    <t>1216916670896954</t>
+  </si>
+  <si>
+    <t>1216916670896955</t>
+  </si>
+  <si>
+    <t>1216916670896956</t>
+  </si>
+  <si>
+    <t>1216916670896957</t>
+  </si>
+  <si>
+    <t>1216916670896958</t>
+  </si>
+  <si>
+    <t>1216916670896959</t>
+  </si>
+  <si>
+    <t>1216916670896960</t>
+  </si>
+  <si>
+    <t>1216916670896961</t>
+  </si>
+  <si>
+    <t>1216916670896962</t>
+  </si>
+  <si>
+    <t>1216916670896963</t>
+  </si>
+  <si>
+    <t>1216916670896964</t>
+  </si>
+  <si>
+    <t>1216916670896965</t>
+  </si>
+  <si>
+    <t>1216916670896966</t>
+  </si>
+  <si>
+    <t>1216916670896967</t>
+  </si>
+  <si>
+    <t>1216916670896968</t>
+  </si>
+  <si>
+    <t>1216916670896969</t>
+  </si>
+  <si>
+    <t>1216916670896972</t>
+  </si>
+  <si>
+    <t>1216916670896973</t>
+  </si>
+  <si>
+    <t>1216916670896974</t>
+  </si>
+  <si>
+    <t>1216916670896970</t>
+  </si>
+  <si>
+    <t>1216916670896971</t>
+  </si>
+  <si>
+    <t>1216950807684452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  ,Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Mecanizado  OT 4382 - OT 4383 ,Recepcion corte plasma   OT 4382 - OT 4383 ,Recepcion mecanizado  OT 4382 - OT 4383  ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950739647056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad corte Laser OT 4382 - OT 4383 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1216950739448529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC corte laser   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte Laser  OT 4382 - OT 4383  1 ,Fabricacion corte laser  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216951179352081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion corte laser  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  ,Corte Laser  OT 4382 - OT 4383  1 </t>
-  </si>
-  <si>
-    <t>1216951179352102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion OC Corte plasma   OT 4382 - OT 4383  ,Fabricación corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950739466470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma   OT 4382 - OT 4383 ,Fabricación corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950739466488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma   OT 4382 - OT 4383 ,Corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950957054599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC mecanizado  OT 4382 - OT 4383 ,Fabricación Mecanizado  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950957054612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado OT 4382 - OT 4383  ,Fabricación Mecanizado  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950957064236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Mecanizado  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion mecanizado  OT 4382 - OT 4383  ,Mecanizado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950739515250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 ,Generacion Oc OT 4382 - OT 4383 ,Armado  OT 4382 - OT 4383 OT 4381 </t>
-  </si>
-  <si>
-    <t>1216950739515263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa   OT 4382 - OT 4383   ,Armado  OT 4382 - OT 4383 OT 4381 </t>
-  </si>
-  <si>
-    <t>1216950739515281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado  OT 4382 - OT 4383 OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 ,Fabricación externa   OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>1216950739385453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216950739385471</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check pruebas FAT  OT 4382 - OT 4383   ,Plano Preliminar  OT 4382 - OT 4383  ,Check Planos  OT 4382 - OT 4383 ,Plano Definitivos  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950828707841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Preliminar  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216916670896948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216916670896949</t>
-  </si>
-  <si>
-    <t>ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216950828707864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>Plano Preliminar  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216916670896950</t>
-  </si>
-  <si>
-    <t>1216916670896951</t>
-  </si>
-  <si>
-    <t>1216951179437504</t>
-  </si>
-  <si>
-    <t>Plano Definitivos  OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Propuesta Fabricación externa   OT 4381OT 4382 - OT 4383   ,Propuesta Mecanizado  OT 4382 - OT 4383 ,Propuesta Corte plasma  OT 4382 - OT 4383 ,propuesta Corte laser  OT 4382 - OT 4383 ,Ingenieria y diseño:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216916670896952</t>
-  </si>
-  <si>
-    <t>1216916670896953</t>
-  </si>
-  <si>
-    <t>1216950828716752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check pruebas FAT  OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseño:,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950739592745</t>
-  </si>
-  <si>
-    <t>1216950739592758</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT 4347 Preparación Materiales,Check pruebas FAT  OT 4382 - OT 4383   ,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1216950739611887</t>
-  </si>
-  <si>
-    <t>1216950807684439</t>
-  </si>
-  <si>
-    <t>1216916670896954</t>
-  </si>
-  <si>
-    <t>1216916670896955</t>
-  </si>
-  <si>
-    <t>1216916670896956</t>
-  </si>
-  <si>
-    <t>1216916670896957</t>
-  </si>
-  <si>
-    <t>1216916670896958</t>
-  </si>
-  <si>
-    <t>1216916670896959</t>
-  </si>
-  <si>
-    <t>1216916670896960</t>
-  </si>
-  <si>
-    <t>1216916670896961</t>
-  </si>
-  <si>
-    <t>1216916670896962</t>
-  </si>
-  <si>
-    <t>1216916670896963</t>
-  </si>
-  <si>
-    <t>1216916670896964</t>
-  </si>
-  <si>
-    <t>1216916670896965</t>
-  </si>
-  <si>
-    <t>1216916670896966</t>
-  </si>
-  <si>
-    <t>1216916670896967</t>
-  </si>
-  <si>
-    <t>1216916670896968</t>
-  </si>
-  <si>
-    <t>1216916670896969</t>
-  </si>
-  <si>
-    <t>1216916670896972</t>
-  </si>
-  <si>
-    <t>1216916670896973</t>
-  </si>
-  <si>
-    <t>1216916670896974</t>
-  </si>
-  <si>
-    <t>1216916670896970</t>
-  </si>
-  <si>
-    <t>1216916670896971</t>
-  </si>
-  <si>
-    <t>1216950807684452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  ,Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Mecanizado  OT 4382 - OT 4383 ,Recepcion corte plasma   OT 4382 - OT 4383 ,Recepcion mecanizado  OT 4382 - OT 4383  ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950739647056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad corte Laser OT 4382 - OT 4383 </t>
   </si>
   <si>
     <t>1216950739647079</t>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46266.16977670139</v>
+        <v>46267.18262917824</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>80</v>
@@ -3778,19 +3778,19 @@
       <c r="R22" s="5">
         <v>46254</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>85</v>
+      <c r="S22" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="9">
         <v>46231.56021947917</v>
@@ -3800,7 +3800,7 @@
         <v>46255.170812743054</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -3833,7 +3833,7 @@
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3844,12 +3844,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" s="5">
         <v>46231.560224166664</v>
@@ -3859,7 +3859,7 @@
         <v>46266.16978236111</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3889,10 +3889,10 @@
         <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3903,22 +3903,22 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="9">
         <v>46231.56022881945</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46266.16978337963</v>
+        <v>46267.18262930556</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3948,7 +3948,7 @@
         <v>79</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3959,19 +3959,19 @@
       <c r="R25" s="9">
         <v>46254</v>
       </c>
-      <c r="S25" s="12" t="s">
-        <v>85</v>
+      <c r="S25" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B26" s="5">
         <v>46231.560233067124</v>
@@ -4008,13 +4008,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" s="9">
         <v>46231.56023700231</v>
@@ -4034,7 +4034,7 @@
         <v>46266.169778888885</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -4061,13 +4061,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -4077,17 +4077,17 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" s="5">
         <v>46231.560240844905</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46266.16978005787</v>
+        <v>46267.18262917824</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -4117,7 +4117,7 @@
         <v>79</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -4128,19 +4128,19 @@
       <c r="R28" s="5">
         <v>46254</v>
       </c>
-      <c r="S28" s="12" t="s">
-        <v>85</v>
+      <c r="S28" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B29" s="9">
         <v>46231.56025052084</v>
@@ -4177,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>76</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B30" s="5">
         <v>46231.5602546875</v>
@@ -4203,7 +4203,7 @@
         <v>46266.1697812037</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -4230,13 +4230,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B31" s="9">
         <v>46231.56025912037</v>
@@ -4256,16 +4256,16 @@
         <v>46232.617424502314</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="I31" s="9">
         <v>46254</v>
@@ -4286,7 +4286,7 @@
         <v>79</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -4304,12 +4304,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32" s="5">
         <v>46231.56026384259</v>
@@ -4319,16 +4319,16 @@
         <v>46262.170702118055</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="I32" s="5">
         <v>46254</v>
@@ -4346,13 +4346,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B33" s="9">
         <v>46231.56026863426</v>
@@ -4372,16 +4372,16 @@
         <v>46231.66516560185</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="I33" s="9">
         <v>46265</v>
@@ -4399,13 +4399,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -4415,7 +4415,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B34" s="5">
         <v>46231.56031771991</v>
@@ -4425,16 +4425,16 @@
         <v>46231.66521511574</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46296</v>
@@ -4452,13 +4452,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35" s="9">
         <v>46231.56032325231</v>
@@ -4478,7 +4478,7 @@
         <v>46238.48777733796</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -4502,7 +4502,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" s="5">
         <v>46231.560327893516</v>
@@ -4527,16 +4527,16 @@
         <v>46242.18180460648</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="I36" s="5">
         <v>46237</v>
@@ -4554,13 +4554,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="P36" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="Q36" s="5">
         <v>46241</v>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B37" s="9">
         <v>46231.5654175463</v>
@@ -4592,16 +4592,16 @@
         <v>46232.578818078706</v>
       </c>
       <c r="E37" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="H37" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -4619,13 +4619,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>45</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46231.56561290509</v>
@@ -4647,16 +4647,16 @@
         <v>46232.5788287037</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46237</v>
@@ -4674,13 +4674,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>45</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B39" s="9">
         <v>46231.5603328588</v>
@@ -4702,16 +4702,16 @@
         <v>46249.186783240744</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="I39" s="9">
         <v>46244</v>
@@ -4729,13 +4729,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O39" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="P39" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="Q39" s="9">
         <v>46248</v>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46231.56590239583</v>
@@ -4767,16 +4767,16 @@
         <v>46238.487596446765</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I40" s="5">
         <v>46244</v>
@@ -4794,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B41" s="9">
         <v>46231.56595512731</v>
@@ -4822,16 +4822,16 @@
         <v>46238.48760439815</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I41" s="9">
         <v>46244</v>
@@ -4849,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" s="5">
         <v>46231.56033739583</v>
@@ -4883,10 +4883,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I42" s="5">
         <v>46251</v>
@@ -4904,13 +4904,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="Q42" s="5">
         <v>46251</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B43" s="9">
         <v>46231.56604482639</v>
@@ -4942,16 +4942,16 @@
         <v>46238.48774091435</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I43" s="9">
         <v>46251</v>
@@ -4972,7 +4972,7 @@
         <v>67</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>67</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B44" s="5">
         <v>46231.56614040509</v>
@@ -4997,16 +4997,16 @@
         <v>46238.4877480787</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I44" s="5">
         <v>46251</v>
@@ -5027,7 +5027,7 @@
         <v>67</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>67</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B45" s="9">
         <v>46231.56035158565</v>
@@ -5050,16 +5050,16 @@
         <v>46232.61799056713</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I45" s="9">
         <v>46297</v>
@@ -5077,13 +5077,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O45" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="Q45" s="9">
         <v>46297</v>
@@ -5098,12 +5098,12 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B46" s="5">
         <v>46231.56035648148</v>
@@ -5113,16 +5113,16 @@
         <v>46231.66593079861</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46297</v>
@@ -5140,13 +5140,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B47" s="9">
         <v>46231.560360868054</v>
@@ -5166,16 +5166,16 @@
         <v>46231.665927685186</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I47" s="9">
         <v>46297</v>
@@ -5193,13 +5193,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B48" s="5">
         <v>46231.56038497685</v>
@@ -5219,16 +5219,16 @@
         <v>46231.66592474537</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I48" s="5">
         <v>46297</v>
@@ -5246,13 +5246,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B49" s="9">
         <v>46231.560389074075</v>
@@ -5272,16 +5272,16 @@
         <v>46231.66592186343</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I49" s="9">
         <v>46297</v>
@@ -5299,13 +5299,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -5315,7 +5315,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B50" s="5">
         <v>46231.56638483796</v>
@@ -5325,16 +5325,16 @@
         <v>46231.66591891204</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I50" s="5">
         <v>46297</v>
@@ -5352,13 +5352,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5368,7 +5368,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B51" s="9">
         <v>46231.56639422454</v>
@@ -5378,16 +5378,16 @@
         <v>46231.66591577546</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I51" s="9">
         <v>46297</v>
@@ -5405,13 +5405,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B52" s="5">
         <v>46231.56640576389</v>
@@ -5431,16 +5431,16 @@
         <v>46231.665912372686</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I52" s="5">
         <v>46297</v>
@@ -5458,13 +5458,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B53" s="9">
         <v>46231.566415312496</v>
@@ -5484,16 +5484,16 @@
         <v>46231.66590944445</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I53" s="9">
         <v>46297</v>
@@ -5511,13 +5511,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B54" s="5">
         <v>46231.566423993056</v>
@@ -5537,16 +5537,16 @@
         <v>46231.66590684028</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I54" s="5">
         <v>46297</v>
@@ -5564,13 +5564,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B55" s="9">
         <v>46231.56643305556</v>
@@ -5590,16 +5590,16 @@
         <v>46231.66590353009</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I55" s="9">
         <v>46297</v>
@@ -5617,13 +5617,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B56" s="5">
         <v>46231.56644292824</v>
@@ -5643,16 +5643,16 @@
         <v>46231.66590057871</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I56" s="5">
         <v>46297</v>
@@ -5670,13 +5670,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5686,7 +5686,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B57" s="9">
         <v>46231.56645200231</v>
@@ -5696,16 +5696,16 @@
         <v>46231.66589771991</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I57" s="9">
         <v>46297</v>
@@ -5723,13 +5723,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B58" s="5">
         <v>46231.5664612963</v>
@@ -5749,16 +5749,16 @@
         <v>46231.66589495371</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I58" s="5">
         <v>46297</v>
@@ -5776,13 +5776,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B59" s="9">
         <v>46231.56647178241</v>
@@ -5802,16 +5802,16 @@
         <v>46231.66589175926</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I59" s="9">
         <v>46297</v>
@@ -5829,13 +5829,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5845,7 +5845,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B60" s="5">
         <v>46231.56650526621</v>
@@ -5855,16 +5855,16 @@
         <v>46231.6658891088</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I60" s="5">
         <v>46297</v>
@@ -5882,13 +5882,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B61" s="9">
         <v>46231.56663635417</v>
@@ -5908,16 +5908,16 @@
         <v>46231.66588648148</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I61" s="9">
         <v>46297</v>
@@ -5935,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5951,7 +5951,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B62" s="5">
         <v>46231.56664680556</v>
@@ -5961,16 +5961,16 @@
         <v>46231.66588371528</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I62" s="5">
         <v>46297</v>
@@ -5988,13 +5988,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -6004,7 +6004,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B63" s="9">
         <v>46231.566655925926</v>
@@ -6014,16 +6014,16 @@
         <v>46231.665880636574</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I63" s="9">
         <v>46297</v>
@@ -6041,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B64" s="5">
         <v>46231.56666523148</v>
@@ -6067,16 +6067,16 @@
         <v>46231.66587766204</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I64" s="5">
         <v>46297</v>
@@ -6094,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B65" s="9">
         <v>46231.56667483796</v>
@@ -6120,16 +6120,16 @@
         <v>46231.66587439815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I65" s="9">
         <v>46297</v>
@@ -6147,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B66" s="5">
         <v>46231.566713113425</v>
@@ -6173,16 +6173,16 @@
         <v>46231.66587150463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I66" s="5">
         <v>46297</v>
@@ -6200,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B67" s="9">
         <v>46231.56672204861</v>
@@ -6226,16 +6226,16 @@
         <v>46231.665866979165</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I67" s="9">
         <v>46297</v>
@@ -6253,13 +6253,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -6269,7 +6269,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B68" s="5">
         <v>46231.56673428241</v>
@@ -6279,16 +6279,16 @@
         <v>46231.66585614583</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I68" s="5">
         <v>46297</v>
@@ -6306,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B69" s="9">
         <v>46231.56668040509</v>
@@ -6332,16 +6332,16 @@
         <v>46231.66585559028</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I69" s="9">
         <v>46297</v>
@@ -6359,13 +6359,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -6375,7 +6375,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B70" s="5">
         <v>46231.56668668981</v>
@@ -6385,16 +6385,16 @@
         <v>46231.665857326385</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I70" s="5">
         <v>46297</v>
@@ -6412,13 +6412,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6428,7 +6428,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B71" s="9">
         <v>46231.56039302083</v>
@@ -6438,7 +6438,7 @@
         <v>46260.662351446765</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -6462,7 +6462,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -6475,26 +6475,26 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B72" s="5">
         <v>46231.56039640046</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46260.18368119213</v>
+        <v>46267.16901923611</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
+      <c r="H72" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -6512,13 +6512,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q72" s="5">
         <v>46267</v>
@@ -6527,13 +6527,13 @@
         <v>46267</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46260.18368162037</v>
+        <v>46267.16902148148</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>192</v>
@@ -6554,10 +6554,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -6575,10 +6575,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>193</v>
@@ -6590,13 +6590,13 @@
         <v>46267</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46260.183681400464</v>
+        <v>46267.16902263889</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>195</v>
@@ -6617,10 +6617,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I74" s="5">
         <v>46267</v>
@@ -6638,10 +6638,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>196</v>
@@ -6653,13 +6653,13 @@
         <v>46267</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6680,10 +6680,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I75" s="9">
         <v>46268</v>
@@ -6701,10 +6701,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>199</v>
@@ -6716,13 +6716,13 @@
         <v>46268</v>
       </c>
       <c r="S75" s="12" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="T75" s="10">
         <v>0</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6745,10 +6745,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I76" s="5">
         <v>46268</v>
@@ -6766,7 +6766,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>192</v>
@@ -6781,7 +6781,7 @@
         <v>46268</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6808,10 +6808,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I77" s="9">
         <v>46268</v>
@@ -6829,7 +6829,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>195</v>
@@ -6844,13 +6844,13 @@
         <v>46268</v>
       </c>
       <c r="S77" s="12" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46260.59824628472</v>
+        <v>46267.182629375</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>74</v>
@@ -6953,8 +6953,8 @@
       <c r="R79" s="9">
         <v>46262</v>
       </c>
-      <c r="S79" s="12" t="s">
-        <v>85</v>
+      <c r="S79" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T79" s="10">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         <v>46267</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
@@ -7038,7 +7038,7 @@
         <v>46260.6623522338</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -7091,7 +7091,7 @@
         <v>46260.662350914354</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -7144,7 +7144,7 @@
         <v>46260.662350370374</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -7197,7 +7197,7 @@
         <v>46238.48778649306</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -7250,7 +7250,7 @@
         <v>46238.48778996528</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -7303,7 +7303,7 @@
         <v>46238.48778768518</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -7356,7 +7356,7 @@
         <v>46238.48778834491</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -7409,7 +7409,7 @@
         <v>46238.48778460648</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7462,7 +7462,7 @@
         <v>46238.48779039352</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -7515,7 +7515,7 @@
         <v>46238.4877950463</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7568,7 +7568,7 @@
         <v>46238.48779283564</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7621,7 +7621,7 @@
         <v>46238.487791493055</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7674,7 +7674,7 @@
         <v>46238.48778605324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7727,7 +7727,7 @@
         <v>46238.48778420139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7780,7 +7780,7 @@
         <v>46238.48779195602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7833,7 +7833,7 @@
         <v>46238.487793657405</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7886,7 +7886,7 @@
         <v>46238.48779326389</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7939,7 +7939,7 @@
         <v>46238.48778962963</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7992,7 +7992,7 @@
         <v>46238.48778335648</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -8045,7 +8045,7 @@
         <v>46238.48778688657</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -8098,7 +8098,7 @@
         <v>46238.487783749995</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -8151,7 +8151,7 @@
         <v>46238.48779547453</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -8204,7 +8204,7 @@
         <v>46238.48778292824</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -8257,7 +8257,7 @@
         <v>46238.487793900465</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8310,7 +8310,7 @@
         <v>46238.48778729167</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46260.59919144676</v>
+        <v>46267.17693162037</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>251</v>
@@ -8369,10 +8369,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I106" s="5">
         <v>46281</v>
@@ -8404,8 +8404,8 @@
       <c r="R106" s="5">
         <v>46274</v>
       </c>
-      <c r="S106" s="7" t="s">
-        <v>32</v>
+      <c r="S106" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -8426,16 +8426,16 @@
         <v>46238.48777921296</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I107" s="9">
         <v>46281</v>
@@ -8479,16 +8479,16 @@
         <v>46238.487780752315</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I108" s="5">
         <v>46281</v>
@@ -8532,16 +8532,16 @@
         <v>46238.4877812037</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I109" s="9">
         <v>46281</v>
@@ -8585,16 +8585,16 @@
         <v>46231.66672795139</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I110" s="5">
         <v>46281</v>
@@ -8615,7 +8615,7 @@
         <v>251</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>259</v>
@@ -8638,16 +8638,16 @@
         <v>46238.487785000005</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I111" s="9">
         <v>46281</v>
@@ -8691,16 +8691,16 @@
         <v>46231.66672108797</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I112" s="5">
         <v>46281</v>
@@ -8744,16 +8744,16 @@
         <v>46238.48779480324</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I113" s="9">
         <v>46281</v>
@@ -8797,16 +8797,16 @@
         <v>46231.66671467593</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I114" s="5">
         <v>46281</v>
@@ -8827,7 +8827,7 @@
         <v>251</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>259</v>
@@ -8850,16 +8850,16 @@
         <v>46231.66671130787</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I115" s="9">
         <v>46281</v>
@@ -8903,16 +8903,16 @@
         <v>46238.487792395834</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I116" s="5">
         <v>46281</v>
@@ -8956,16 +8956,16 @@
         <v>46238.487790949075</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I117" s="9">
         <v>46281</v>
@@ -9009,16 +9009,16 @@
         <v>46231.66670135417</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I118" s="5">
         <v>46281</v>
@@ -9039,7 +9039,7 @@
         <v>251</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>259</v>
@@ -9062,16 +9062,16 @@
         <v>46238.48779597222</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I119" s="9">
         <v>46281</v>
@@ -9115,16 +9115,16 @@
         <v>46231.66669519676</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I120" s="5">
         <v>46281</v>
@@ -9145,7 +9145,7 @@
         <v>251</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>259</v>
@@ -9168,16 +9168,16 @@
         <v>46231.66669142361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I121" s="9">
         <v>46281</v>
@@ -9198,7 +9198,7 @@
         <v>251</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>259</v>
@@ -9221,16 +9221,16 @@
         <v>46231.66668751158</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I122" s="5">
         <v>46281</v>
@@ -9251,7 +9251,7 @@
         <v>251</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>273</v>
@@ -9274,16 +9274,16 @@
         <v>46231.66668429398</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I123" s="9">
         <v>46281</v>
@@ -9304,7 +9304,7 @@
         <v>251</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>273</v>
@@ -9327,16 +9327,16 @@
         <v>46231.66667890047</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I124" s="5">
         <v>46281</v>
@@ -9357,7 +9357,7 @@
         <v>251</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>273</v>
@@ -9380,16 +9380,16 @@
         <v>46231.66666850694</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I125" s="9">
         <v>46281</v>
@@ -9410,7 +9410,7 @@
         <v>251</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>273</v>
@@ -9433,16 +9433,16 @@
         <v>46231.66667090278</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I126" s="5">
         <v>46281</v>
@@ -9463,7 +9463,7 @@
         <v>251</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>273</v>
@@ -9486,16 +9486,16 @@
         <v>46240.823163877314</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I127" s="9">
         <v>46281</v>
@@ -9539,16 +9539,16 @@
         <v>46240.82316032407</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I128" s="5">
         <v>46281</v>
@@ -9569,7 +9569,7 @@
         <v>251</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>273</v>
@@ -9592,16 +9592,16 @@
         <v>46240.8231571412</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I129" s="9">
         <v>46281</v>
@@ -9622,7 +9622,7 @@
         <v>251</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>273</v>
@@ -9645,16 +9645,16 @@
         <v>46240.823153680554</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I130" s="5">
         <v>46281</v>
@@ -9698,16 +9698,16 @@
         <v>46240.82315002315</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="I131" s="9">
         <v>46281</v>
@@ -9804,10 +9804,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I133" s="9">
         <v>46237</v>
@@ -9846,7 +9846,7 @@
         <v>0</v>
       </c>
       <c r="U133" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
@@ -9867,10 +9867,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I134" s="5">
         <v>46237</v>
@@ -9909,7 +9909,7 @@
         <v>0</v>
       </c>
       <c r="U134" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
@@ -9930,10 +9930,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I135" s="9">
         <v>46237</v>
@@ -9972,7 +9972,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -10082,7 +10082,7 @@
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -10097,7 +10097,7 @@
         <v>46231.66768597222</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10127,7 +10127,7 @@
         <v>301</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>304</v>
@@ -10150,7 +10150,7 @@
         <v>46231.66769336806</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -10180,7 +10180,7 @@
         <v>301</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>306</v>
@@ -10203,7 +10203,7 @@
         <v>46231.667685312495</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10233,7 +10233,7 @@
         <v>301</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>308</v>
@@ -10256,7 +10256,7 @@
         <v>46231.66768938657</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10286,7 +10286,7 @@
         <v>301</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>310</v>
@@ -10309,7 +10309,7 @@
         <v>46231.667695219905</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10339,7 +10339,7 @@
         <v>301</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>301</v>
@@ -10362,7 +10362,7 @@
         <v>46231.6676892824</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10392,7 +10392,7 @@
         <v>301</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>301</v>
@@ -10415,7 +10415,7 @@
         <v>46231.667685821754</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10445,7 +10445,7 @@
         <v>301</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>301</v>
@@ -10468,7 +10468,7 @@
         <v>46231.66768554398</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10498,7 +10498,7 @@
         <v>301</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P145" s="10" t="s">
         <v>301</v>
@@ -10521,7 +10521,7 @@
         <v>46231.6676859838</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10551,7 +10551,7 @@
         <v>301</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>301</v>
@@ -10574,7 +10574,7 @@
         <v>46231.66768939815</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10604,7 +10604,7 @@
         <v>301</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P147" s="10" t="s">
         <v>301</v>
@@ -10627,7 +10627,7 @@
         <v>46231.667693055555</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10657,7 +10657,7 @@
         <v>301</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>301</v>
@@ -10680,7 +10680,7 @@
         <v>46231.66769350694</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10710,7 +10710,7 @@
         <v>301</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>301</v>
@@ -10733,7 +10733,7 @@
         <v>46231.66769018519</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10763,7 +10763,7 @@
         <v>301</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>301</v>
@@ -10786,7 +10786,7 @@
         <v>46231.66768600694</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10816,7 +10816,7 @@
         <v>301</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>301</v>
@@ -10839,7 +10839,7 @@
         <v>46231.66768511574</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10869,7 +10869,7 @@
         <v>301</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>301</v>
@@ -10892,7 +10892,7 @@
         <v>46231.66771173611</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10922,7 +10922,7 @@
         <v>301</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P153" s="10" t="s">
         <v>301</v>
@@ -10945,7 +10945,7 @@
         <v>46231.66768918981</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10975,7 +10975,7 @@
         <v>301</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>301</v>
@@ -10998,7 +10998,7 @@
         <v>46231.66768920139</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -11028,7 +11028,7 @@
         <v>301</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>301</v>
@@ -11051,7 +11051,7 @@
         <v>46231.66768591435</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -11081,7 +11081,7 @@
         <v>301</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>301</v>
@@ -11104,7 +11104,7 @@
         <v>46231.66768583334</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -11134,7 +11134,7 @@
         <v>301</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>301</v>
@@ -11157,7 +11157,7 @@
         <v>46231.66768583334</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11187,7 +11187,7 @@
         <v>301</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>301</v>
@@ -11210,7 +11210,7 @@
         <v>46231.66768945602</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -11240,7 +11240,7 @@
         <v>301</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>301</v>
@@ -11263,7 +11263,7 @@
         <v>46231.66768604166</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11293,7 +11293,7 @@
         <v>301</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>301</v>
@@ -11316,7 +11316,7 @@
         <v>46231.66768939815</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11346,7 +11346,7 @@
         <v>301</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>301</v>
@@ -11369,7 +11369,7 @@
         <v>46231.66769310185</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11399,7 +11399,7 @@
         <v>301</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>301</v>
@@ -11470,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="U163" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -11485,7 +11485,7 @@
         <v>46238.48777972222</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11538,7 +11538,7 @@
         <v>46238.487781620366</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11591,7 +11591,7 @@
         <v>46238.487778553244</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11644,7 +11644,7 @@
         <v>46231.667831597224</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11697,7 +11697,7 @@
         <v>46231.667839699076</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11750,7 +11750,7 @@
         <v>46231.667835925924</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11803,7 +11803,7 @@
         <v>46231.667833680556</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11856,7 +11856,7 @@
         <v>46231.667830844905</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11909,7 +11909,7 @@
         <v>46231.66784657407</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11962,7 +11962,7 @@
         <v>46231.66782869213</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -12015,7 +12015,7 @@
         <v>46231.667833217594</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -12068,7 +12068,7 @@
         <v>46231.66783061343</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -12121,7 +12121,7 @@
         <v>46231.66784224537</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -12174,7 +12174,7 @@
         <v>46231.66783100694</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -12227,7 +12227,7 @@
         <v>46231.667828958336</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -12280,7 +12280,7 @@
         <v>46231.66783663194</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -12333,7 +12333,7 @@
         <v>46231.66783365741</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12386,7 +12386,7 @@
         <v>46231.66783075231</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12439,7 +12439,7 @@
         <v>46231.66782876157</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12492,7 +12492,7 @@
         <v>46231.66783196759</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12545,7 +12545,7 @@
         <v>46231.66783085648</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12598,7 +12598,7 @@
         <v>46231.6678306713</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12651,7 +12651,7 @@
         <v>46231.66784248843</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12704,7 +12704,7 @@
         <v>46231.667834085645</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12757,7 +12757,7 @@
         <v>46231.6678331713</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="U189" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
@@ -12873,7 +12873,7 @@
         <v>46231.66826131944</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12926,7 +12926,7 @@
         <v>46231.667989050926</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12979,7 +12979,7 @@
         <v>46231.6679641088</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -13032,7 +13032,7 @@
         <v>46231.66796936342</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -13085,7 +13085,7 @@
         <v>46231.66796449074</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -13138,7 +13138,7 @@
         <v>46231.66796210648</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -13191,7 +13191,7 @@
         <v>46231.66797386574</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -13244,7 +13244,7 @@
         <v>46231.66796228009</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -13297,7 +13297,7 @@
         <v>46231.66796244213</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -13350,7 +13350,7 @@
         <v>46231.66801194444</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -13403,7 +13403,7 @@
         <v>46231.668014675924</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13456,7 +13456,7 @@
         <v>46231.66801396991</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13509,7 +13509,7 @@
         <v>46231.66801421296</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13562,7 +13562,7 @@
         <v>46231.668014097224</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13615,7 +13615,7 @@
         <v>46231.66801686343</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13668,7 +13668,7 @@
         <v>46231.66801703704</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13721,7 +13721,7 @@
         <v>46231.668013946764</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13774,7 +13774,7 @@
         <v>46231.66801465278</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13827,7 +13827,7 @@
         <v>46231.66801458334</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13880,7 +13880,7 @@
         <v>46231.66796421296</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13933,7 +13933,7 @@
         <v>46231.6679640625</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13986,7 +13986,7 @@
         <v>46231.66796466435</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -14039,7 +14039,7 @@
         <v>46231.66796478009</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -14092,7 +14092,7 @@
         <v>46231.66796820602</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -14145,7 +14145,7 @@
         <v>46231.667986134256</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="U215" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
@@ -14261,7 +14261,7 @@
         <v>46231.66839868056</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -14314,7 +14314,7 @@
         <v>46238.48778229167</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -14367,7 +14367,7 @@
         <v>46231.668395995366</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -14420,7 +14420,7 @@
         <v>46231.66839239583</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14473,7 +14473,7 @@
         <v>46231.668395671295</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14526,7 +14526,7 @@
         <v>46231.66839586805</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14579,7 +14579,7 @@
         <v>46231.66839528935</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14632,7 +14632,7 @@
         <v>46231.66839170139</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
@@ -14685,7 +14685,7 @@
         <v>46231.66839528935</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
@@ -14738,7 +14738,7 @@
         <v>46231.66839199074</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
@@ -14791,7 +14791,7 @@
         <v>46231.668389108796</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
@@ -14844,7 +14844,7 @@
         <v>46231.668388935184</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
@@ -14897,7 +14897,7 @@
         <v>46231.66839212963</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
@@ -14950,7 +14950,7 @@
         <v>46231.66839202546</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
@@ -15003,7 +15003,7 @@
         <v>46231.66839535879</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
@@ -15056,7 +15056,7 @@
         <v>46231.66839859953</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
@@ -15109,7 +15109,7 @@
         <v>46231.668392141204</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -15162,7 +15162,7 @@
         <v>46231.66838898148</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
@@ -15215,7 +15215,7 @@
         <v>46231.66839825231</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
@@ -15268,7 +15268,7 @@
         <v>46231.668391851854</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
@@ -15321,7 +15321,7 @@
         <v>46231.668389583334</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
@@ -15374,7 +15374,7 @@
         <v>46231.668389074075</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15427,7 +15427,7 @@
         <v>46231.66838769676</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>26</v>
@@ -15480,7 +15480,7 @@
         <v>46231.6683890162</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15533,7 +15533,7 @@
         <v>46231.66838675926</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="T241" s="10"/>
       <c r="U241" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.25">
@@ -15643,7 +15643,7 @@
         <v>46231.66850771991</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>26</v>
@@ -15696,7 +15696,7 @@
         <v>46231.66851130787</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>26</v>
@@ -15749,7 +15749,7 @@
         <v>46231.66851420139</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>26</v>
@@ -15802,7 +15802,7 @@
         <v>46231.66851157407</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>26</v>
@@ -15855,7 +15855,7 @@
         <v>46231.66850605324</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>26</v>
@@ -15908,7 +15908,7 @@
         <v>46231.66851423611</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>26</v>
@@ -15961,7 +15961,7 @@
         <v>46231.66850797454</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>26</v>
@@ -16014,7 +16014,7 @@
         <v>46231.66850921296</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>26</v>
@@ -16067,7 +16067,7 @@
         <v>46231.668514537036</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F250" s="6" t="s">
         <v>26</v>
@@ -16120,7 +16120,7 @@
         <v>46231.66850494213</v>
       </c>
       <c r="E251" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F251" s="10" t="s">
         <v>26</v>
@@ -16173,7 +16173,7 @@
         <v>46231.6685083912</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F252" s="6" t="s">
         <v>26</v>
@@ -16226,7 +16226,7 @@
         <v>46231.66850829861</v>
       </c>
       <c r="E253" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F253" s="10" t="s">
         <v>26</v>
@@ -16279,7 +16279,7 @@
         <v>46231.668502939814</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F254" s="6" t="s">
         <v>26</v>
@@ -16332,7 +16332,7 @@
         <v>46231.66851447917</v>
       </c>
       <c r="E255" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F255" s="10" t="s">
         <v>26</v>
@@ -16385,7 +16385,7 @@
         <v>46231.668505520836</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>26</v>
@@ -16438,7 +16438,7 @@
         <v>46231.66850818287</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>26</v>
@@ -16491,7 +16491,7 @@
         <v>46231.66851451389</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>26</v>
@@ -16544,7 +16544,7 @@
         <v>46231.6685082176</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F259" s="10" t="s">
         <v>26</v>
@@ -16597,7 +16597,7 @@
         <v>46231.66850509259</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>26</v>
@@ -16650,7 +16650,7 @@
         <v>46231.66851416667</v>
       </c>
       <c r="E261" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F261" s="10" t="s">
         <v>26</v>
@@ -16703,7 +16703,7 @@
         <v>46231.66851125</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F262" s="6" t="s">
         <v>26</v>
@@ -16756,7 +16756,7 @@
         <v>46231.66851166666</v>
       </c>
       <c r="E263" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F263" s="10" t="s">
         <v>26</v>
@@ -16809,7 +16809,7 @@
         <v>46231.668511192125</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F264" s="6" t="s">
         <v>26</v>
@@ -16862,7 +16862,7 @@
         <v>46231.66850479167</v>
       </c>
       <c r="E265" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F265" s="10" t="s">
         <v>26</v>
@@ -16915,7 +16915,7 @@
         <v>46231.66851174769</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>26</v>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="T267" s="10"/>
       <c r="U267" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.25">
@@ -17025,7 +17025,7 @@
         <v>46231.6686428588</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>26</v>
@@ -17078,7 +17078,7 @@
         <v>46231.668646087965</v>
       </c>
       <c r="E269" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F269" s="10" t="s">
         <v>26</v>
@@ -17131,7 +17131,7 @@
         <v>46231.66864605324</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>26</v>
@@ -17184,7 +17184,7 @@
         <v>46231.66864655093</v>
       </c>
       <c r="E271" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F271" s="10" t="s">
         <v>26</v>
@@ -17237,7 +17237,7 @@
         <v>46231.668646261576</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>26</v>
@@ -17290,7 +17290,7 @@
         <v>46231.668647604165</v>
       </c>
       <c r="E273" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F273" s="10" t="s">
         <v>26</v>
@@ -17343,7 +17343,7 @@
         <v>46231.66865532407</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>26</v>
@@ -17396,7 +17396,7 @@
         <v>46231.66864230324</v>
       </c>
       <c r="E275" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F275" s="10" t="s">
         <v>26</v>
@@ -17449,7 +17449,7 @@
         <v>46231.66865127315</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F276" s="6" t="s">
         <v>26</v>
@@ -17502,7 +17502,7 @@
         <v>46231.66864081018</v>
       </c>
       <c r="E277" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F277" s="10" t="s">
         <v>26</v>
@@ -17555,7 +17555,7 @@
         <v>46231.668640868054</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F278" s="6" t="s">
         <v>26</v>
@@ -17608,7 +17608,7 @@
         <v>46231.66864261574</v>
       </c>
       <c r="E279" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F279" s="10" t="s">
         <v>26</v>
@@ -17661,7 +17661,7 @@
         <v>46231.668640648146</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F280" s="6" t="s">
         <v>26</v>
@@ -17714,7 +17714,7 @@
         <v>46231.668646122685</v>
       </c>
       <c r="E281" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F281" s="10" t="s">
         <v>26</v>
@@ -17767,7 +17767,7 @@
         <v>46231.66864037037</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F282" s="6" t="s">
         <v>26</v>
@@ -17820,7 +17820,7 @@
         <v>46231.66863724537</v>
       </c>
       <c r="E283" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F283" s="10" t="s">
         <v>26</v>
@@ -17873,7 +17873,7 @@
         <v>46231.66864261574</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>26</v>
@@ -17926,7 +17926,7 @@
         <v>46231.66864297454</v>
       </c>
       <c r="E285" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F285" s="10" t="s">
         <v>26</v>
@@ -17979,7 +17979,7 @@
         <v>46231.66863702546</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F286" s="6" t="s">
         <v>26</v>
@@ -18032,7 +18032,7 @@
         <v>46231.66864275463</v>
       </c>
       <c r="E287" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F287" s="10" t="s">
         <v>26</v>
@@ -18085,7 +18085,7 @@
         <v>46231.66864267361</v>
       </c>
       <c r="E288" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F288" s="6" t="s">
         <v>26</v>
@@ -18138,7 +18138,7 @@
         <v>46231.66863684027</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F289" s="10" t="s">
         <v>26</v>
@@ -18191,7 +18191,7 @@
         <v>46231.66864052083</v>
       </c>
       <c r="E290" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F290" s="6" t="s">
         <v>26</v>
@@ -18244,7 +18244,7 @@
         <v>46231.66864081018</v>
       </c>
       <c r="E291" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F291" s="10" t="s">
         <v>26</v>
@@ -18297,7 +18297,7 @@
         <v>46231.668645937505</v>
       </c>
       <c r="E292" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F292" s="6" t="s">
         <v>26</v>
@@ -18392,7 +18392,7 @@
       </c>
       <c r="T293" s="10"/>
       <c r="U293" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="294" spans="1:21" x14ac:dyDescent="0.25">
@@ -18407,7 +18407,7 @@
         <v>46231.66880484954</v>
       </c>
       <c r="E294" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F294" s="6" t="s">
         <v>26</v>
@@ -18437,7 +18437,7 @@
         <v>489</v>
       </c>
       <c r="O294" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P294" s="6" t="s">
         <v>489</v>
@@ -18460,7 +18460,7 @@
         <v>46231.66880197916</v>
       </c>
       <c r="E295" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>26</v>
@@ -18490,7 +18490,7 @@
         <v>489</v>
       </c>
       <c r="O295" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P295" s="10" t="s">
         <v>489</v>
@@ -18513,7 +18513,7 @@
         <v>46231.66881472222</v>
       </c>
       <c r="E296" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F296" s="6" t="s">
         <v>26</v>
@@ -18543,7 +18543,7 @@
         <v>489</v>
       </c>
       <c r="O296" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P296" s="6" t="s">
         <v>489</v>
@@ -18566,7 +18566,7 @@
         <v>46231.66881128472</v>
       </c>
       <c r="E297" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F297" s="10" t="s">
         <v>26</v>
@@ -18596,7 +18596,7 @@
         <v>489</v>
       </c>
       <c r="O297" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P297" s="10" t="s">
         <v>489</v>
@@ -18619,7 +18619,7 @@
         <v>46231.66880478009</v>
       </c>
       <c r="E298" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F298" s="6" t="s">
         <v>26</v>
@@ -18649,7 +18649,7 @@
         <v>489</v>
       </c>
       <c r="O298" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P298" s="6" t="s">
         <v>489</v>
@@ -18672,7 +18672,7 @@
         <v>46231.668812268515</v>
       </c>
       <c r="E299" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F299" s="10" t="s">
         <v>26</v>
@@ -18702,7 +18702,7 @@
         <v>489</v>
       </c>
       <c r="O299" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P299" s="10" t="s">
         <v>489</v>
@@ -18725,7 +18725,7 @@
         <v>46231.66880841435</v>
       </c>
       <c r="E300" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F300" s="6" t="s">
         <v>26</v>
@@ -18755,7 +18755,7 @@
         <v>489</v>
       </c>
       <c r="O300" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P300" s="6" t="s">
         <v>489</v>
@@ -18778,7 +18778,7 @@
         <v>46231.66880237269</v>
       </c>
       <c r="E301" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F301" s="10" t="s">
         <v>26</v>
@@ -18808,7 +18808,7 @@
         <v>489</v>
       </c>
       <c r="O301" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P301" s="10" t="s">
         <v>489</v>
@@ -18831,7 +18831,7 @@
         <v>46231.66881479167</v>
       </c>
       <c r="E302" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F302" s="6" t="s">
         <v>26</v>
@@ -18861,7 +18861,7 @@
         <v>489</v>
       </c>
       <c r="O302" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P302" s="6" t="s">
         <v>489</v>
@@ -18884,7 +18884,7 @@
         <v>46231.66880479167</v>
       </c>
       <c r="E303" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F303" s="10" t="s">
         <v>26</v>
@@ -18914,7 +18914,7 @@
         <v>489</v>
       </c>
       <c r="O303" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P303" s="10" t="s">
         <v>489</v>
@@ -18937,7 +18937,7 @@
         <v>46231.66880506944</v>
       </c>
       <c r="E304" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F304" s="6" t="s">
         <v>26</v>
@@ -18990,7 +18990,7 @@
         <v>46231.668814432865</v>
       </c>
       <c r="E305" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F305" s="10" t="s">
         <v>26</v>
@@ -19020,7 +19020,7 @@
         <v>489</v>
       </c>
       <c r="O305" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P305" s="10" t="s">
         <v>489</v>
@@ -19043,7 +19043,7 @@
         <v>46231.66880857639</v>
       </c>
       <c r="E306" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F306" s="6" t="s">
         <v>26</v>
@@ -19073,7 +19073,7 @@
         <v>489</v>
       </c>
       <c r="O306" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P306" s="6" t="s">
         <v>489</v>
@@ -19096,7 +19096,7 @@
         <v>46231.66880244213</v>
       </c>
       <c r="E307" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F307" s="10" t="s">
         <v>26</v>
@@ -19126,7 +19126,7 @@
         <v>489</v>
       </c>
       <c r="O307" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P307" s="10" t="s">
         <v>489</v>
@@ -19149,7 +19149,7 @@
         <v>46231.6688147338</v>
       </c>
       <c r="E308" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F308" s="6" t="s">
         <v>26</v>
@@ -19202,7 +19202,7 @@
         <v>46231.66880950231</v>
       </c>
       <c r="E309" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F309" s="10" t="s">
         <v>26</v>
@@ -19232,7 +19232,7 @@
         <v>489</v>
       </c>
       <c r="O309" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P309" s="10" t="s">
         <v>489</v>
@@ -19255,7 +19255,7 @@
         <v>46231.668803611115</v>
       </c>
       <c r="E310" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F310" s="6" t="s">
         <v>26</v>
@@ -19285,7 +19285,7 @@
         <v>489</v>
       </c>
       <c r="O310" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P310" s="6" t="s">
         <v>489</v>
@@ -19308,7 +19308,7 @@
         <v>46231.66881472222</v>
       </c>
       <c r="E311" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F311" s="10" t="s">
         <v>26</v>
@@ -19338,7 +19338,7 @@
         <v>489</v>
       </c>
       <c r="O311" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P311" s="10" t="s">
         <v>489</v>
@@ -19361,7 +19361,7 @@
         <v>46231.66880457176</v>
       </c>
       <c r="E312" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F312" s="6" t="s">
         <v>26</v>
@@ -19391,7 +19391,7 @@
         <v>489</v>
       </c>
       <c r="O312" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P312" s="6" t="s">
         <v>489</v>
@@ -19414,7 +19414,7 @@
         <v>46231.66881471065</v>
       </c>
       <c r="E313" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F313" s="10" t="s">
         <v>26</v>
@@ -19444,7 +19444,7 @@
         <v>489</v>
       </c>
       <c r="O313" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P313" s="10" t="s">
         <v>489</v>
@@ -19467,7 +19467,7 @@
         <v>46231.668809305556</v>
       </c>
       <c r="E314" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F314" s="6" t="s">
         <v>26</v>
@@ -19497,7 +19497,7 @@
         <v>489</v>
       </c>
       <c r="O314" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P314" s="6" t="s">
         <v>489</v>
@@ -19520,7 +19520,7 @@
         <v>46231.66880247685</v>
       </c>
       <c r="E315" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F315" s="10" t="s">
         <v>26</v>
@@ -19550,7 +19550,7 @@
         <v>489</v>
       </c>
       <c r="O315" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P315" s="10" t="s">
         <v>489</v>
@@ -19573,7 +19573,7 @@
         <v>46231.66881210648</v>
       </c>
       <c r="E316" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F316" s="6" t="s">
         <v>26</v>
@@ -19603,7 +19603,7 @@
         <v>489</v>
       </c>
       <c r="O316" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P316" s="6" t="s">
         <v>489</v>
@@ -19626,7 +19626,7 @@
         <v>46231.668805208334</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F317" s="10" t="s">
         <v>26</v>
@@ -19656,7 +19656,7 @@
         <v>489</v>
       </c>
       <c r="O317" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P317" s="10" t="s">
         <v>489</v>
@@ -19679,7 +19679,7 @@
         <v>46231.668802141205</v>
       </c>
       <c r="E318" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F318" s="6" t="s">
         <v>26</v>
@@ -19709,7 +19709,7 @@
         <v>489</v>
       </c>
       <c r="O318" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P318" s="6" t="s">
         <v>489</v>
@@ -19827,7 +19827,7 @@
         <v>0</v>
       </c>
       <c r="U320" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="321" spans="1:21" x14ac:dyDescent="0.25">
@@ -19842,7 +19842,7 @@
         <v>46231.66971627314</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F321" s="10" t="s">
         <v>26</v>
@@ -19895,7 +19895,7 @@
         <v>46231.66971195602</v>
       </c>
       <c r="E322" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F322" s="6" t="s">
         <v>26</v>
@@ -19948,7 +19948,7 @@
         <v>46231.66970780093</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F323" s="10" t="s">
         <v>26</v>
@@ -20001,7 +20001,7 @@
         <v>46231.669704722226</v>
       </c>
       <c r="E324" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F324" s="6" t="s">
         <v>26</v>
@@ -20054,7 +20054,7 @@
         <v>46231.6697007176</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F325" s="10" t="s">
         <v>26</v>
@@ -20107,7 +20107,7 @@
         <v>46231.66969769676</v>
       </c>
       <c r="E326" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F326" s="6" t="s">
         <v>26</v>
@@ -20160,7 +20160,7 @@
         <v>46231.66969472222</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F327" s="10" t="s">
         <v>26</v>
@@ -20213,7 +20213,7 @@
         <v>46231.669691689814</v>
       </c>
       <c r="E328" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F328" s="6" t="s">
         <v>26</v>
@@ -20266,7 +20266,7 @@
         <v>46231.66968831018</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F329" s="10" t="s">
         <v>26</v>
@@ -20319,7 +20319,7 @@
         <v>46231.66968530093</v>
       </c>
       <c r="E330" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F330" s="6" t="s">
         <v>26</v>
@@ -20372,7 +20372,7 @@
         <v>46231.66968244213</v>
       </c>
       <c r="E331" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F331" s="10" t="s">
         <v>26</v>
@@ -20425,7 +20425,7 @@
         <v>46231.669678935184</v>
       </c>
       <c r="E332" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F332" s="6" t="s">
         <v>26</v>
@@ -20478,7 +20478,7 @@
         <v>46231.669675763886</v>
       </c>
       <c r="E333" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F333" s="10" t="s">
         <v>26</v>
@@ -20531,7 +20531,7 @@
         <v>46231.669672777774</v>
       </c>
       <c r="E334" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F334" s="6" t="s">
         <v>26</v>
@@ -20584,7 +20584,7 @@
         <v>46231.66966976852</v>
       </c>
       <c r="E335" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F335" s="10" t="s">
         <v>26</v>
@@ -20637,7 +20637,7 @@
         <v>46231.66966627315</v>
       </c>
       <c r="E336" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F336" s="6" t="s">
         <v>26</v>
@@ -20690,7 +20690,7 @@
         <v>46231.66966341435</v>
       </c>
       <c r="E337" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F337" s="10" t="s">
         <v>26</v>
@@ -20743,7 +20743,7 @@
         <v>46231.669660671294</v>
       </c>
       <c r="E338" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F338" s="6" t="s">
         <v>26</v>
@@ -20796,7 +20796,7 @@
         <v>46231.66965815972</v>
       </c>
       <c r="E339" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F339" s="10" t="s">
         <v>26</v>
@@ -20849,7 +20849,7 @@
         <v>46231.669653634264</v>
       </c>
       <c r="E340" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F340" s="6" t="s">
         <v>26</v>
@@ -20902,7 +20902,7 @@
         <v>46231.669650173615</v>
       </c>
       <c r="E341" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F341" s="10" t="s">
         <v>26</v>
@@ -20955,7 +20955,7 @@
         <v>46231.66964695602</v>
       </c>
       <c r="E342" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F342" s="6" t="s">
         <v>26</v>
@@ -21008,7 +21008,7 @@
         <v>46231.669632986115</v>
       </c>
       <c r="E343" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F343" s="10" t="s">
         <v>26</v>
@@ -21061,7 +21061,7 @@
         <v>46231.66963234954</v>
       </c>
       <c r="E344" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F344" s="6" t="s">
         <v>26</v>
@@ -21114,7 +21114,7 @@
         <v>46231.66963550926</v>
       </c>
       <c r="E345" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F345" s="10" t="s">
         <v>26</v>
@@ -21215,7 +21215,7 @@
         <v>0</v>
       </c>
       <c r="U346" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.25">
@@ -21230,7 +21230,7 @@
         <v>46231.670200057866</v>
       </c>
       <c r="E347" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F347" s="10" t="s">
         <v>26</v>
@@ -21260,7 +21260,7 @@
         <v>555</v>
       </c>
       <c r="O347" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P347" s="10" t="s">
         <v>555</v>
@@ -21283,7 +21283,7 @@
         <v>46231.66998844907</v>
       </c>
       <c r="E348" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F348" s="6" t="s">
         <v>26</v>
@@ -21313,7 +21313,7 @@
         <v>555</v>
       </c>
       <c r="O348" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P348" s="6" t="s">
         <v>559</v>
@@ -21336,7 +21336,7 @@
         <v>46231.66998445602</v>
       </c>
       <c r="E349" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F349" s="10" t="s">
         <v>26</v>
@@ -21366,7 +21366,7 @@
         <v>555</v>
       </c>
       <c r="O349" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P349" s="10" t="s">
         <v>561</v>
@@ -21389,7 +21389,7 @@
         <v>46231.669980046296</v>
       </c>
       <c r="E350" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F350" s="6" t="s">
         <v>26</v>
@@ -21419,7 +21419,7 @@
         <v>555</v>
       </c>
       <c r="O350" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P350" s="6" t="s">
         <v>561</v>
@@ -21442,7 +21442,7 @@
         <v>46231.66997524306</v>
       </c>
       <c r="E351" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F351" s="10" t="s">
         <v>26</v>
@@ -21472,7 +21472,7 @@
         <v>555</v>
       </c>
       <c r="O351" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P351" s="10" t="s">
         <v>561</v>
@@ -21495,7 +21495,7 @@
         <v>46231.66997137731</v>
       </c>
       <c r="E352" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F352" s="6" t="s">
         <v>26</v>
@@ -21525,7 +21525,7 @@
         <v>555</v>
       </c>
       <c r="O352" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P352" s="6" t="s">
         <v>561</v>
@@ -21548,7 +21548,7 @@
         <v>46231.66996653935</v>
       </c>
       <c r="E353" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F353" s="10" t="s">
         <v>26</v>
@@ -21578,7 +21578,7 @@
         <v>555</v>
       </c>
       <c r="O353" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P353" s="10" t="s">
         <v>561</v>
@@ -21601,7 +21601,7 @@
         <v>46231.669961064814</v>
       </c>
       <c r="E354" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F354" s="6" t="s">
         <v>26</v>
@@ -21631,7 +21631,7 @@
         <v>555</v>
       </c>
       <c r="O354" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P354" s="6" t="s">
         <v>561</v>
@@ -21654,7 +21654,7 @@
         <v>46231.66995664352</v>
       </c>
       <c r="E355" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F355" s="10" t="s">
         <v>26</v>
@@ -21684,7 +21684,7 @@
         <v>555</v>
       </c>
       <c r="O355" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P355" s="10" t="s">
         <v>559</v>
@@ -21707,7 +21707,7 @@
         <v>46231.669952916665</v>
       </c>
       <c r="E356" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F356" s="6" t="s">
         <v>26</v>
@@ -21737,7 +21737,7 @@
         <v>555</v>
       </c>
       <c r="O356" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P356" s="6" t="s">
         <v>561</v>
@@ -21760,7 +21760,7 @@
         <v>46231.66994847222</v>
       </c>
       <c r="E357" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F357" s="10" t="s">
         <v>26</v>
@@ -21790,7 +21790,7 @@
         <v>555</v>
       </c>
       <c r="O357" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P357" s="10" t="s">
         <v>561</v>
@@ -21813,7 +21813,7 @@
         <v>46231.66994402777</v>
       </c>
       <c r="E358" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F358" s="6" t="s">
         <v>26</v>
@@ -21843,7 +21843,7 @@
         <v>555</v>
       </c>
       <c r="O358" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P358" s="6" t="s">
         <v>559</v>
@@ -21866,7 +21866,7 @@
         <v>46231.66994043981</v>
       </c>
       <c r="E359" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F359" s="10" t="s">
         <v>26</v>
@@ -21896,7 +21896,7 @@
         <v>555</v>
       </c>
       <c r="O359" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P359" s="10" t="s">
         <v>559</v>
@@ -21919,7 +21919,7 @@
         <v>46231.66993686343</v>
       </c>
       <c r="E360" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F360" s="6" t="s">
         <v>26</v>
@@ -21949,7 +21949,7 @@
         <v>555</v>
       </c>
       <c r="O360" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P360" s="6" t="s">
         <v>559</v>
@@ -21972,7 +21972,7 @@
         <v>46231.6699325</v>
       </c>
       <c r="E361" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F361" s="10" t="s">
         <v>26</v>
@@ -22002,7 +22002,7 @@
         <v>555</v>
       </c>
       <c r="O361" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P361" s="10" t="s">
         <v>559</v>
@@ -22025,7 +22025,7 @@
         <v>46231.66992857639</v>
       </c>
       <c r="E362" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F362" s="6" t="s">
         <v>26</v>
@@ -22055,7 +22055,7 @@
         <v>555</v>
       </c>
       <c r="O362" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P362" s="6" t="s">
         <v>575</v>
@@ -22078,7 +22078,7 @@
         <v>46231.66992512731</v>
       </c>
       <c r="E363" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F363" s="10" t="s">
         <v>26</v>
@@ -22108,7 +22108,7 @@
         <v>555</v>
       </c>
       <c r="O363" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P363" s="10" t="s">
         <v>575</v>
@@ -22131,7 +22131,7 @@
         <v>46231.669921064815</v>
       </c>
       <c r="E364" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F364" s="6" t="s">
         <v>26</v>
@@ -22161,7 +22161,7 @@
         <v>555</v>
       </c>
       <c r="O364" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P364" s="6" t="s">
         <v>578</v>
@@ -22184,7 +22184,7 @@
         <v>46231.6699174074</v>
       </c>
       <c r="E365" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F365" s="10" t="s">
         <v>26</v>
@@ -22214,7 +22214,7 @@
         <v>555</v>
       </c>
       <c r="O365" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P365" s="10" t="s">
         <v>578</v>
@@ -22237,7 +22237,7 @@
         <v>46231.66991390046</v>
       </c>
       <c r="E366" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F366" s="6" t="s">
         <v>26</v>
@@ -22267,7 +22267,7 @@
         <v>555</v>
       </c>
       <c r="O366" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P366" s="6" t="s">
         <v>578</v>
@@ -22290,7 +22290,7 @@
         <v>46231.66990978009</v>
       </c>
       <c r="E367" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F367" s="10" t="s">
         <v>26</v>
@@ -22320,7 +22320,7 @@
         <v>555</v>
       </c>
       <c r="O367" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P367" s="10" t="s">
         <v>578</v>
@@ -22343,7 +22343,7 @@
         <v>46231.66990606481</v>
       </c>
       <c r="E368" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F368" s="6" t="s">
         <v>26</v>
@@ -22373,7 +22373,7 @@
         <v>555</v>
       </c>
       <c r="O368" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P368" s="6" t="s">
         <v>578</v>
@@ -22396,7 +22396,7 @@
         <v>46231.66989173611</v>
       </c>
       <c r="E369" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F369" s="10" t="s">
         <v>26</v>
@@ -22426,7 +22426,7 @@
         <v>555</v>
       </c>
       <c r="O369" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P369" s="10" t="s">
         <v>575</v>
@@ -22449,7 +22449,7 @@
         <v>46231.66989118056</v>
       </c>
       <c r="E370" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F370" s="6" t="s">
         <v>26</v>
@@ -22479,7 +22479,7 @@
         <v>555</v>
       </c>
       <c r="O370" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P370" s="6" t="s">
         <v>575</v>
@@ -22502,7 +22502,7 @@
         <v>46231.669893796294</v>
       </c>
       <c r="E371" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F371" s="10" t="s">
         <v>26</v>
@@ -22532,7 +22532,7 @@
         <v>555</v>
       </c>
       <c r="O371" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P371" s="10" t="s">
         <v>578</v>
@@ -22603,7 +22603,7 @@
         <v>0</v>
       </c>
       <c r="U372" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="373" spans="1:21" x14ac:dyDescent="0.25">
@@ -22618,7 +22618,7 @@
         <v>46231.67078247685</v>
       </c>
       <c r="E373" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F373" s="10" t="s">
         <v>26</v>
@@ -22671,7 +22671,7 @@
         <v>46231.67077917824</v>
       </c>
       <c r="E374" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F374" s="6" t="s">
         <v>26</v>
@@ -22701,7 +22701,7 @@
         <v>587</v>
       </c>
       <c r="O374" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P374" s="6" t="s">
         <v>591</v>
@@ -22724,7 +22724,7 @@
         <v>46231.6707759375</v>
       </c>
       <c r="E375" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F375" s="10" t="s">
         <v>26</v>
@@ -22754,7 +22754,7 @@
         <v>587</v>
       </c>
       <c r="O375" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P375" s="10" t="s">
         <v>591</v>
@@ -22777,7 +22777,7 @@
         <v>46231.67077253472</v>
       </c>
       <c r="E376" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F376" s="6" t="s">
         <v>26</v>
@@ -22807,7 +22807,7 @@
         <v>587</v>
       </c>
       <c r="O376" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P376" s="6" t="s">
         <v>591</v>
@@ -22830,7 +22830,7 @@
         <v>46231.67076925926</v>
       </c>
       <c r="E377" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F377" s="10" t="s">
         <v>26</v>
@@ -22860,7 +22860,7 @@
         <v>587</v>
       </c>
       <c r="O377" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P377" s="10" t="s">
         <v>591</v>
@@ -22883,7 +22883,7 @@
         <v>46231.670765393515</v>
       </c>
       <c r="E378" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F378" s="6" t="s">
         <v>26</v>
@@ -22913,7 +22913,7 @@
         <v>587</v>
       </c>
       <c r="O378" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P378" s="6" t="s">
         <v>589</v>
@@ -22936,7 +22936,7 @@
         <v>46231.6707622338</v>
       </c>
       <c r="E379" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F379" s="10" t="s">
         <v>26</v>
@@ -22966,7 +22966,7 @@
         <v>587</v>
       </c>
       <c r="O379" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P379" s="10" t="s">
         <v>589</v>
@@ -22989,7 +22989,7 @@
         <v>46231.67075878472</v>
       </c>
       <c r="E380" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F380" s="6" t="s">
         <v>26</v>
@@ -23019,7 +23019,7 @@
         <v>587</v>
       </c>
       <c r="O380" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P380" s="6" t="s">
         <v>591</v>
@@ -23042,7 +23042,7 @@
         <v>46231.670755451385</v>
       </c>
       <c r="E381" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F381" s="10" t="s">
         <v>26</v>
@@ -23072,7 +23072,7 @@
         <v>587</v>
       </c>
       <c r="O381" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P381" s="10" t="s">
         <v>591</v>
@@ -23095,7 +23095,7 @@
         <v>46231.67075229167</v>
       </c>
       <c r="E382" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F382" s="6" t="s">
         <v>26</v>
@@ -23125,7 +23125,7 @@
         <v>587</v>
       </c>
       <c r="O382" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P382" s="6" t="s">
         <v>591</v>
@@ -23148,7 +23148,7 @@
         <v>46231.67074930556</v>
       </c>
       <c r="E383" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F383" s="10" t="s">
         <v>26</v>
@@ -23178,7 +23178,7 @@
         <v>587</v>
       </c>
       <c r="O383" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P383" s="10" t="s">
         <v>591</v>
@@ -23201,7 +23201,7 @@
         <v>46231.67074609954</v>
       </c>
       <c r="E384" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F384" s="6" t="s">
         <v>26</v>
@@ -23231,7 +23231,7 @@
         <v>587</v>
       </c>
       <c r="O384" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P384" s="6" t="s">
         <v>589</v>
@@ -23254,7 +23254,7 @@
         <v>46231.67074238426</v>
       </c>
       <c r="E385" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F385" s="10" t="s">
         <v>26</v>
@@ -23284,7 +23284,7 @@
         <v>587</v>
       </c>
       <c r="O385" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P385" s="10" t="s">
         <v>591</v>
@@ -23307,7 +23307,7 @@
         <v>46231.670739340276</v>
       </c>
       <c r="E386" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F386" s="6" t="s">
         <v>26</v>
@@ -23337,7 +23337,7 @@
         <v>587</v>
       </c>
       <c r="O386" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P386" s="6" t="s">
         <v>591</v>
@@ -23360,7 +23360,7 @@
         <v>46231.67073607639</v>
       </c>
       <c r="E387" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F387" s="10" t="s">
         <v>26</v>
@@ -23390,7 +23390,7 @@
         <v>587</v>
       </c>
       <c r="O387" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P387" s="10" t="s">
         <v>591</v>
@@ -23413,7 +23413,7 @@
         <v>46231.67073236111</v>
       </c>
       <c r="E388" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F388" s="6" t="s">
         <v>26</v>
@@ -23443,7 +23443,7 @@
         <v>587</v>
       </c>
       <c r="O388" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P388" s="6" t="s">
         <v>606</v>
@@ -23466,7 +23466,7 @@
         <v>46231.67072928241</v>
       </c>
       <c r="E389" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F389" s="10" t="s">
         <v>26</v>
@@ -23496,7 +23496,7 @@
         <v>587</v>
       </c>
       <c r="O389" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P389" s="10" t="s">
         <v>608</v>
@@ -23519,7 +23519,7 @@
         <v>46231.67072601852</v>
       </c>
       <c r="E390" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F390" s="6" t="s">
         <v>26</v>
@@ -23549,7 +23549,7 @@
         <v>587</v>
       </c>
       <c r="O390" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P390" s="6" t="s">
         <v>608</v>
@@ -23572,7 +23572,7 @@
         <v>46231.67072258102</v>
       </c>
       <c r="E391" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F391" s="10" t="s">
         <v>26</v>
@@ -23602,7 +23602,7 @@
         <v>587</v>
       </c>
       <c r="O391" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P391" s="10" t="s">
         <v>606</v>
@@ -23625,7 +23625,7 @@
         <v>46231.67071851852</v>
       </c>
       <c r="E392" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F392" s="6" t="s">
         <v>26</v>
@@ -23655,7 +23655,7 @@
         <v>587</v>
       </c>
       <c r="O392" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P392" s="6" t="s">
         <v>608</v>
@@ -23678,7 +23678,7 @@
         <v>46231.67071464121</v>
       </c>
       <c r="E393" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F393" s="10" t="s">
         <v>26</v>
@@ -23708,7 +23708,7 @@
         <v>587</v>
       </c>
       <c r="O393" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P393" s="10" t="s">
         <v>606</v>
@@ -23731,7 +23731,7 @@
         <v>46231.67071099537</v>
       </c>
       <c r="E394" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F394" s="6" t="s">
         <v>26</v>
@@ -23761,7 +23761,7 @@
         <v>587</v>
       </c>
       <c r="O394" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P394" s="6" t="s">
         <v>606</v>
@@ -23784,7 +23784,7 @@
         <v>46231.67070591435</v>
       </c>
       <c r="E395" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F395" s="10" t="s">
         <v>26</v>
@@ -23814,7 +23814,7 @@
         <v>587</v>
       </c>
       <c r="O395" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P395" s="10" t="s">
         <v>608</v>
@@ -23837,7 +23837,7 @@
         <v>46231.67069403935</v>
       </c>
       <c r="E396" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F396" s="6" t="s">
         <v>26</v>
@@ -23867,7 +23867,7 @@
         <v>587</v>
       </c>
       <c r="O396" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P396" s="6" t="s">
         <v>606</v>
@@ -23890,7 +23890,7 @@
         <v>46231.670696319445</v>
       </c>
       <c r="E397" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F397" s="10" t="s">
         <v>26</v>
@@ -23920,7 +23920,7 @@
         <v>587</v>
       </c>
       <c r="O397" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P397" s="10" t="s">
         <v>606</v>
@@ -23991,7 +23991,7 @@
         <v>0</v>
       </c>
       <c r="U398" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="399" spans="1:21" x14ac:dyDescent="0.25">
@@ -24006,7 +24006,7 @@
         <v>46231.67106579861</v>
       </c>
       <c r="E399" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F399" s="10" t="s">
         <v>26</v>
@@ -24036,7 +24036,7 @@
         <v>618</v>
       </c>
       <c r="O399" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P399" s="10" t="s">
         <v>621</v>
@@ -24059,7 +24059,7 @@
         <v>46231.671062407404</v>
       </c>
       <c r="E400" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F400" s="6" t="s">
         <v>26</v>
@@ -24089,7 +24089,7 @@
         <v>618</v>
       </c>
       <c r="O400" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P400" s="6" t="s">
         <v>623</v>
@@ -24112,7 +24112,7 @@
         <v>46231.67105903935</v>
       </c>
       <c r="E401" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F401" s="10" t="s">
         <v>26</v>
@@ -24142,7 +24142,7 @@
         <v>618</v>
       </c>
       <c r="O401" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P401" s="10" t="s">
         <v>625</v>
@@ -24165,7 +24165,7 @@
         <v>46231.67105518519</v>
       </c>
       <c r="E402" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F402" s="6" t="s">
         <v>26</v>
@@ -24195,7 +24195,7 @@
         <v>618</v>
       </c>
       <c r="O402" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P402" s="6" t="s">
         <v>618</v>
@@ -24218,7 +24218,7 @@
         <v>46231.671052025464</v>
       </c>
       <c r="E403" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F403" s="10" t="s">
         <v>26</v>
@@ -24248,7 +24248,7 @@
         <v>618</v>
       </c>
       <c r="O403" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P403" s="10" t="s">
         <v>618</v>
@@ -24271,7 +24271,7 @@
         <v>46231.67104925926</v>
       </c>
       <c r="E404" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F404" s="6" t="s">
         <v>26</v>
@@ -24301,7 +24301,7 @@
         <v>618</v>
       </c>
       <c r="O404" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P404" s="6" t="s">
         <v>618</v>
@@ -24324,7 +24324,7 @@
         <v>46231.67104619213</v>
       </c>
       <c r="E405" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F405" s="10" t="s">
         <v>26</v>
@@ -24354,7 +24354,7 @@
         <v>618</v>
       </c>
       <c r="O405" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P405" s="10" t="s">
         <v>618</v>
@@ -24377,7 +24377,7 @@
         <v>46231.67104260417</v>
       </c>
       <c r="E406" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F406" s="6" t="s">
         <v>26</v>
@@ -24407,7 +24407,7 @@
         <v>618</v>
       </c>
       <c r="O406" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P406" s="6" t="s">
         <v>618</v>
@@ -24430,7 +24430,7 @@
         <v>46231.67103974537</v>
       </c>
       <c r="E407" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F407" s="10" t="s">
         <v>26</v>
@@ -24460,7 +24460,7 @@
         <v>618</v>
       </c>
       <c r="O407" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P407" s="10" t="s">
         <v>618</v>
@@ -24483,7 +24483,7 @@
         <v>46231.67103653935</v>
       </c>
       <c r="E408" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F408" s="6" t="s">
         <v>26</v>
@@ -24513,7 +24513,7 @@
         <v>618</v>
       </c>
       <c r="O408" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P408" s="6" t="s">
         <v>618</v>
@@ -24536,7 +24536,7 @@
         <v>46231.671033182865</v>
       </c>
       <c r="E409" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F409" s="10" t="s">
         <v>26</v>
@@ -24566,7 +24566,7 @@
         <v>618</v>
       </c>
       <c r="O409" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P409" s="10" t="s">
         <v>618</v>
@@ -24589,7 +24589,7 @@
         <v>46231.67103011574</v>
       </c>
       <c r="E410" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F410" s="6" t="s">
         <v>26</v>
@@ -24619,7 +24619,7 @@
         <v>618</v>
       </c>
       <c r="O410" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P410" s="6" t="s">
         <v>618</v>
@@ -24642,7 +24642,7 @@
         <v>46231.67102701389</v>
       </c>
       <c r="E411" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F411" s="10" t="s">
         <v>26</v>
@@ -24672,7 +24672,7 @@
         <v>618</v>
       </c>
       <c r="O411" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P411" s="10" t="s">
         <v>618</v>
@@ -24695,7 +24695,7 @@
         <v>46231.671023993054</v>
       </c>
       <c r="E412" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F412" s="6" t="s">
         <v>26</v>
@@ -24725,7 +24725,7 @@
         <v>618</v>
       </c>
       <c r="O412" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P412" s="6" t="s">
         <v>618</v>
@@ -24748,7 +24748,7 @@
         <v>46231.67102047453</v>
       </c>
       <c r="E413" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F413" s="10" t="s">
         <v>26</v>
@@ -24778,7 +24778,7 @@
         <v>618</v>
       </c>
       <c r="O413" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P413" s="10" t="s">
         <v>618</v>
@@ -24801,7 +24801,7 @@
         <v>46231.67101741898</v>
       </c>
       <c r="E414" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F414" s="6" t="s">
         <v>26</v>
@@ -24831,7 +24831,7 @@
         <v>618</v>
       </c>
       <c r="O414" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P414" s="6" t="s">
         <v>618</v>
@@ -24854,7 +24854,7 @@
         <v>46231.671014259264</v>
       </c>
       <c r="E415" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F415" s="10" t="s">
         <v>26</v>
@@ -24884,7 +24884,7 @@
         <v>618</v>
       </c>
       <c r="O415" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P415" s="10" t="s">
         <v>618</v>
@@ -24907,7 +24907,7 @@
         <v>46231.671010289356</v>
       </c>
       <c r="E416" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F416" s="6" t="s">
         <v>26</v>
@@ -24937,7 +24937,7 @@
         <v>618</v>
       </c>
       <c r="O416" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P416" s="6" t="s">
         <v>618</v>
@@ -24960,7 +24960,7 @@
         <v>46231.67100728009</v>
       </c>
       <c r="E417" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F417" s="10" t="s">
         <v>26</v>
@@ -24990,7 +24990,7 @@
         <v>618</v>
       </c>
       <c r="O417" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P417" s="10" t="s">
         <v>618</v>
@@ -25013,7 +25013,7 @@
         <v>46231.67100423611</v>
       </c>
       <c r="E418" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F418" s="6" t="s">
         <v>26</v>
@@ -25043,7 +25043,7 @@
         <v>618</v>
       </c>
       <c r="O418" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P418" s="6" t="s">
         <v>618</v>
@@ -25066,7 +25066,7 @@
         <v>46231.6710006713</v>
       </c>
       <c r="E419" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F419" s="10" t="s">
         <v>26</v>
@@ -25096,7 +25096,7 @@
         <v>618</v>
       </c>
       <c r="O419" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P419" s="10" t="s">
         <v>618</v>
@@ -25119,7 +25119,7 @@
         <v>46231.67099731481</v>
       </c>
       <c r="E420" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F420" s="6" t="s">
         <v>26</v>
@@ -25149,7 +25149,7 @@
         <v>618</v>
       </c>
       <c r="O420" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P420" s="6" t="s">
         <v>618</v>
@@ -25172,7 +25172,7 @@
         <v>46231.67098568287</v>
       </c>
       <c r="E421" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F421" s="10" t="s">
         <v>26</v>
@@ -25202,7 +25202,7 @@
         <v>618</v>
       </c>
       <c r="O421" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P421" s="10" t="s">
         <v>618</v>
@@ -25225,7 +25225,7 @@
         <v>46231.670985115736</v>
       </c>
       <c r="E422" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F422" s="6" t="s">
         <v>26</v>
@@ -25255,7 +25255,7 @@
         <v>618</v>
       </c>
       <c r="O422" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P422" s="6" t="s">
         <v>618</v>
@@ -25278,7 +25278,7 @@
         <v>46231.67098739583</v>
       </c>
       <c r="E423" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F423" s="10" t="s">
         <v>26</v>
@@ -25308,7 +25308,7 @@
         <v>618</v>
       </c>
       <c r="O423" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P423" s="10" t="s">
         <v>618</v>
@@ -25426,7 +25426,7 @@
         <v>0</v>
       </c>
       <c r="U425" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="426" spans="1:21" x14ac:dyDescent="0.25">
@@ -25489,7 +25489,7 @@
         <v>0</v>
       </c>
       <c r="U426" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -621,34 +621,34 @@
     <t xml:space="preserve">Bodega ,Control de calidad corte Laser OT 4382 - OT 4383 </t>
   </si>
   <si>
+    <t>1216950739647079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma   OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950828741855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion mecanizado  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad Mecanizado  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950739657964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte Laser OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216950739647079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma   OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950828741855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion mecanizado  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad Mecanizado  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950739657964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte Laser OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1216950739657987</t>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46267.16901923611</v>
+        <v>46268.20746693287</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>186</v>
@@ -6526,8 +6526,8 @@
       <c r="R72" s="5">
         <v>46267</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>190</v>
+      <c r="S72" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -6538,17 +6538,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B73" s="9">
         <v>46231.56040099537</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46267.16902148148</v>
+        <v>46268.20746695602</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -6581,7 +6581,7 @@
         <v>98</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q73" s="9">
         <v>46267</v>
@@ -6589,8 +6589,8 @@
       <c r="R73" s="9">
         <v>46267</v>
       </c>
-      <c r="S73" s="12" t="s">
-        <v>190</v>
+      <c r="S73" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -6601,17 +6601,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B74" s="5">
         <v>46231.56041240741</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46267.16902263889</v>
+        <v>46268.207467326385</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6644,7 +6644,7 @@
         <v>106</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q74" s="5">
         <v>46267</v>
@@ -6652,8 +6652,8 @@
       <c r="R74" s="5">
         <v>46267</v>
       </c>
-      <c r="S74" s="12" t="s">
-        <v>190</v>
+      <c r="S74" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -6664,17 +6664,17 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B75" s="9">
         <v>46231.560417534725</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46261.19540744213</v>
+        <v>46268.16879358796</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6707,7 +6707,7 @@
         <v>186</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q75" s="9">
         <v>46268</v>
@@ -6716,7 +6716,7 @@
         <v>46268</v>
       </c>
       <c r="S75" s="12" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="T75" s="10">
         <v>0</v>
@@ -6769,7 +6769,7 @@
         <v>183</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>202</v>
@@ -6781,7 +6781,7 @@
         <v>46268</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46261.19540776621</v>
+        <v>46268.16879915509</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>204</v>
@@ -6832,10 +6832,10 @@
         <v>183</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q77" s="9">
         <v>46268</v>
@@ -6844,7 +6844,7 @@
         <v>46268</v>
       </c>
       <c r="S77" s="12" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         <v>46267</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
@@ -8405,7 +8405,7 @@
         <v>46274</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -648,55 +648,55 @@
     <t xml:space="preserve">Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
+    <t>1216950739657987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216951179504781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216950807714118</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado OT 4382 - OT 4383  ,Preparacion materiales OT 4382 - OT 4383   ,Armado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950807714130</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Caldereria,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1216950828770257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216950739657987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Bodega ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216951179504781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216950807714118</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado OT 4382 - OT 4383  ,Preparacion materiales OT 4382 - OT 4383   ,Armado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950807714130</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Caldereria,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216950828770257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1216951179525264</t>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46268.16879358796</v>
+        <v>46269.19417200232</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>197</v>
@@ -6715,8 +6715,8 @@
       <c r="R75" s="9">
         <v>46268</v>
       </c>
-      <c r="S75" s="12" t="s">
-        <v>199</v>
+      <c r="S75" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T75" s="10">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B76" s="5">
         <v>46231.560422361115</v>
@@ -6736,10 +6736,10 @@
         <v>46260.662343703705</v>
       </c>
       <c r="D76" s="5">
-        <v>46261.19540667824</v>
+        <v>46269.194171759256</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6772,7 +6772,7 @@
         <v>191</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q76" s="5">
         <v>46268</v>
@@ -6780,8 +6780,8 @@
       <c r="R76" s="5">
         <v>46268</v>
       </c>
-      <c r="S76" s="12" t="s">
-        <v>199</v>
+      <c r="S76" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6792,17 +6792,17 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B77" s="9">
         <v>46231.56042736111</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46268.16879915509</v>
+        <v>46269.1941724537</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6843,8 +6843,8 @@
       <c r="R77" s="9">
         <v>46268</v>
       </c>
-      <c r="S77" s="12" t="s">
-        <v>199</v>
+      <c r="S77" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
@@ -6855,7 +6855,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B78" s="5">
         <v>46231.560432708335</v>
@@ -6865,7 +6865,7 @@
         <v>46231.65338133102</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6889,7 +6889,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6902,7 +6902,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B79" s="9">
         <v>46231.5604353588</v>
@@ -6918,10 +6918,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I79" s="9">
         <v>46269</v>
@@ -6939,13 +6939,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>73</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q79" s="9">
         <v>46266</v>
@@ -6960,12 +6960,12 @@
         <v>0</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B80" s="5">
         <v>46231.56044074074</v>
@@ -6975,16 +6975,16 @@
         <v>46266.20265497685</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I80" s="5">
         <v>46274</v>
@@ -7002,13 +7002,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q80" s="5">
         <v>46273</v>
@@ -7017,13 +7017,13 @@
         <v>46267</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -7044,10 +7044,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -7065,7 +7065,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>217</v>
@@ -7097,10 +7097,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I82" s="5">
         <v>46274</v>
@@ -7118,7 +7118,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>220</v>
@@ -7150,10 +7150,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I83" s="9">
         <v>46274</v>
@@ -7171,7 +7171,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>223</v>
@@ -7203,10 +7203,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I84" s="5">
         <v>46274</v>
@@ -7224,7 +7224,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>225</v>
@@ -7256,10 +7256,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I85" s="9">
         <v>46274</v>
@@ -7277,7 +7277,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>225</v>
@@ -7309,10 +7309,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I86" s="5">
         <v>46274</v>
@@ -7330,7 +7330,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>228</v>
@@ -7362,10 +7362,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I87" s="9">
         <v>46274</v>
@@ -7383,7 +7383,7 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>225</v>
@@ -7415,10 +7415,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I88" s="5">
         <v>46274</v>
@@ -7436,7 +7436,7 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>225</v>
@@ -7468,10 +7468,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I89" s="9">
         <v>46274</v>
@@ -7489,7 +7489,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>225</v>
@@ -7521,10 +7521,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I90" s="5">
         <v>46274</v>
@@ -7542,7 +7542,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>225</v>
@@ -7574,10 +7574,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7595,7 +7595,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>225</v>
@@ -7627,10 +7627,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I92" s="5">
         <v>46274</v>
@@ -7648,7 +7648,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>225</v>
@@ -7680,10 +7680,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I93" s="9">
         <v>46274</v>
@@ -7701,7 +7701,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>228</v>
@@ -7733,10 +7733,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I94" s="5">
         <v>46274</v>
@@ -7754,7 +7754,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>225</v>
@@ -7786,10 +7786,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I95" s="9">
         <v>46274</v>
@@ -7807,7 +7807,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>225</v>
@@ -7839,10 +7839,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I96" s="5">
         <v>46274</v>
@@ -7860,7 +7860,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>225</v>
@@ -7892,10 +7892,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I97" s="9">
         <v>46274</v>
@@ -7913,7 +7913,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>225</v>
@@ -7945,10 +7945,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I98" s="5">
         <v>46274</v>
@@ -7966,7 +7966,7 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>225</v>
@@ -7998,10 +7998,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I99" s="9">
         <v>46274</v>
@@ -8019,7 +8019,7 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>228</v>
@@ -8051,10 +8051,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I100" s="5">
         <v>46274</v>
@@ -8072,7 +8072,7 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>225</v>
@@ -8104,10 +8104,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I101" s="9">
         <v>46274</v>
@@ -8125,7 +8125,7 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>228</v>
@@ -8157,10 +8157,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I102" s="5">
         <v>46274</v>
@@ -8178,7 +8178,7 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>225</v>
@@ -8210,10 +8210,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I103" s="9">
         <v>46274</v>
@@ -8231,7 +8231,7 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>228</v>
@@ -8263,10 +8263,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I104" s="5">
         <v>46274</v>
@@ -8284,7 +8284,7 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>225</v>
@@ -8316,10 +8316,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I105" s="9">
         <v>46274</v>
@@ -8337,7 +8337,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>225</v>
@@ -8390,13 +8390,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>252</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q106" s="5">
         <v>46274</v>
@@ -8405,13 +8405,13 @@
         <v>46274</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
       <c r="U106" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -22561,10 +22561,10 @@
         <v>26</v>
       </c>
       <c r="G372" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H372" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H372" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I372" s="5">
         <v>46303</v>
@@ -22585,7 +22585,7 @@
         <v>518</v>
       </c>
       <c r="O372" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P372" s="6" t="s">
         <v>518</v>
@@ -22624,10 +22624,10 @@
         <v>26</v>
       </c>
       <c r="G373" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H373" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H373" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I373" s="9">
         <v>46303</v>
@@ -22677,10 +22677,10 @@
         <v>26</v>
       </c>
       <c r="G374" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H374" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H374" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I374" s="5">
         <v>46303</v>
@@ -22730,10 +22730,10 @@
         <v>26</v>
       </c>
       <c r="G375" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H375" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H375" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I375" s="9">
         <v>46303</v>
@@ -22783,10 +22783,10 @@
         <v>26</v>
       </c>
       <c r="G376" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H376" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H376" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I376" s="5">
         <v>46303</v>
@@ -22836,10 +22836,10 @@
         <v>26</v>
       </c>
       <c r="G377" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H377" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H377" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I377" s="9">
         <v>46303</v>
@@ -22889,10 +22889,10 @@
         <v>26</v>
       </c>
       <c r="G378" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H378" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H378" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I378" s="5">
         <v>46303</v>
@@ -22942,10 +22942,10 @@
         <v>26</v>
       </c>
       <c r="G379" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H379" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H379" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I379" s="9">
         <v>46303</v>
@@ -22995,10 +22995,10 @@
         <v>26</v>
       </c>
       <c r="G380" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H380" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H380" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I380" s="5">
         <v>46303</v>
@@ -23048,10 +23048,10 @@
         <v>26</v>
       </c>
       <c r="G381" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H381" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H381" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I381" s="9">
         <v>46303</v>
@@ -23101,10 +23101,10 @@
         <v>26</v>
       </c>
       <c r="G382" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H382" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H382" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I382" s="5">
         <v>46303</v>
@@ -23154,10 +23154,10 @@
         <v>26</v>
       </c>
       <c r="G383" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H383" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H383" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I383" s="9">
         <v>46303</v>
@@ -23207,10 +23207,10 @@
         <v>26</v>
       </c>
       <c r="G384" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H384" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H384" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I384" s="5">
         <v>46303</v>
@@ -23260,10 +23260,10 @@
         <v>26</v>
       </c>
       <c r="G385" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H385" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H385" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I385" s="9">
         <v>46303</v>
@@ -23313,10 +23313,10 @@
         <v>26</v>
       </c>
       <c r="G386" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H386" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H386" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I386" s="5">
         <v>46303</v>
@@ -23366,10 +23366,10 @@
         <v>26</v>
       </c>
       <c r="G387" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H387" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H387" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I387" s="9">
         <v>46303</v>
@@ -23419,10 +23419,10 @@
         <v>26</v>
       </c>
       <c r="G388" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H388" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H388" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I388" s="5">
         <v>46303</v>
@@ -23472,10 +23472,10 @@
         <v>26</v>
       </c>
       <c r="G389" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H389" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H389" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I389" s="9">
         <v>46303</v>
@@ -23525,10 +23525,10 @@
         <v>26</v>
       </c>
       <c r="G390" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H390" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H390" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I390" s="5">
         <v>46303</v>
@@ -23578,10 +23578,10 @@
         <v>26</v>
       </c>
       <c r="G391" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H391" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H391" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I391" s="9">
         <v>46303</v>
@@ -23631,10 +23631,10 @@
         <v>26</v>
       </c>
       <c r="G392" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H392" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H392" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I392" s="5">
         <v>46303</v>
@@ -23684,10 +23684,10 @@
         <v>26</v>
       </c>
       <c r="G393" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H393" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H393" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I393" s="9">
         <v>46303</v>
@@ -23737,10 +23737,10 @@
         <v>26</v>
       </c>
       <c r="G394" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H394" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H394" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I394" s="5">
         <v>46303</v>
@@ -23790,10 +23790,10 @@
         <v>26</v>
       </c>
       <c r="G395" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H395" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H395" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I395" s="9">
         <v>46303</v>
@@ -23843,10 +23843,10 @@
         <v>26</v>
       </c>
       <c r="G396" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H396" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H396" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I396" s="5">
         <v>46303</v>
@@ -23896,10 +23896,10 @@
         <v>26</v>
       </c>
       <c r="G397" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H397" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H397" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I397" s="9">
         <v>46303</v>
@@ -23949,10 +23949,10 @@
         <v>26</v>
       </c>
       <c r="G398" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H398" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H398" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I398" s="5">
         <v>46304</v>
@@ -24012,10 +24012,10 @@
         <v>26</v>
       </c>
       <c r="G399" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H399" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H399" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I399" s="9">
         <v>46304</v>
@@ -24065,10 +24065,10 @@
         <v>26</v>
       </c>
       <c r="G400" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H400" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H400" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I400" s="5">
         <v>46304</v>
@@ -24118,10 +24118,10 @@
         <v>26</v>
       </c>
       <c r="G401" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H401" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H401" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I401" s="9">
         <v>46304</v>
@@ -24171,10 +24171,10 @@
         <v>26</v>
       </c>
       <c r="G402" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H402" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H402" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I402" s="5">
         <v>46304</v>
@@ -24224,10 +24224,10 @@
         <v>26</v>
       </c>
       <c r="G403" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H403" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H403" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I403" s="9">
         <v>46304</v>
@@ -24277,10 +24277,10 @@
         <v>26</v>
       </c>
       <c r="G404" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H404" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H404" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I404" s="5">
         <v>46304</v>
@@ -24330,10 +24330,10 @@
         <v>26</v>
       </c>
       <c r="G405" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H405" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H405" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I405" s="9">
         <v>46304</v>
@@ -24383,10 +24383,10 @@
         <v>26</v>
       </c>
       <c r="G406" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H406" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H406" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I406" s="5">
         <v>46304</v>
@@ -24436,10 +24436,10 @@
         <v>26</v>
       </c>
       <c r="G407" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H407" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H407" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I407" s="9">
         <v>46304</v>
@@ -24489,10 +24489,10 @@
         <v>26</v>
       </c>
       <c r="G408" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H408" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H408" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I408" s="5">
         <v>46304</v>
@@ -24542,10 +24542,10 @@
         <v>26</v>
       </c>
       <c r="G409" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H409" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H409" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I409" s="9">
         <v>46304</v>
@@ -24595,10 +24595,10 @@
         <v>26</v>
       </c>
       <c r="G410" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H410" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H410" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I410" s="5">
         <v>46304</v>
@@ -24648,10 +24648,10 @@
         <v>26</v>
       </c>
       <c r="G411" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H411" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H411" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I411" s="9">
         <v>46304</v>
@@ -24701,10 +24701,10 @@
         <v>26</v>
       </c>
       <c r="G412" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H412" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H412" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I412" s="5">
         <v>46304</v>
@@ -24754,10 +24754,10 @@
         <v>26</v>
       </c>
       <c r="G413" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H413" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H413" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I413" s="9">
         <v>46304</v>
@@ -24807,10 +24807,10 @@
         <v>26</v>
       </c>
       <c r="G414" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H414" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H414" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I414" s="5">
         <v>46304</v>
@@ -24860,10 +24860,10 @@
         <v>26</v>
       </c>
       <c r="G415" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H415" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H415" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I415" s="9">
         <v>46304</v>
@@ -24913,10 +24913,10 @@
         <v>26</v>
       </c>
       <c r="G416" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H416" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H416" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I416" s="5">
         <v>46304</v>
@@ -24966,10 +24966,10 @@
         <v>26</v>
       </c>
       <c r="G417" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H417" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H417" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I417" s="9">
         <v>46304</v>
@@ -25019,10 +25019,10 @@
         <v>26</v>
       </c>
       <c r="G418" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H418" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H418" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I418" s="5">
         <v>46304</v>
@@ -25072,10 +25072,10 @@
         <v>26</v>
       </c>
       <c r="G419" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H419" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H419" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I419" s="9">
         <v>46304</v>
@@ -25125,10 +25125,10 @@
         <v>26</v>
       </c>
       <c r="G420" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H420" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H420" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I420" s="5">
         <v>46304</v>
@@ -25178,10 +25178,10 @@
         <v>26</v>
       </c>
       <c r="G421" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H421" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H421" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I421" s="9">
         <v>46304</v>
@@ -25231,10 +25231,10 @@
         <v>26</v>
       </c>
       <c r="G422" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H422" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H422" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I422" s="5">
         <v>46304</v>
@@ -25284,10 +25284,10 @@
         <v>26</v>
       </c>
       <c r="G423" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H423" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H423" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I423" s="9">
         <v>46304</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46267.182629375</v>
+        <v>46273.16887540509</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>74</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -696,118 +696,118 @@
     <t>ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
+    <t>1216951179525264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado  OT 4382 - OT 4383 ,Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Corte plasma  OT 4382 - OT 4383  ,Check Planos  OT 4382 - OT 4383 ,Preparacion materiales OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Armado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950828786955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Planos  OT 4382 - OT 4383 ,Preparacion materiales OT 4382 - OT 4383   ,Control de calidad Mecanizado  OT 4382 - OT 4383 ,Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950807727165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Corte plasma  OT 4382 - OT 4383  ,Control de calidad Mecanizado  OT 4382 - OT 4383 ,Check Planos  OT 4382 - OT 4383 ,Preparacion materiales OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>1216950739712535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparacion materiales OT 4382 - OT 4383   ,Check Planos  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216916670896976</t>
+  </si>
+  <si>
+    <t>1216916670896977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Planos  OT 4382 - OT 4383 ,Preparacion materiales OT 4382 - OT 4383   </t>
+  </si>
+  <si>
+    <t>1216916670896978</t>
+  </si>
+  <si>
+    <t>1216916670896979</t>
+  </si>
+  <si>
+    <t>1216916670896980</t>
+  </si>
+  <si>
+    <t>1216916670896981</t>
+  </si>
+  <si>
+    <t>1216916670896982</t>
+  </si>
+  <si>
+    <t>1216916670896983</t>
+  </si>
+  <si>
+    <t>1216916670896984</t>
+  </si>
+  <si>
+    <t>1216916670896985</t>
+  </si>
+  <si>
+    <t>1216916670896986</t>
+  </si>
+  <si>
+    <t>1216916670896987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,Armado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216916670896988</t>
+  </si>
+  <si>
+    <t>1216916670896990</t>
+  </si>
+  <si>
+    <t>Armado OT 4382 - OT 4383  ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216916670896992</t>
+  </si>
+  <si>
+    <t>1216916670896993</t>
+  </si>
+  <si>
+    <t>1216916670896994</t>
+  </si>
+  <si>
+    <t>1216916670896995</t>
+  </si>
+  <si>
+    <t>1216916670896996</t>
+  </si>
+  <si>
+    <t>1216916670896991</t>
+  </si>
+  <si>
+    <t>1216916670896989</t>
+  </si>
+  <si>
+    <t>1216950739385369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216951179525264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado  OT 4382 - OT 4383 ,Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Corte plasma  OT 4382 - OT 4383  ,Check Planos  OT 4382 - OT 4383 ,Preparacion materiales OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Armado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950828786955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Planos  OT 4382 - OT 4383 ,Preparacion materiales OT 4382 - OT 4383   ,Control de calidad Mecanizado  OT 4382 - OT 4383 ,Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Corte plasma  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950807727165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte Laser OT 4382 - OT 4383 ,Control de calidad Corte plasma  OT 4382 - OT 4383  ,Control de calidad Mecanizado  OT 4382 - OT 4383 ,Check Planos  OT 4382 - OT 4383 ,Preparacion materiales OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>1216950739712535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparacion materiales OT 4382 - OT 4383   ,Check Planos  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216916670896976</t>
-  </si>
-  <si>
-    <t>1216916670896977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Planos  OT 4382 - OT 4383 ,Preparacion materiales OT 4382 - OT 4383   </t>
-  </si>
-  <si>
-    <t>1216916670896978</t>
-  </si>
-  <si>
-    <t>1216916670896979</t>
-  </si>
-  <si>
-    <t>1216916670896980</t>
-  </si>
-  <si>
-    <t>1216916670896981</t>
-  </si>
-  <si>
-    <t>1216916670896982</t>
-  </si>
-  <si>
-    <t>1216916670896983</t>
-  </si>
-  <si>
-    <t>1216916670896984</t>
-  </si>
-  <si>
-    <t>1216916670896985</t>
-  </si>
-  <si>
-    <t>1216916670896986</t>
-  </si>
-  <si>
-    <t>1216916670896987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,Armado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216916670896988</t>
-  </si>
-  <si>
-    <t>1216916670896990</t>
-  </si>
-  <si>
-    <t>Armado OT 4382 - OT 4383  ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216916670896992</t>
-  </si>
-  <si>
-    <t>1216916670896993</t>
-  </si>
-  <si>
-    <t>1216916670896994</t>
-  </si>
-  <si>
-    <t>1216916670896995</t>
-  </si>
-  <si>
-    <t>1216916670896996</t>
-  </si>
-  <si>
-    <t>1216916670896991</t>
-  </si>
-  <si>
-    <t>1216916670896989</t>
-  </si>
-  <si>
-    <t>1216950739385369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1216950957290015</t>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46266.20265497685</v>
+        <v>46274.12650756944</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>213</v>
@@ -7016,8 +7016,8 @@
       <c r="R80" s="5">
         <v>46267</v>
       </c>
-      <c r="S80" s="12" t="s">
-        <v>215</v>
+      <c r="S80" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
@@ -7028,7 +7028,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B81" s="9">
         <v>46231.560445104165</v>
@@ -7068,10 +7068,10 @@
         <v>213</v>
       </c>
       <c r="O81" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>218</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -7081,7 +7081,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B82" s="5">
         <v>46231.560451550926</v>
@@ -7121,10 +7121,10 @@
         <v>213</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -7134,7 +7134,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B83" s="9">
         <v>46231.56045803241</v>
@@ -7174,10 +7174,10 @@
         <v>213</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B84" s="5">
         <v>46231.560464525464</v>
@@ -7227,10 +7227,10 @@
         <v>213</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -7240,7 +7240,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B85" s="9">
         <v>46231.56788371528</v>
@@ -7280,10 +7280,10 @@
         <v>213</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B86" s="5">
         <v>46231.567891875005</v>
@@ -7333,10 +7333,10 @@
         <v>213</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B87" s="9">
         <v>46231.56790112269</v>
@@ -7386,10 +7386,10 @@
         <v>213</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B88" s="5">
         <v>46231.56790915509</v>
@@ -7439,10 +7439,10 @@
         <v>213</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7452,7 +7452,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B89" s="9">
         <v>46231.567918981484</v>
@@ -7492,10 +7492,10 @@
         <v>213</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B90" s="5">
         <v>46231.56792915509</v>
@@ -7545,10 +7545,10 @@
         <v>213</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7558,7 +7558,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B91" s="9">
         <v>46231.56793802083</v>
@@ -7598,10 +7598,10 @@
         <v>213</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7611,7 +7611,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B92" s="5">
         <v>46231.567949178236</v>
@@ -7651,10 +7651,10 @@
         <v>213</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7664,7 +7664,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B93" s="9">
         <v>46231.567958263884</v>
@@ -7704,10 +7704,10 @@
         <v>213</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7717,7 +7717,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B94" s="5">
         <v>46231.567968240735</v>
@@ -7757,10 +7757,10 @@
         <v>213</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7770,7 +7770,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B95" s="9">
         <v>46231.567976921295</v>
@@ -7810,10 +7810,10 @@
         <v>213</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7823,7 +7823,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B96" s="5">
         <v>46231.56803997685</v>
@@ -7863,10 +7863,10 @@
         <v>213</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7876,7 +7876,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B97" s="9">
         <v>46231.56805166666</v>
@@ -7916,10 +7916,10 @@
         <v>213</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B98" s="5">
         <v>46231.56807842593</v>
@@ -7969,10 +7969,10 @@
         <v>213</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7982,7 +7982,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B99" s="9">
         <v>46231.56814173611</v>
@@ -8022,10 +8022,10 @@
         <v>213</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -8035,7 +8035,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B100" s="5">
         <v>46231.568154374996</v>
@@ -8075,10 +8075,10 @@
         <v>213</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B101" s="9">
         <v>46231.56816440972</v>
@@ -8128,10 +8128,10 @@
         <v>213</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -8141,7 +8141,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B102" s="5">
         <v>46231.568173472224</v>
@@ -8181,10 +8181,10 @@
         <v>213</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8194,7 +8194,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B103" s="9">
         <v>46231.568183854164</v>
@@ -8234,10 +8234,10 @@
         <v>213</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -8247,7 +8247,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B104" s="5">
         <v>46231.56808208334</v>
@@ -8287,10 +8287,10 @@
         <v>213</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8300,7 +8300,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B105" s="9">
         <v>46231.56805582176</v>
@@ -8340,10 +8340,10 @@
         <v>213</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B106" s="5">
         <v>46231.56051829861</v>
@@ -8363,7 +8363,7 @@
         <v>46267.17693162037</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8393,7 +8393,7 @@
         <v>205</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>205</v>
@@ -8405,7 +8405,7 @@
         <v>46274</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -8453,7 +8453,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>254</v>
@@ -8506,7 +8506,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>254</v>
@@ -8559,7 +8559,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>258</v>
@@ -8612,7 +8612,7 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>134</v>
@@ -8665,7 +8665,7 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>258</v>
@@ -8718,7 +8718,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>254</v>
@@ -8771,7 +8771,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O113" s="10" t="s">
         <v>254</v>
@@ -8824,7 +8824,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>134</v>
@@ -8877,7 +8877,7 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>254</v>
@@ -8930,7 +8930,7 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>258</v>
@@ -8983,7 +8983,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>254</v>
@@ -9036,7 +9036,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>134</v>
@@ -9089,7 +9089,7 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>254</v>
@@ -9142,7 +9142,7 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>134</v>
@@ -9195,7 +9195,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>134</v>
@@ -9248,7 +9248,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>138</v>
@@ -9301,7 +9301,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>138</v>
@@ -9354,7 +9354,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>138</v>
@@ -9407,7 +9407,7 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>138</v>
@@ -9460,7 +9460,7 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>138</v>
@@ -9513,7 +9513,7 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>279</v>
@@ -9566,7 +9566,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>138</v>
@@ -9619,7 +9619,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O129" s="10" t="s">
         <v>138</v>
@@ -9672,7 +9672,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>283</v>
@@ -9725,7 +9725,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>283</v>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46231.667687002315</v>
+        <v>46274.16181846065</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>301</v>
@@ -10075,8 +10075,8 @@
       <c r="R137" s="9">
         <v>46275</v>
       </c>
-      <c r="S137" s="7" t="s">
-        <v>32</v>
+      <c r="S137" s="12" t="s">
+        <v>252</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -807,157 +807,157 @@
     <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
+    <t>1216950957290015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Check Planos  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Control de calidad Armado OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950957290038</t>
+  </si>
+  <si>
+    <t>1216951179605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950739771595</t>
+  </si>
+  <si>
+    <t>1216916670896997</t>
+  </si>
+  <si>
+    <t>1216916670896998</t>
+  </si>
+  <si>
+    <t>1216916670896999</t>
+  </si>
+  <si>
+    <t>1216916670897000</t>
+  </si>
+  <si>
+    <t>1216916670897001</t>
+  </si>
+  <si>
+    <t>1216916670897002</t>
+  </si>
+  <si>
+    <t>1216916670897003</t>
+  </si>
+  <si>
+    <t>1216916670897004</t>
+  </si>
+  <si>
+    <t>1216916670897005</t>
+  </si>
+  <si>
+    <t>1216916670897006</t>
+  </si>
+  <si>
+    <t>1216916670897007</t>
+  </si>
+  <si>
+    <t>1216916670897008</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado OT 4382 - OT 4383  ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216916670897009</t>
+  </si>
+  <si>
+    <t>1216916670897010</t>
+  </si>
+  <si>
+    <t>1216916670897011</t>
+  </si>
+  <si>
+    <t>1216916670897012</t>
+  </si>
+  <si>
+    <t>1216916670897013</t>
+  </si>
+  <si>
+    <t>Check Planos  OT 4382 - OT 4383 ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216916670897014</t>
+  </si>
+  <si>
+    <t>1216916670897015</t>
+  </si>
+  <si>
+    <t>1216916670897017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,Check Planos  OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216916670897018</t>
+  </si>
+  <si>
+    <t>1216950739771613</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion motor OT 4382 - OT 4383 ,Recepcion Alabe OT 4382 - OT 4383 ,Recepcion Rodete OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950807824354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950807824377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Rodete OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Bodega:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950828871461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion motor OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950739783663</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento OT 4382 - OT 4383 ,Montaje motor OT 4382 - OT 4383,Montaje rodete OT 4382 - OT 4383,Armado de rodete  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>1216950739783675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216950957290015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Check Planos  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Control de calidad Armado OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950957290038</t>
-  </si>
-  <si>
-    <t>1216951179605164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Planos  OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado OT 4382 - OT 4383  ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950739771595</t>
-  </si>
-  <si>
-    <t>1216916670896997</t>
-  </si>
-  <si>
-    <t>1216916670896998</t>
-  </si>
-  <si>
-    <t>1216916670896999</t>
-  </si>
-  <si>
-    <t>1216916670897000</t>
-  </si>
-  <si>
-    <t>1216916670897001</t>
-  </si>
-  <si>
-    <t>1216916670897002</t>
-  </si>
-  <si>
-    <t>1216916670897003</t>
-  </si>
-  <si>
-    <t>1216916670897004</t>
-  </si>
-  <si>
-    <t>1216916670897005</t>
-  </si>
-  <si>
-    <t>1216916670897006</t>
-  </si>
-  <si>
-    <t>1216916670897007</t>
-  </si>
-  <si>
-    <t>1216916670897008</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado OT 4382 - OT 4383  ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216916670897009</t>
-  </si>
-  <si>
-    <t>1216916670897010</t>
-  </si>
-  <si>
-    <t>1216916670897011</t>
-  </si>
-  <si>
-    <t>1216916670897012</t>
-  </si>
-  <si>
-    <t>1216916670897013</t>
-  </si>
-  <si>
-    <t>Check Planos  OT 4382 - OT 4383 ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216916670897014</t>
-  </si>
-  <si>
-    <t>1216916670897015</t>
-  </si>
-  <si>
-    <t>1216916670897017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,Check Planos  OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216916670897018</t>
-  </si>
-  <si>
-    <t>1216950739771613</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion motor OT 4382 - OT 4383 ,Recepcion Alabe OT 4382 - OT 4383 ,Recepcion Rodete OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950807824354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950807824377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Rodete OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Bodega:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950828871461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion motor OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950739783663</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento OT 4382 - OT 4383 ,Montaje motor OT 4382 - OT 4383,Montaje rodete OT 4382 - OT 4383,Armado de rodete  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>1216950739783675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1216950807852788</t>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46267.17693162037</v>
+        <v>46275.13813133102</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>250</v>
@@ -8404,8 +8404,8 @@
       <c r="R106" s="5">
         <v>46274</v>
       </c>
-      <c r="S106" s="12" t="s">
-        <v>252</v>
+      <c r="S106" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B107" s="9">
         <v>46231.56052395834</v>
@@ -8456,10 +8456,10 @@
         <v>250</v>
       </c>
       <c r="O107" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="P107" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="P107" s="10" t="s">
-        <v>255</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -8469,7 +8469,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B108" s="5">
         <v>46231.56052922454</v>
@@ -8509,10 +8509,10 @@
         <v>250</v>
       </c>
       <c r="O108" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B109" s="9">
         <v>46231.560534212964</v>
@@ -8562,10 +8562,10 @@
         <v>250</v>
       </c>
       <c r="O109" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="P109" s="10" t="s">
         <v>258</v>
-      </c>
-      <c r="P109" s="10" t="s">
-        <v>259</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8575,7 +8575,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B110" s="5">
         <v>46231.560539479164</v>
@@ -8618,7 +8618,7 @@
         <v>134</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B111" s="9">
         <v>46231.56832815972</v>
@@ -8668,10 +8668,10 @@
         <v>250</v>
       </c>
       <c r="O111" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>258</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>259</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8681,7 +8681,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B112" s="5">
         <v>46231.56833731481</v>
@@ -8721,10 +8721,10 @@
         <v>250</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8734,7 +8734,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B113" s="9">
         <v>46231.56834770834</v>
@@ -8774,10 +8774,10 @@
         <v>250</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8787,7 +8787,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B114" s="5">
         <v>46231.56835971065</v>
@@ -8830,7 +8830,7 @@
         <v>134</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8840,7 +8840,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B115" s="9">
         <v>46231.56837003472</v>
@@ -8880,10 +8880,10 @@
         <v>250</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8893,7 +8893,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B116" s="5">
         <v>46231.56838118055</v>
@@ -8933,10 +8933,10 @@
         <v>250</v>
       </c>
       <c r="O116" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="P116" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B117" s="9">
         <v>46231.56839273148</v>
@@ -8986,10 +8986,10 @@
         <v>250</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8999,7 +8999,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B118" s="5">
         <v>46231.568401666664</v>
@@ -9042,7 +9042,7 @@
         <v>134</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -9052,7 +9052,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B119" s="9">
         <v>46231.56841270834</v>
@@ -9092,10 +9092,10 @@
         <v>250</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -9105,7 +9105,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B120" s="5">
         <v>46231.56842167824</v>
@@ -9148,7 +9148,7 @@
         <v>134</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -9158,7 +9158,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B121" s="9">
         <v>46231.56843238426</v>
@@ -9201,7 +9201,7 @@
         <v>134</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -9211,7 +9211,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B122" s="5">
         <v>46231.56848189815</v>
@@ -9254,7 +9254,7 @@
         <v>138</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B123" s="9">
         <v>46231.56849222222</v>
@@ -9307,7 +9307,7 @@
         <v>138</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9317,7 +9317,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B124" s="5">
         <v>46231.568500995374</v>
@@ -9360,7 +9360,7 @@
         <v>138</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9370,7 +9370,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B125" s="9">
         <v>46231.56851067129</v>
@@ -9413,7 +9413,7 @@
         <v>138</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B126" s="5">
         <v>46231.56851788194</v>
@@ -9466,7 +9466,7 @@
         <v>138</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9476,7 +9476,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B127" s="9">
         <v>46231.56852594907</v>
@@ -9516,10 +9516,10 @@
         <v>250</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9529,7 +9529,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B128" s="5">
         <v>46231.56854065972</v>
@@ -9572,7 +9572,7 @@
         <v>138</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9582,7 +9582,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B129" s="9">
         <v>46231.56855627315</v>
@@ -9625,7 +9625,7 @@
         <v>138</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9635,7 +9635,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B130" s="5">
         <v>46231.56856540509</v>
@@ -9675,10 +9675,10 @@
         <v>250</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9688,7 +9688,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B131" s="9">
         <v>46231.56862815972</v>
@@ -9728,10 +9728,10 @@
         <v>250</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9741,7 +9741,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B132" s="5">
         <v>46231.56054324074</v>
@@ -9751,7 +9751,7 @@
         <v>46231.65316503472</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>25</v>
@@ -9775,7 +9775,7 @@
         <v>26</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>26</v>
@@ -9788,7 +9788,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B133" s="9">
         <v>46231.560546215274</v>
@@ -9798,7 +9798,7 @@
         <v>46238.17175262731</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9825,13 +9825,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>52</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q133" s="9">
         <v>46231</v>
@@ -9851,7 +9851,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B134" s="5">
         <v>46231.560551215276</v>
@@ -9861,7 +9861,7 @@
         <v>46238.17175491898</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9888,13 +9888,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q134" s="5">
         <v>46231</v>
@@ -9914,7 +9914,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B135" s="9">
         <v>46231.560557199075</v>
@@ -9924,7 +9924,7 @@
         <v>46238.171760439815</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9951,13 +9951,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q135" s="9">
         <v>46231</v>
@@ -9977,7 +9977,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B136" s="5">
         <v>46231.56056219907</v>
@@ -9987,7 +9987,7 @@
         <v>46231.654316886576</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>25</v>
@@ -10011,7 +10011,7 @@
         <v>26</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>26</v>
@@ -10024,7 +10024,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B137" s="9">
         <v>46231.560565277774</v>
@@ -10034,7 +10034,7 @@
         <v>46274.16181846065</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -10061,13 +10061,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q137" s="9">
         <v>46281</v>
@@ -10076,7 +10076,7 @@
         <v>46275</v>
       </c>
       <c r="S137" s="12" t="s">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
@@ -10124,7 +10124,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>134</v>
@@ -10177,7 +10177,7 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>134</v>
@@ -10230,7 +10230,7 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>134</v>
@@ -10283,7 +10283,7 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O141" s="10" t="s">
         <v>134</v>
@@ -10336,13 +10336,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>134</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10389,13 +10389,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O143" s="10" t="s">
         <v>134</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10442,13 +10442,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>134</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10495,13 +10495,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O145" s="10" t="s">
         <v>134</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10548,13 +10548,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>134</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10601,13 +10601,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O147" s="10" t="s">
         <v>134</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10654,13 +10654,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>134</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10707,13 +10707,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O149" s="10" t="s">
         <v>134</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10760,13 +10760,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>134</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10813,13 +10813,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O151" s="10" t="s">
         <v>134</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10866,13 +10866,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>134</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10919,13 +10919,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O153" s="10" t="s">
         <v>138</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10972,13 +10972,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -11025,13 +11025,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O155" s="10" t="s">
         <v>138</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -11078,13 +11078,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -11131,13 +11131,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O157" s="10" t="s">
         <v>138</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -11184,13 +11184,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O158" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -11237,13 +11237,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O159" s="10" t="s">
         <v>138</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -11290,13 +11290,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11343,13 +11343,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O161" s="10" t="s">
         <v>138</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11396,13 +11396,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11449,7 +11449,7 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O163" s="10" t="s">
         <v>334</v>
@@ -12837,13 +12837,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O189" s="10" t="s">
         <v>368</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q189" s="9">
         <v>46287</v>
@@ -13115,7 +13115,7 @@
         <v>367</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>367</v>
@@ -13168,7 +13168,7 @@
         <v>367</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P195" s="10" t="s">
         <v>367</v>
@@ -13221,7 +13221,7 @@
         <v>367</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>367</v>
@@ -13274,7 +13274,7 @@
         <v>367</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P197" s="10" t="s">
         <v>367</v>
@@ -13327,7 +13327,7 @@
         <v>367</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>367</v>
@@ -13380,7 +13380,7 @@
         <v>367</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P199" s="10" t="s">
         <v>367</v>
@@ -13433,7 +13433,7 @@
         <v>367</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>367</v>
@@ -13486,7 +13486,7 @@
         <v>367</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P201" s="10" t="s">
         <v>367</v>
@@ -13539,7 +13539,7 @@
         <v>367</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>367</v>
@@ -13592,7 +13592,7 @@
         <v>367</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P203" s="10" t="s">
         <v>367</v>
@@ -13645,7 +13645,7 @@
         <v>367</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>367</v>
@@ -13698,7 +13698,7 @@
         <v>367</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P205" s="10" t="s">
         <v>367</v>
@@ -13751,7 +13751,7 @@
         <v>367</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P206" s="6" t="s">
         <v>367</v>
@@ -13804,7 +13804,7 @@
         <v>367</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P207" s="10" t="s">
         <v>367</v>
@@ -13857,7 +13857,7 @@
         <v>367</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>367</v>
@@ -13910,7 +13910,7 @@
         <v>367</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>367</v>
@@ -13963,7 +13963,7 @@
         <v>367</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>367</v>
@@ -14016,7 +14016,7 @@
         <v>367</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>367</v>
@@ -14069,7 +14069,7 @@
         <v>367</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>367</v>
@@ -14122,7 +14122,7 @@
         <v>367</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>367</v>
@@ -14175,7 +14175,7 @@
         <v>367</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>367</v>
@@ -14225,7 +14225,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>399</v>
@@ -15613,7 +15613,7 @@
         <v>26</v>
       </c>
       <c r="N241" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O241" s="10" t="s">
         <v>431</v>
@@ -16995,7 +16995,7 @@
         <v>26</v>
       </c>
       <c r="N267" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O267" s="10" t="s">
         <v>460</v>
@@ -18377,7 +18377,7 @@
         <v>26</v>
       </c>
       <c r="N293" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O293" s="10" t="s">
         <v>490</v>
